--- a/notas.xlsx
+++ b/notas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/daniloas.com/projetos/FertilidadeSoloAlegreUFES/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B08C8F3-20DA-4849-95EA-6EE3B5FE5C5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3816C1EE-FDB0-D34D-8FF5-A24905722401}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="620" windowWidth="20740" windowHeight="11320" xr2:uid="{BB9E0E1E-73DF-4AB6-A949-07A69840CAF7}"/>
+    <workbookView xWindow="0" yWindow="620" windowWidth="28700" windowHeight="17360" xr2:uid="{BB9E0E1E-73DF-4AB6-A949-07A69840CAF7}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -1421,7 +1421,7 @@
         <v>13</v>
       </c>
       <c r="F27">
-        <v>0.60000000000000009</v>
+        <v>0.6</v>
       </c>
       <c r="G27" t="s">
         <v>10</v>

--- a/notas.xlsx
+++ b/notas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/daniloas.com/projetos/FertilidadeSoloAlegreUFES/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3816C1EE-FDB0-D34D-8FF5-A24905722401}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F05FE502-A6F2-D540-B220-CF65A9210BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="28700" windowHeight="17360" xr2:uid="{BB9E0E1E-73DF-4AB6-A949-07A69840CAF7}"/>
   </bookViews>

--- a/notas.xlsx
+++ b/notas.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11109"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuário\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/daniloas.com/projetos/FertilidadeSoloAlegreUFES/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E72795C6-6815-48FB-86EC-2C10DE2ABD97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D14B25CB-D763-3A48-90FE-1362A7D655E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11310" xr2:uid="{BB9E0E1E-73DF-4AB6-A949-07A69840CAF7}"/>
+    <workbookView xWindow="0" yWindow="620" windowWidth="20740" windowHeight="11320" xr2:uid="{BB9E0E1E-73DF-4AB6-A949-07A69840CAF7}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -42,14 +42,6 @@
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="22">
   <si>
     <t>Matrícula</t>
-  </si>
-  <si>
-    <t>Pontuação 
-dos exercícios extras</t>
-  </si>
-  <si>
-    <t>Pontuação total
-(Prova + Extra)</t>
   </si>
   <si>
     <t>Item a</t>
@@ -107,6 +99,12 @@
   </si>
   <si>
     <t>0/6</t>
+  </si>
+  <si>
+    <t>Pontuação dos exercícios extras</t>
+  </si>
+  <si>
+    <t>Pontuação total (Prova + Extra)</t>
   </si>
 </sst>
 </file>
@@ -567,91 +565,91 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCC50A17-1BAD-4261-9C73-1273FB998B6D}">
   <dimension ref="A1:X65"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.28515625" customWidth="1"/>
+    <col min="2" max="2" width="16.33203125" customWidth="1"/>
     <col min="3" max="3" width="17" customWidth="1"/>
-    <col min="4" max="4" width="26.5703125" customWidth="1"/>
+    <col min="4" max="4" width="26.5" customWidth="1"/>
     <col min="5" max="5" width="7" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:24" ht="33" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="F1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="H1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="I1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="J1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="K1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="L1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="O1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="P1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="R1" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="S1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="T1" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="U1" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="V1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="W1" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="X1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="K1" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="L1" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N1" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="O1" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="P1" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q1" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="R1" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="S1" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="T1" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="U1" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="V1" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="W1" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="X1" s="6" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A2" s="7">
         <v>2023200939</v>
       </c>
@@ -665,31 +663,31 @@
         <v>9.1999999999999993</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F2" s="8">
         <v>0.4</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H2" s="8">
         <v>1</v>
       </c>
       <c r="I2" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J2" s="8">
         <v>1.2</v>
       </c>
       <c r="K2" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L2" s="8">
         <v>1</v>
       </c>
       <c r="M2" s="8" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N2" s="8">
         <v>0.6</v>
@@ -725,7 +723,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A3" s="9">
         <v>2023100005</v>
       </c>
@@ -769,7 +767,7 @@
       <c r="W3" s="8"/>
       <c r="X3" s="8"/>
     </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A4" s="7">
         <v>2021101895</v>
       </c>
@@ -783,31 +781,31 @@
         <v>8.75</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F4" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H4" s="8">
         <v>1</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J4" s="8">
         <v>1.2</v>
       </c>
       <c r="K4" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L4" s="8">
         <v>1</v>
       </c>
       <c r="M4" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="N4" s="8">
         <v>1.2</v>
@@ -843,7 +841,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="9">
         <v>2024101156</v>
       </c>
@@ -857,31 +855,31 @@
         <v>9</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F5" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H5" s="8">
         <v>1</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J5" s="8">
         <v>1.2</v>
       </c>
       <c r="K5" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L5" s="8">
         <v>1</v>
       </c>
       <c r="M5" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="N5" s="8">
         <v>1.2</v>
@@ -917,7 +915,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A6" s="7">
         <v>2023200783</v>
       </c>
@@ -961,7 +959,7 @@
       <c r="W6" s="8"/>
       <c r="X6" s="8"/>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A7" s="9">
         <v>2022200360</v>
       </c>
@@ -975,31 +973,31 @@
         <v>9.3999999999999986</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F7" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H7" s="8">
         <v>1</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J7" s="8">
         <v>1.2</v>
       </c>
       <c r="K7" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L7" s="8">
         <v>1</v>
       </c>
       <c r="M7" s="8" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N7" s="8">
         <v>0.6</v>
@@ -1035,7 +1033,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A8" s="7">
         <v>2024101774</v>
       </c>
@@ -1079,7 +1077,7 @@
       <c r="W8" s="8"/>
       <c r="X8" s="8"/>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A9" s="9">
         <v>2024203414</v>
       </c>
@@ -1093,31 +1091,31 @@
         <v>8.75</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F9" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H9" s="8">
         <v>1</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J9" s="8">
         <v>1.2</v>
       </c>
       <c r="K9" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L9" s="8">
         <v>1</v>
       </c>
       <c r="M9" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="N9" s="8">
         <v>1.2</v>
@@ -1153,7 +1151,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A10" s="7">
         <v>2023101046</v>
       </c>
@@ -1197,7 +1195,7 @@
       <c r="W10" s="8"/>
       <c r="X10" s="8"/>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A11" s="9">
         <v>2019109848</v>
       </c>
@@ -1241,7 +1239,7 @@
       <c r="W11" s="8"/>
       <c r="X11" s="8"/>
     </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A12" s="7">
         <v>2023102012</v>
       </c>
@@ -1255,31 +1253,31 @@
         <v>4.45</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F12" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H12" s="8">
         <v>1</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J12" s="8">
         <v>0.6</v>
       </c>
       <c r="K12" s="8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="L12" s="8">
         <v>0</v>
       </c>
       <c r="M12" s="8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="N12" s="8">
         <v>0</v>
@@ -1315,7 +1313,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A13" s="9">
         <v>2024101768</v>
       </c>
@@ -1359,7 +1357,7 @@
       <c r="W13" s="8"/>
       <c r="X13" s="8"/>
     </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A14" s="7">
         <v>2018104222</v>
       </c>
@@ -1403,7 +1401,7 @@
       <c r="W14" s="8"/>
       <c r="X14" s="8"/>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A15" s="9">
         <v>2017102706</v>
       </c>
@@ -1447,7 +1445,7 @@
       <c r="W15" s="8"/>
       <c r="X15" s="8"/>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A16" s="7">
         <v>2024103491</v>
       </c>
@@ -1491,7 +1489,7 @@
       <c r="W16" s="8"/>
       <c r="X16" s="8"/>
     </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A17" s="9">
         <v>2023100158</v>
       </c>
@@ -1535,7 +1533,7 @@
       <c r="W17" s="8"/>
       <c r="X17" s="8"/>
     </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A18" s="7">
         <v>2024101776</v>
       </c>
@@ -1579,7 +1577,7 @@
       <c r="W18" s="8"/>
       <c r="X18" s="8"/>
     </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A19" s="9">
         <v>2020102895</v>
       </c>
@@ -1623,7 +1621,7 @@
       <c r="W19" s="8"/>
       <c r="X19" s="8"/>
     </row>
-    <row r="20" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A20" s="7">
         <v>2018104240</v>
       </c>
@@ -1667,7 +1665,7 @@
       <c r="W20" s="8"/>
       <c r="X20" s="8"/>
     </row>
-    <row r="21" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A21" s="9">
         <v>2024101764</v>
       </c>
@@ -1711,7 +1709,7 @@
       <c r="W21" s="8"/>
       <c r="X21" s="8"/>
     </row>
-    <row r="22" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A22" s="7">
         <v>2022102060</v>
       </c>
@@ -1755,7 +1753,7 @@
       <c r="W22" s="8"/>
       <c r="X22" s="8"/>
     </row>
-    <row r="23" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A23" s="9">
         <v>2024103490</v>
       </c>
@@ -1799,7 +1797,7 @@
       <c r="W23" s="8"/>
       <c r="X23" s="8"/>
     </row>
-    <row r="24" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A24" s="7">
         <v>2023100771</v>
       </c>
@@ -1813,31 +1811,31 @@
         <v>6.35</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F24" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G24" s="8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H24" s="8">
         <v>1</v>
       </c>
       <c r="I24" s="8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J24" s="8">
         <v>0</v>
       </c>
       <c r="K24" s="8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="L24" s="8">
         <v>0</v>
       </c>
       <c r="M24" s="8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="N24" s="8">
         <v>0</v>
@@ -1873,7 +1871,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="25" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A25" s="9">
         <v>2023100962</v>
       </c>
@@ -1917,7 +1915,7 @@
       <c r="W25" s="8"/>
       <c r="X25" s="8"/>
     </row>
-    <row r="26" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A26" s="7">
         <v>2021101361</v>
       </c>
@@ -1961,7 +1959,7 @@
       <c r="W26" s="8"/>
       <c r="X26" s="8"/>
     </row>
-    <row r="27" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A27" s="9">
         <v>2023201341</v>
       </c>
@@ -1975,31 +1973,31 @@
         <v>8.65</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F27" s="8">
         <v>0.6</v>
       </c>
       <c r="G27" s="8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H27" s="8">
         <v>1</v>
       </c>
       <c r="I27" s="8" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J27" s="8">
         <v>0.6</v>
       </c>
       <c r="K27" s="8" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L27" s="8">
         <v>0.5</v>
       </c>
       <c r="M27" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="N27" s="8">
         <v>1.2</v>
@@ -2035,7 +2033,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="28" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A28" s="7">
         <v>2023101463</v>
       </c>
@@ -2079,7 +2077,7 @@
       <c r="W28" s="8"/>
       <c r="X28" s="8"/>
     </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A29" s="9">
         <v>2022201037</v>
       </c>
@@ -2093,31 +2091,31 @@
         <v>9.25</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F29" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G29" s="8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H29" s="8">
         <v>1</v>
       </c>
       <c r="I29" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J29" s="8">
         <v>1.2</v>
       </c>
       <c r="K29" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L29" s="8">
         <v>1</v>
       </c>
       <c r="M29" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="N29" s="8">
         <v>1.2</v>
@@ -2153,7 +2151,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="30" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A30" s="7">
         <v>2021101896</v>
       </c>
@@ -2167,31 +2165,31 @@
         <v>10</v>
       </c>
       <c r="E30" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F30" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G30" s="8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H30" s="8">
         <v>1</v>
       </c>
       <c r="I30" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J30" s="8">
         <v>1.2</v>
       </c>
       <c r="K30" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L30" s="8">
         <v>1</v>
       </c>
       <c r="M30" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="N30" s="8">
         <v>1.2</v>
@@ -2227,7 +2225,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="31" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A31" s="9">
         <v>2022201042</v>
       </c>
@@ -2271,7 +2269,7 @@
       <c r="W31" s="8"/>
       <c r="X31" s="8"/>
     </row>
-    <row r="32" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A32" s="7">
         <v>2020102888</v>
       </c>
@@ -2285,31 +2283,31 @@
         <v>7.95</v>
       </c>
       <c r="E32" s="8" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F32" s="8">
         <v>0.2</v>
       </c>
       <c r="G32" s="8" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H32" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="I32" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J32" s="8">
         <v>1.2</v>
       </c>
       <c r="K32" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L32" s="8">
         <v>1</v>
       </c>
       <c r="M32" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="N32" s="8">
         <v>1.2</v>
@@ -2345,7 +2343,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A33" s="9">
         <v>2024101765</v>
       </c>
@@ -2359,31 +2357,31 @@
         <v>8.3000000000000007</v>
       </c>
       <c r="E33" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F33" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G33" s="8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H33" s="8">
         <v>1</v>
       </c>
       <c r="I33" s="8" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J33" s="8">
         <v>0.6</v>
       </c>
       <c r="K33" s="8" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L33" s="8">
         <v>0.5</v>
       </c>
       <c r="M33" s="8" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N33" s="8">
         <v>0.6</v>
@@ -2419,7 +2417,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="34" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A34" s="7">
         <v>2022100612</v>
       </c>
@@ -2463,7 +2461,7 @@
       <c r="W34" s="8"/>
       <c r="X34" s="8"/>
     </row>
-    <row r="35" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A35" s="9">
         <v>2023101467</v>
       </c>
@@ -2507,7 +2505,7 @@
       <c r="W35" s="8"/>
       <c r="X35" s="8"/>
     </row>
-    <row r="36" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A36" s="7">
         <v>2022100511</v>
       </c>
@@ -2551,7 +2549,7 @@
       <c r="W36" s="8"/>
       <c r="X36" s="8"/>
     </row>
-    <row r="37" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A37" s="9">
         <v>2023200147</v>
       </c>
@@ -2565,31 +2563,31 @@
         <v>10</v>
       </c>
       <c r="E37" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F37" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G37" s="8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H37" s="8">
         <v>1</v>
       </c>
       <c r="I37" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J37" s="8">
         <v>1.2</v>
       </c>
       <c r="K37" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L37" s="8">
         <v>1</v>
       </c>
       <c r="M37" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="N37" s="8">
         <v>1.2</v>
@@ -2625,7 +2623,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="38" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A38" s="7">
         <v>2023100776</v>
       </c>
@@ -2669,7 +2667,7 @@
       <c r="W38" s="8"/>
       <c r="X38" s="8"/>
     </row>
-    <row r="39" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A39" s="9">
         <v>2024101158</v>
       </c>
@@ -2713,7 +2711,7 @@
       <c r="W39" s="8"/>
       <c r="X39" s="8"/>
     </row>
-    <row r="40" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A40" s="7">
         <v>2024101773</v>
       </c>
@@ -2757,7 +2755,7 @@
       <c r="W40" s="8"/>
       <c r="X40" s="8"/>
     </row>
-    <row r="41" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A41" s="9">
         <v>2023100068</v>
       </c>
@@ -2801,7 +2799,7 @@
       <c r="W41" s="8"/>
       <c r="X41" s="8"/>
     </row>
-    <row r="42" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A42" s="7">
         <v>2023200790</v>
       </c>
@@ -2845,7 +2843,7 @@
       <c r="W42" s="8"/>
       <c r="X42" s="8"/>
     </row>
-    <row r="43" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A43" s="9">
         <v>2022200719</v>
       </c>
@@ -2859,31 +2857,31 @@
         <v>9.75</v>
       </c>
       <c r="E43" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F43" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G43" s="8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H43" s="8">
         <v>1</v>
       </c>
       <c r="I43" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J43" s="8">
         <v>1.2</v>
       </c>
       <c r="K43" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L43" s="8">
         <v>1</v>
       </c>
       <c r="M43" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="N43" s="8">
         <v>1.2</v>
@@ -2919,7 +2917,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="44" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A44" s="8">
         <v>2025201178</v>
       </c>
@@ -2933,31 +2931,31 @@
         <v>6.05</v>
       </c>
       <c r="E44" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F44" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G44" s="8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H44" s="8">
         <v>1</v>
       </c>
       <c r="I44" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J44" s="8">
         <v>1.2</v>
       </c>
       <c r="K44" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L44" s="8">
         <v>1</v>
       </c>
       <c r="M44" s="8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="N44" s="8">
         <v>0</v>
@@ -2993,7 +2991,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A45" s="9">
         <v>2024101775</v>
       </c>
@@ -3037,7 +3035,7 @@
       <c r="W45" s="8"/>
       <c r="X45" s="8"/>
     </row>
-    <row r="46" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A46" s="7">
         <v>2024103187</v>
       </c>
@@ -3081,7 +3079,7 @@
       <c r="W46" s="8"/>
       <c r="X46" s="8"/>
     </row>
-    <row r="47" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A47" s="9">
         <v>2023102386</v>
       </c>
@@ -3095,31 +3093,31 @@
         <v>9</v>
       </c>
       <c r="E47" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F47" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G47" s="8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H47" s="8">
         <v>1</v>
       </c>
       <c r="I47" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J47" s="8">
         <v>1.2</v>
       </c>
       <c r="K47" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L47" s="8">
         <v>1</v>
       </c>
       <c r="M47" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="N47" s="8">
         <v>1.2</v>
@@ -3155,7 +3153,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="48" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A48" s="7">
         <v>2020101654</v>
       </c>
@@ -3199,7 +3197,7 @@
       <c r="W48" s="8"/>
       <c r="X48" s="8"/>
     </row>
-    <row r="49" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A49" s="9">
         <v>2022201082</v>
       </c>
@@ -3213,31 +3211,31 @@
         <v>9.65</v>
       </c>
       <c r="E49" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F49" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G49" s="8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H49" s="8">
         <v>0.9</v>
       </c>
       <c r="I49" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J49" s="8">
         <v>1.2</v>
       </c>
       <c r="K49" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L49" s="8">
         <v>1</v>
       </c>
       <c r="M49" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="N49" s="8">
         <v>1.2</v>
@@ -3273,7 +3271,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="50" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A50" s="7">
         <v>2024101769</v>
       </c>
@@ -3317,7 +3315,7 @@
       <c r="W50" s="8"/>
       <c r="X50" s="8"/>
     </row>
-    <row r="51" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A51" s="9">
         <v>2024101154</v>
       </c>
@@ -3361,7 +3359,7 @@
       <c r="W51" s="8"/>
       <c r="X51" s="8"/>
     </row>
-    <row r="52" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A52" s="7">
         <v>2022102045</v>
       </c>
@@ -3375,31 +3373,31 @@
         <v>7.8000000000000007</v>
       </c>
       <c r="E52" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F52" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G52" s="8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H52" s="8">
         <v>1</v>
       </c>
       <c r="I52" s="8" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J52" s="8">
         <v>0.6</v>
       </c>
       <c r="K52" s="8" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L52" s="8">
         <v>0.5</v>
       </c>
       <c r="M52" s="8" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N52" s="8">
         <v>0.6</v>
@@ -3435,7 +3433,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="53" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A53" s="9">
         <v>2023101690</v>
       </c>
@@ -3479,7 +3477,7 @@
       <c r="W53" s="8"/>
       <c r="X53" s="8"/>
     </row>
-    <row r="54" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A54" s="7">
         <v>2023100954</v>
       </c>
@@ -3523,7 +3521,7 @@
       <c r="W54" s="8"/>
       <c r="X54" s="8"/>
     </row>
-    <row r="55" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A55" s="9">
         <v>2024202997</v>
       </c>
@@ -3537,31 +3535,31 @@
         <v>7.65</v>
       </c>
       <c r="E55" s="8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F55" s="8">
         <v>0</v>
       </c>
       <c r="G55" s="8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H55" s="8">
         <v>1</v>
       </c>
       <c r="I55" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J55" s="8">
         <v>1.2</v>
       </c>
       <c r="K55" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L55" s="8">
         <v>1</v>
       </c>
       <c r="M55" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="N55" s="8">
         <v>1.2</v>
@@ -3597,7 +3595,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A56" s="7">
         <v>2020101573</v>
       </c>
@@ -3641,7 +3639,7 @@
       <c r="W56" s="8"/>
       <c r="X56" s="8"/>
     </row>
-    <row r="57" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A57" s="9">
         <v>2024101785</v>
       </c>
@@ -3685,7 +3683,7 @@
       <c r="W57" s="8"/>
       <c r="X57" s="8"/>
     </row>
-    <row r="58" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A58" s="7">
         <v>2021201017</v>
       </c>
@@ -3729,7 +3727,7 @@
       <c r="W58" s="8"/>
       <c r="X58" s="8"/>
     </row>
-    <row r="59" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A59" s="9">
         <v>2023101691</v>
       </c>
@@ -3773,7 +3771,7 @@
       <c r="W59" s="8"/>
       <c r="X59" s="8"/>
     </row>
-    <row r="60" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A60" s="7">
         <v>2024101770</v>
       </c>
@@ -3817,7 +3815,7 @@
       <c r="W60" s="8"/>
       <c r="X60" s="8"/>
     </row>
-    <row r="61" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A61" s="9">
         <v>2022200727</v>
       </c>
@@ -3831,31 +3829,31 @@
         <v>9.5</v>
       </c>
       <c r="E61" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F61" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G61" s="8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H61" s="8">
         <v>1</v>
       </c>
       <c r="I61" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J61" s="8">
         <v>1.2</v>
       </c>
       <c r="K61" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L61" s="8">
         <v>1</v>
       </c>
       <c r="M61" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="N61" s="8">
         <v>1.2</v>
@@ -3891,7 +3889,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="62" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A62" s="7">
         <v>2023101729</v>
       </c>
@@ -3905,31 +3903,31 @@
         <v>6.05</v>
       </c>
       <c r="E62" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F62" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G62" s="8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H62" s="8">
         <v>0.9</v>
       </c>
       <c r="I62" s="8" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J62" s="8">
         <v>0.6</v>
       </c>
       <c r="K62" s="8" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L62" s="8">
         <v>0.5</v>
       </c>
       <c r="M62" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="N62" s="8">
         <v>1.2</v>
@@ -3965,7 +3963,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A63" s="9">
         <v>2023100965</v>
       </c>
@@ -3979,31 +3977,31 @@
         <v>6.6499999999999995</v>
       </c>
       <c r="E63" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F63" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G63" s="8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H63" s="8">
         <v>1</v>
       </c>
       <c r="I63" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J63" s="8">
         <v>1.2</v>
       </c>
       <c r="K63" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L63" s="8">
         <v>1</v>
       </c>
       <c r="M63" s="8" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N63" s="8">
         <v>0.6</v>
@@ -4039,7 +4037,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A64" s="7">
         <v>2024101155</v>
       </c>
@@ -4083,7 +4081,7 @@
       <c r="W64" s="8"/>
       <c r="X64" s="8"/>
     </row>
-    <row r="65" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A65" s="9">
         <v>2023200064</v>
       </c>

--- a/notas.xlsx
+++ b/notas.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11109"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/daniloas.com/projetos/FertilidadeSoloAlegreUFES/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuário\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D14B25CB-D763-3A48-90FE-1362A7D655E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76C81D95-47DC-404F-90DC-8C81499912D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="620" windowWidth="20740" windowHeight="11320" xr2:uid="{BB9E0E1E-73DF-4AB6-A949-07A69840CAF7}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11310" xr2:uid="{BB9E0E1E-73DF-4AB6-A949-07A69840CAF7}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -39,9 +39,17 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="24">
   <si>
     <t>Matrícula</t>
+  </si>
+  <si>
+    <t>Pontuação 
+dos exercícios extras</t>
+  </si>
+  <si>
+    <t>Pontuação total
+(Prova + Extra)</t>
   </si>
   <si>
     <t>Item a</t>
@@ -101,10 +109,10 @@
     <t>0/6</t>
   </si>
   <si>
-    <t>Pontuação dos exercícios extras</t>
+    <t>0/1</t>
   </si>
   <si>
-    <t>Pontuação total (Prova + Extra)</t>
+    <t>0/0</t>
   </si>
 </sst>
 </file>
@@ -565,91 +573,91 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCC50A17-1BAD-4261-9C73-1273FB998B6D}">
   <dimension ref="A1:X65"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.33203125" customWidth="1"/>
+    <col min="2" max="2" width="16.28515625" customWidth="1"/>
     <col min="3" max="3" width="17" customWidth="1"/>
-    <col min="4" max="4" width="26.5" customWidth="1"/>
+    <col min="4" max="4" width="26.5703125" customWidth="1"/>
     <col min="5" max="5" width="7" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="33" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="O1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="K1" s="3" t="s">
+      <c r="P1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="L1" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="M1" s="3" t="s">
+      <c r="Q1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="N1" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="O1" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="P1" s="5" t="s">
+      <c r="R1" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="S1" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="T1" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="U1" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="V1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="Q1" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="R1" s="5" t="s">
+      <c r="W1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="S1" s="5" t="s">
+      <c r="X1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="T1" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="U1" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="V1" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="W1" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="X1" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A2" s="7">
         <v>2023200939</v>
       </c>
@@ -663,31 +671,31 @@
         <v>9.1999999999999993</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F2" s="8">
         <v>0.4</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H2" s="8">
         <v>1</v>
       </c>
       <c r="I2" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J2" s="8">
         <v>1.2</v>
       </c>
       <c r="K2" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L2" s="8">
         <v>1</v>
       </c>
       <c r="M2" s="8" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="N2" s="8">
         <v>0.6</v>
@@ -723,51 +731,81 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A3" s="9">
         <v>2023100005</v>
       </c>
       <c r="B3" s="8">
         <v>0.81555555555555548</v>
       </c>
-      <c r="C3" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="D3" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="G3" s="8"/>
-      <c r="H3" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="I3" s="8"/>
-      <c r="J3" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="K3" s="8"/>
-      <c r="L3" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="M3" s="8"/>
-      <c r="N3" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="O3" s="8"/>
-      <c r="P3" s="8"/>
-      <c r="Q3" s="8"/>
-      <c r="R3" s="8"/>
-      <c r="S3" s="8"/>
-      <c r="T3" s="8"/>
-      <c r="U3" s="8"/>
-      <c r="V3" s="8"/>
-      <c r="W3" s="8"/>
-      <c r="X3" s="8"/>
-    </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="C3" s="8">
+        <v>9.5155555555555544</v>
+      </c>
+      <c r="D3" s="8">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H3" s="8">
+        <v>1</v>
+      </c>
+      <c r="I3" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J3" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="K3" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L3" s="8">
+        <v>1</v>
+      </c>
+      <c r="M3" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="N3" s="8">
+        <v>0.6</v>
+      </c>
+      <c r="O3" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="P3" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="Q3" s="8">
+        <v>0.25</v>
+      </c>
+      <c r="R3" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="S3" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="T3" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="U3" s="8">
+        <v>0.25</v>
+      </c>
+      <c r="V3" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="W3" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="X3" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A4" s="7">
         <v>2021101895</v>
       </c>
@@ -781,31 +819,31 @@
         <v>8.75</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F4" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H4" s="8">
         <v>1</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J4" s="8">
         <v>1.2</v>
       </c>
       <c r="K4" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L4" s="8">
         <v>1</v>
       </c>
       <c r="M4" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="N4" s="8">
         <v>1.2</v>
@@ -841,7 +879,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A5" s="9">
         <v>2024101156</v>
       </c>
@@ -855,31 +893,31 @@
         <v>9</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F5" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H5" s="8">
         <v>1</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J5" s="8">
         <v>1.2</v>
       </c>
       <c r="K5" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L5" s="8">
         <v>1</v>
       </c>
       <c r="M5" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="N5" s="8">
         <v>1.2</v>
@@ -915,7 +953,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A6" s="7">
         <v>2023200783</v>
       </c>
@@ -959,7 +997,7 @@
       <c r="W6" s="8"/>
       <c r="X6" s="8"/>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A7" s="9">
         <v>2022200360</v>
       </c>
@@ -973,31 +1011,31 @@
         <v>9.3999999999999986</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F7" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H7" s="8">
         <v>1</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J7" s="8">
         <v>1.2</v>
       </c>
       <c r="K7" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L7" s="8">
         <v>1</v>
       </c>
       <c r="M7" s="8" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="N7" s="8">
         <v>0.6</v>
@@ -1033,51 +1071,81 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A8" s="7">
         <v>2024101774</v>
       </c>
       <c r="B8" s="8">
         <v>0.85692810457516333</v>
       </c>
-      <c r="C8" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="D8" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="G8" s="8"/>
-      <c r="H8" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="I8" s="8"/>
-      <c r="J8" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="K8" s="8"/>
-      <c r="L8" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="M8" s="8"/>
-      <c r="N8" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="O8" s="8"/>
-      <c r="P8" s="8"/>
-      <c r="Q8" s="8"/>
-      <c r="R8" s="8"/>
-      <c r="S8" s="8"/>
-      <c r="T8" s="8"/>
-      <c r="U8" s="8"/>
-      <c r="V8" s="8"/>
-      <c r="W8" s="8"/>
-      <c r="X8" s="8"/>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="C8" s="8">
+        <v>10.606928104575164</v>
+      </c>
+      <c r="D8" s="8">
+        <v>9.75</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F8" s="8">
+        <v>0.60000000000000009</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H8" s="8">
+        <v>1</v>
+      </c>
+      <c r="I8" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J8" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="K8" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L8" s="8">
+        <v>1</v>
+      </c>
+      <c r="M8" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="N8" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="O8" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="P8" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="Q8" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="R8" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="S8" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="T8" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="U8" s="8">
+        <v>0.25</v>
+      </c>
+      <c r="V8" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="W8" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="X8" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A9" s="9">
         <v>2024203414</v>
       </c>
@@ -1091,31 +1159,31 @@
         <v>8.75</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F9" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H9" s="8">
         <v>1</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J9" s="8">
         <v>1.2</v>
       </c>
       <c r="K9" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L9" s="8">
         <v>1</v>
       </c>
       <c r="M9" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="N9" s="8">
         <v>1.2</v>
@@ -1151,7 +1219,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A10" s="7">
         <v>2023101046</v>
       </c>
@@ -1195,7 +1263,7 @@
       <c r="W10" s="8"/>
       <c r="X10" s="8"/>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A11" s="9">
         <v>2019109848</v>
       </c>
@@ -1239,7 +1307,7 @@
       <c r="W11" s="8"/>
       <c r="X11" s="8"/>
     </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A12" s="7">
         <v>2023102012</v>
       </c>
@@ -1253,31 +1321,31 @@
         <v>4.45</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F12" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H12" s="8">
         <v>1</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J12" s="8">
         <v>0.6</v>
       </c>
       <c r="K12" s="8" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="L12" s="8">
         <v>0</v>
       </c>
       <c r="M12" s="8" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="N12" s="8">
         <v>0</v>
@@ -1313,7 +1381,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A13" s="9">
         <v>2024101768</v>
       </c>
@@ -1357,51 +1425,81 @@
       <c r="W13" s="8"/>
       <c r="X13" s="8"/>
     </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A14" s="7">
         <v>2018104222</v>
       </c>
       <c r="B14" s="8">
         <v>0.51771241830065362</v>
       </c>
-      <c r="C14" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="D14" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="E14" s="8"/>
-      <c r="F14" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="G14" s="8"/>
-      <c r="H14" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="I14" s="8"/>
-      <c r="J14" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="K14" s="8"/>
-      <c r="L14" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="M14" s="8"/>
-      <c r="N14" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="O14" s="8"/>
-      <c r="P14" s="8"/>
-      <c r="Q14" s="8"/>
-      <c r="R14" s="8"/>
-      <c r="S14" s="8"/>
-      <c r="T14" s="8"/>
-      <c r="U14" s="8"/>
-      <c r="V14" s="8"/>
-      <c r="W14" s="8"/>
-      <c r="X14" s="8"/>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="C14" s="8">
+        <v>4.1177124183006537</v>
+      </c>
+      <c r="D14" s="8">
+        <v>3.6</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F14" s="8">
+        <v>0.60000000000000009</v>
+      </c>
+      <c r="G14" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H14" s="8">
+        <v>1</v>
+      </c>
+      <c r="I14" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="J14" s="8">
+        <v>0</v>
+      </c>
+      <c r="K14" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="L14" s="8">
+        <v>0</v>
+      </c>
+      <c r="M14" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="N14" s="8">
+        <v>0</v>
+      </c>
+      <c r="O14" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="P14" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="Q14" s="8">
+        <v>0.25</v>
+      </c>
+      <c r="R14" s="8">
+        <v>0.25</v>
+      </c>
+      <c r="S14" s="8">
+        <v>0.25</v>
+      </c>
+      <c r="T14" s="8">
+        <v>0</v>
+      </c>
+      <c r="U14" s="8">
+        <v>0.25</v>
+      </c>
+      <c r="V14" s="8">
+        <v>0</v>
+      </c>
+      <c r="W14" s="8">
+        <v>0</v>
+      </c>
+      <c r="X14" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A15" s="9">
         <v>2017102706</v>
       </c>
@@ -1445,95 +1543,155 @@
       <c r="W15" s="8"/>
       <c r="X15" s="8"/>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A16" s="7">
         <v>2024103491</v>
       </c>
       <c r="B16" s="8">
         <v>0.93174291938997822</v>
       </c>
-      <c r="C16" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="D16" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="E16" s="8"/>
-      <c r="F16" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="G16" s="8"/>
-      <c r="H16" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="I16" s="8"/>
-      <c r="J16" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="K16" s="8"/>
-      <c r="L16" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="M16" s="8"/>
-      <c r="N16" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="O16" s="8"/>
-      <c r="P16" s="8"/>
-      <c r="Q16" s="8"/>
-      <c r="R16" s="8"/>
-      <c r="S16" s="8"/>
-      <c r="T16" s="8"/>
-      <c r="U16" s="8"/>
-      <c r="V16" s="8"/>
-      <c r="W16" s="8"/>
-      <c r="X16" s="8"/>
-    </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="C16" s="8">
+        <v>10.431742919389979</v>
+      </c>
+      <c r="D16" s="8">
+        <v>9.5</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F16" s="8">
+        <v>0.60000000000000009</v>
+      </c>
+      <c r="G16" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H16" s="8">
+        <v>1</v>
+      </c>
+      <c r="I16" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J16" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="K16" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="L16" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M16" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="N16" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="O16" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="P16" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="Q16" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="R16" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="S16" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="T16" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="U16" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="V16" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="W16" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="X16" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A17" s="9">
         <v>2023100158</v>
       </c>
       <c r="B17" s="8">
         <v>0.22222222222222221</v>
       </c>
-      <c r="C17" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="D17" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="E17" s="8"/>
-      <c r="F17" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="G17" s="8"/>
-      <c r="H17" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="I17" s="8"/>
-      <c r="J17" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="K17" s="8"/>
-      <c r="L17" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="M17" s="8"/>
-      <c r="N17" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="O17" s="8"/>
-      <c r="P17" s="8"/>
-      <c r="Q17" s="8"/>
-      <c r="R17" s="8"/>
-      <c r="S17" s="8"/>
-      <c r="T17" s="8"/>
-      <c r="U17" s="8"/>
-      <c r="V17" s="8"/>
-      <c r="W17" s="8"/>
-      <c r="X17" s="8"/>
-    </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="C17" s="8">
+        <v>8.6222222222222218</v>
+      </c>
+      <c r="D17" s="8">
+        <v>8.3999999999999986</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F17" s="8">
+        <v>0.60000000000000009</v>
+      </c>
+      <c r="G17" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H17" s="8">
+        <v>1</v>
+      </c>
+      <c r="I17" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J17" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="K17" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L17" s="8">
+        <v>1</v>
+      </c>
+      <c r="M17" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="N17" s="8">
+        <v>0.6</v>
+      </c>
+      <c r="O17" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="P17" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="Q17" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="R17" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="S17" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="T17" s="8">
+        <v>0.25</v>
+      </c>
+      <c r="U17" s="8">
+        <v>0.25</v>
+      </c>
+      <c r="V17" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="W17" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="X17" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A18" s="7">
         <v>2024101776</v>
       </c>
@@ -1577,7 +1735,7 @@
       <c r="W18" s="8"/>
       <c r="X18" s="8"/>
     </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A19" s="9">
         <v>2020102895</v>
       </c>
@@ -1621,95 +1779,155 @@
       <c r="W19" s="8"/>
       <c r="X19" s="8"/>
     </row>
-    <row r="20" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A20" s="7">
         <v>2018104240</v>
       </c>
       <c r="B20" s="8">
         <v>0.33333333333333331</v>
       </c>
-      <c r="C20" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="D20" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="E20" s="8"/>
-      <c r="F20" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="G20" s="8"/>
-      <c r="H20" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="I20" s="8"/>
-      <c r="J20" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="K20" s="8"/>
-      <c r="L20" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="M20" s="8"/>
-      <c r="N20" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="O20" s="8"/>
-      <c r="P20" s="8"/>
-      <c r="Q20" s="8"/>
-      <c r="R20" s="8"/>
-      <c r="S20" s="8"/>
-      <c r="T20" s="8"/>
-      <c r="U20" s="8"/>
-      <c r="V20" s="8"/>
-      <c r="W20" s="8"/>
-      <c r="X20" s="8"/>
-    </row>
-    <row r="21" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="C20" s="8">
+        <v>6.0333333333333332</v>
+      </c>
+      <c r="D20" s="8">
+        <v>5.7</v>
+      </c>
+      <c r="E20" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="F20" s="8">
+        <v>0</v>
+      </c>
+      <c r="G20" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H20" s="8">
+        <v>1</v>
+      </c>
+      <c r="I20" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J20" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="K20" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L20" s="8">
+        <v>1</v>
+      </c>
+      <c r="M20" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="N20" s="8">
+        <v>0</v>
+      </c>
+      <c r="O20" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="P20" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="8">
+        <v>0</v>
+      </c>
+      <c r="R20" s="8">
+        <v>0.25</v>
+      </c>
+      <c r="S20" s="8">
+        <v>0.25</v>
+      </c>
+      <c r="T20" s="8">
+        <v>0.25</v>
+      </c>
+      <c r="U20" s="8">
+        <v>0.25</v>
+      </c>
+      <c r="V20" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="W20" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="X20" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A21" s="9">
         <v>2024101764</v>
       </c>
       <c r="B21" s="8">
         <v>0.91901960784313719</v>
       </c>
-      <c r="C21" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="D21" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="E21" s="8"/>
-      <c r="F21" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="G21" s="8"/>
-      <c r="H21" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="I21" s="8"/>
-      <c r="J21" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="K21" s="8"/>
-      <c r="L21" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="M21" s="8"/>
-      <c r="N21" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="O21" s="8"/>
-      <c r="P21" s="8"/>
-      <c r="Q21" s="8"/>
-      <c r="R21" s="8"/>
-      <c r="S21" s="8"/>
-      <c r="T21" s="8"/>
-      <c r="U21" s="8"/>
-      <c r="V21" s="8"/>
-      <c r="W21" s="8"/>
-      <c r="X21" s="8"/>
-    </row>
-    <row r="22" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="C21" s="8">
+        <v>9.8190196078431367</v>
+      </c>
+      <c r="D21" s="8">
+        <v>8.8999999999999986</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F21" s="8">
+        <v>0.60000000000000009</v>
+      </c>
+      <c r="G21" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H21" s="8">
+        <v>1</v>
+      </c>
+      <c r="I21" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J21" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="K21" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L21" s="8">
+        <v>1</v>
+      </c>
+      <c r="M21" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="N21" s="8">
+        <v>0.6</v>
+      </c>
+      <c r="O21" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="P21" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="Q21" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="R21" s="8">
+        <v>0.25</v>
+      </c>
+      <c r="S21" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="T21" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="U21" s="8">
+        <v>0.25</v>
+      </c>
+      <c r="V21" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="W21" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="X21" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A22" s="7">
         <v>2022102060</v>
       </c>
@@ -1753,51 +1971,81 @@
       <c r="W22" s="8"/>
       <c r="X22" s="8"/>
     </row>
-    <row r="23" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A23" s="9">
         <v>2024103490</v>
       </c>
       <c r="B23" s="8">
         <v>0.94388888888888889</v>
       </c>
-      <c r="C23" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="D23" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="E23" s="8"/>
-      <c r="F23" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="G23" s="8"/>
-      <c r="H23" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="I23" s="8"/>
-      <c r="J23" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="K23" s="8"/>
-      <c r="L23" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="M23" s="8"/>
-      <c r="N23" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="O23" s="8"/>
-      <c r="P23" s="8"/>
-      <c r="Q23" s="8"/>
-      <c r="R23" s="8"/>
-      <c r="S23" s="8"/>
-      <c r="T23" s="8"/>
-      <c r="U23" s="8"/>
-      <c r="V23" s="8"/>
-      <c r="W23" s="8"/>
-      <c r="X23" s="8"/>
-    </row>
-    <row r="24" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="C23" s="8">
+        <v>10.093888888888888</v>
+      </c>
+      <c r="D23" s="8">
+        <v>9.1499999999999986</v>
+      </c>
+      <c r="E23" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F23" s="8">
+        <v>0.60000000000000009</v>
+      </c>
+      <c r="G23" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H23" s="8">
+        <v>1</v>
+      </c>
+      <c r="I23" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J23" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="K23" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L23" s="8">
+        <v>1</v>
+      </c>
+      <c r="M23" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="N23" s="8">
+        <v>0.6</v>
+      </c>
+      <c r="O23" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="P23" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="Q23" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="R23" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="S23" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="T23" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="U23" s="8">
+        <v>0.25</v>
+      </c>
+      <c r="V23" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="W23" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="X23" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A24" s="7">
         <v>2023100771</v>
       </c>
@@ -1811,31 +2059,31 @@
         <v>6.35</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F24" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G24" s="8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H24" s="8">
         <v>1</v>
       </c>
       <c r="I24" s="8" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J24" s="8">
         <v>0</v>
       </c>
       <c r="K24" s="8" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="L24" s="8">
         <v>0</v>
       </c>
       <c r="M24" s="8" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="N24" s="8">
         <v>0</v>
@@ -1871,7 +2119,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="25" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A25" s="9">
         <v>2023100962</v>
       </c>
@@ -1915,51 +2163,81 @@
       <c r="W25" s="8"/>
       <c r="X25" s="8"/>
     </row>
-    <row r="26" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A26" s="7">
         <v>2021101361</v>
       </c>
       <c r="B26" s="8">
         <v>0.32407407407407407</v>
       </c>
-      <c r="C26" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="D26" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="E26" s="8"/>
-      <c r="F26" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="G26" s="8"/>
-      <c r="H26" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="I26" s="8"/>
-      <c r="J26" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="K26" s="8"/>
-      <c r="L26" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="M26" s="8"/>
-      <c r="N26" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="O26" s="8"/>
-      <c r="P26" s="8"/>
-      <c r="Q26" s="8"/>
-      <c r="R26" s="8"/>
-      <c r="S26" s="8"/>
-      <c r="T26" s="8"/>
-      <c r="U26" s="8"/>
-      <c r="V26" s="8"/>
-      <c r="W26" s="8"/>
-      <c r="X26" s="8"/>
-    </row>
-    <row r="27" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="C26" s="8">
+        <v>7.6240740740740742</v>
+      </c>
+      <c r="D26" s="8">
+        <v>7.3</v>
+      </c>
+      <c r="E26" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F26" s="8">
+        <v>0.60000000000000009</v>
+      </c>
+      <c r="G26" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H26" s="8">
+        <v>1</v>
+      </c>
+      <c r="I26" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J26" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="K26" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L26" s="8">
+        <v>1</v>
+      </c>
+      <c r="M26" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="N26" s="8">
+        <v>0</v>
+      </c>
+      <c r="O26" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="P26" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="Q26" s="8">
+        <v>0.25</v>
+      </c>
+      <c r="R26" s="8">
+        <v>0</v>
+      </c>
+      <c r="S26" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="T26" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="U26" s="8">
+        <v>0.25</v>
+      </c>
+      <c r="V26" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="W26" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="X26" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A27" s="9">
         <v>2023201341</v>
       </c>
@@ -1973,31 +2251,31 @@
         <v>8.65</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F27" s="8">
-        <v>0.6</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="G27" s="8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H27" s="8">
         <v>1</v>
       </c>
       <c r="I27" s="8" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J27" s="8">
         <v>0.6</v>
       </c>
       <c r="K27" s="8" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="L27" s="8">
         <v>0.5</v>
       </c>
       <c r="M27" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="N27" s="8">
         <v>1.2</v>
@@ -2033,51 +2311,81 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="28" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A28" s="7">
         <v>2023101463</v>
       </c>
       <c r="B28" s="8">
         <v>0.33333333333333331</v>
       </c>
-      <c r="C28" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="D28" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="E28" s="8"/>
-      <c r="F28" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="G28" s="8"/>
-      <c r="H28" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="I28" s="8"/>
-      <c r="J28" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="K28" s="8"/>
-      <c r="L28" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="M28" s="8"/>
-      <c r="N28" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="O28" s="8"/>
-      <c r="P28" s="8"/>
-      <c r="Q28" s="8"/>
-      <c r="R28" s="8"/>
-      <c r="S28" s="8"/>
-      <c r="T28" s="8"/>
-      <c r="U28" s="8"/>
-      <c r="V28" s="8"/>
-      <c r="W28" s="8"/>
-      <c r="X28" s="8"/>
-    </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="C28" s="8">
+        <v>6.8833333333333329</v>
+      </c>
+      <c r="D28" s="8">
+        <v>6.5500000000000007</v>
+      </c>
+      <c r="E28" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F28" s="8">
+        <v>0.60000000000000009</v>
+      </c>
+      <c r="G28" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H28" s="8">
+        <v>1</v>
+      </c>
+      <c r="I28" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="J28" s="8">
+        <v>0.6</v>
+      </c>
+      <c r="K28" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="L28" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M28" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="N28" s="8">
+        <v>0.6</v>
+      </c>
+      <c r="O28" s="8">
+        <v>0</v>
+      </c>
+      <c r="P28" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="Q28" s="8">
+        <v>0.25</v>
+      </c>
+      <c r="R28" s="8">
+        <v>0.25</v>
+      </c>
+      <c r="S28" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="T28" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="U28" s="8">
+        <v>0.25</v>
+      </c>
+      <c r="V28" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="W28" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="X28" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A29" s="9">
         <v>2022201037</v>
       </c>
@@ -2091,31 +2399,31 @@
         <v>9.25</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F29" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G29" s="8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H29" s="8">
         <v>1</v>
       </c>
       <c r="I29" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J29" s="8">
         <v>1.2</v>
       </c>
       <c r="K29" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L29" s="8">
         <v>1</v>
       </c>
       <c r="M29" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="N29" s="8">
         <v>1.2</v>
@@ -2151,7 +2459,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="30" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A30" s="7">
         <v>2021101896</v>
       </c>
@@ -2165,31 +2473,31 @@
         <v>10</v>
       </c>
       <c r="E30" s="8" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F30" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G30" s="8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H30" s="8">
         <v>1</v>
       </c>
       <c r="I30" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J30" s="8">
         <v>1.2</v>
       </c>
       <c r="K30" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L30" s="8">
         <v>1</v>
       </c>
       <c r="M30" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="N30" s="8">
         <v>1.2</v>
@@ -2225,7 +2533,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="31" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A31" s="9">
         <v>2022201042</v>
       </c>
@@ -2269,7 +2577,7 @@
       <c r="W31" s="8"/>
       <c r="X31" s="8"/>
     </row>
-    <row r="32" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A32" s="7">
         <v>2020102888</v>
       </c>
@@ -2283,31 +2591,31 @@
         <v>7.95</v>
       </c>
       <c r="E32" s="8" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F32" s="8">
         <v>0.2</v>
       </c>
       <c r="G32" s="8" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H32" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="I32" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J32" s="8">
         <v>1.2</v>
       </c>
       <c r="K32" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L32" s="8">
         <v>1</v>
       </c>
       <c r="M32" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="N32" s="8">
         <v>1.2</v>
@@ -2343,7 +2651,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A33" s="9">
         <v>2024101765</v>
       </c>
@@ -2357,31 +2665,31 @@
         <v>8.3000000000000007</v>
       </c>
       <c r="E33" s="8" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F33" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G33" s="8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H33" s="8">
         <v>1</v>
       </c>
       <c r="I33" s="8" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J33" s="8">
         <v>0.6</v>
       </c>
       <c r="K33" s="8" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="L33" s="8">
         <v>0.5</v>
       </c>
       <c r="M33" s="8" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="N33" s="8">
         <v>0.6</v>
@@ -2417,7 +2725,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="34" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A34" s="7">
         <v>2022100612</v>
       </c>
@@ -2461,7 +2769,7 @@
       <c r="W34" s="8"/>
       <c r="X34" s="8"/>
     </row>
-    <row r="35" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A35" s="9">
         <v>2023101467</v>
       </c>
@@ -2505,51 +2813,81 @@
       <c r="W35" s="8"/>
       <c r="X35" s="8"/>
     </row>
-    <row r="36" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A36" s="7">
         <v>2022100511</v>
       </c>
       <c r="B36" s="8">
         <v>0.3202614379084967</v>
       </c>
-      <c r="C36" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="D36" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="E36" s="8"/>
-      <c r="F36" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="G36" s="8"/>
-      <c r="H36" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="I36" s="8"/>
-      <c r="J36" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="K36" s="8"/>
-      <c r="L36" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="M36" s="8"/>
-      <c r="N36" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="O36" s="8"/>
-      <c r="P36" s="8"/>
-      <c r="Q36" s="8"/>
-      <c r="R36" s="8"/>
-      <c r="S36" s="8"/>
-      <c r="T36" s="8"/>
-      <c r="U36" s="8"/>
-      <c r="V36" s="8"/>
-      <c r="W36" s="8"/>
-      <c r="X36" s="8"/>
-    </row>
-    <row r="37" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="C36" s="8">
+        <v>6.670261437908497</v>
+      </c>
+      <c r="D36" s="8">
+        <v>6.35</v>
+      </c>
+      <c r="E36" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F36" s="8">
+        <v>0.60000000000000009</v>
+      </c>
+      <c r="G36" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H36" s="8">
+        <v>1</v>
+      </c>
+      <c r="I36" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="J36" s="8">
+        <v>0</v>
+      </c>
+      <c r="K36" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="L36" s="8">
+        <v>0</v>
+      </c>
+      <c r="M36" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="N36" s="8">
+        <v>0</v>
+      </c>
+      <c r="O36" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="P36" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="Q36" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="R36" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="S36" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="T36" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="U36" s="8">
+        <v>0.25</v>
+      </c>
+      <c r="V36" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="W36" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="X36" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A37" s="9">
         <v>2023200147</v>
       </c>
@@ -2563,31 +2901,31 @@
         <v>10</v>
       </c>
       <c r="E37" s="8" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F37" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G37" s="8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H37" s="8">
         <v>1</v>
       </c>
       <c r="I37" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J37" s="8">
         <v>1.2</v>
       </c>
       <c r="K37" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L37" s="8">
         <v>1</v>
       </c>
       <c r="M37" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="N37" s="8">
         <v>1.2</v>
@@ -2623,139 +2961,229 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="38" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A38" s="7">
         <v>2023100776</v>
       </c>
       <c r="B38" s="8">
         <v>0.78388888888888875</v>
       </c>
-      <c r="C38" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="D38" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="E38" s="8"/>
-      <c r="F38" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="G38" s="8"/>
-      <c r="H38" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="I38" s="8"/>
-      <c r="J38" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="K38" s="8"/>
-      <c r="L38" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="M38" s="8"/>
-      <c r="N38" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="O38" s="8"/>
-      <c r="P38" s="8"/>
-      <c r="Q38" s="8"/>
-      <c r="R38" s="8"/>
-      <c r="S38" s="8"/>
-      <c r="T38" s="8"/>
-      <c r="U38" s="8"/>
-      <c r="V38" s="8"/>
-      <c r="W38" s="8"/>
-      <c r="X38" s="8"/>
-    </row>
-    <row r="39" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="C38" s="8">
+        <v>10.283888888888889</v>
+      </c>
+      <c r="D38" s="8">
+        <v>9.5</v>
+      </c>
+      <c r="E38" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F38" s="8">
+        <v>0.60000000000000009</v>
+      </c>
+      <c r="G38" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H38" s="8">
+        <v>1</v>
+      </c>
+      <c r="I38" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J38" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="K38" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L38" s="8">
+        <v>1</v>
+      </c>
+      <c r="M38" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="N38" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="O38" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="P38" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="Q38" s="8">
+        <v>0.25</v>
+      </c>
+      <c r="R38" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="S38" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="T38" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="U38" s="8">
+        <v>0.25</v>
+      </c>
+      <c r="V38" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="W38" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="X38" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="39" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A39" s="9">
         <v>2024101158</v>
       </c>
       <c r="B39" s="8">
         <v>0.96333333333333349</v>
       </c>
-      <c r="C39" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="D39" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="E39" s="8"/>
-      <c r="F39" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="G39" s="8"/>
-      <c r="H39" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="I39" s="8"/>
-      <c r="J39" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="K39" s="8"/>
-      <c r="L39" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="M39" s="8"/>
-      <c r="N39" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="O39" s="8"/>
-      <c r="P39" s="8"/>
-      <c r="Q39" s="8"/>
-      <c r="R39" s="8"/>
-      <c r="S39" s="8"/>
-      <c r="T39" s="8"/>
-      <c r="U39" s="8"/>
-      <c r="V39" s="8"/>
-      <c r="W39" s="8"/>
-      <c r="X39" s="8"/>
-    </row>
-    <row r="40" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="C39" s="8">
+        <v>10.963333333333335</v>
+      </c>
+      <c r="D39" s="8">
+        <v>10</v>
+      </c>
+      <c r="E39" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F39" s="8">
+        <v>0.60000000000000009</v>
+      </c>
+      <c r="G39" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H39" s="8">
+        <v>1</v>
+      </c>
+      <c r="I39" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J39" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="K39" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L39" s="8">
+        <v>1</v>
+      </c>
+      <c r="M39" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="N39" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="O39" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="P39" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="Q39" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="R39" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="S39" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="T39" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="U39" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="V39" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="W39" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="X39" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="40" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A40" s="7">
         <v>2024101773</v>
       </c>
       <c r="B40" s="8">
         <v>0.79666666666666663</v>
       </c>
-      <c r="C40" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="D40" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="E40" s="8"/>
-      <c r="F40" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="G40" s="8"/>
-      <c r="H40" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="I40" s="8"/>
-      <c r="J40" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="K40" s="8"/>
-      <c r="L40" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="M40" s="8"/>
-      <c r="N40" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="O40" s="8"/>
-      <c r="P40" s="8"/>
-      <c r="Q40" s="8"/>
-      <c r="R40" s="8"/>
-      <c r="S40" s="8"/>
-      <c r="T40" s="8"/>
-      <c r="U40" s="8"/>
-      <c r="V40" s="8"/>
-      <c r="W40" s="8"/>
-      <c r="X40" s="8"/>
-    </row>
-    <row r="41" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="C40" s="8">
+        <v>10.546666666666667</v>
+      </c>
+      <c r="D40" s="8">
+        <v>9.75</v>
+      </c>
+      <c r="E40" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F40" s="8">
+        <v>0.60000000000000009</v>
+      </c>
+      <c r="G40" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H40" s="8">
+        <v>1</v>
+      </c>
+      <c r="I40" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J40" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="K40" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L40" s="8">
+        <v>1</v>
+      </c>
+      <c r="M40" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="N40" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="O40" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="P40" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="Q40" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="R40" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="S40" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="T40" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="U40" s="8">
+        <v>0.25</v>
+      </c>
+      <c r="V40" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="W40" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="X40" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="41" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A41" s="9">
         <v>2023100068</v>
       </c>
@@ -2799,7 +3227,7 @@
       <c r="W41" s="8"/>
       <c r="X41" s="8"/>
     </row>
-    <row r="42" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A42" s="7">
         <v>2023200790</v>
       </c>
@@ -2843,7 +3271,7 @@
       <c r="W42" s="8"/>
       <c r="X42" s="8"/>
     </row>
-    <row r="43" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A43" s="9">
         <v>2022200719</v>
       </c>
@@ -2857,31 +3285,31 @@
         <v>9.75</v>
       </c>
       <c r="E43" s="8" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F43" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G43" s="8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H43" s="8">
         <v>1</v>
       </c>
       <c r="I43" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J43" s="8">
         <v>1.2</v>
       </c>
       <c r="K43" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L43" s="8">
         <v>1</v>
       </c>
       <c r="M43" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="N43" s="8">
         <v>1.2</v>
@@ -2917,7 +3345,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="44" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A44" s="8">
         <v>2025201178</v>
       </c>
@@ -2931,31 +3359,31 @@
         <v>6.05</v>
       </c>
       <c r="E44" s="8" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F44" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G44" s="8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H44" s="8">
         <v>1</v>
       </c>
       <c r="I44" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J44" s="8">
         <v>1.2</v>
       </c>
       <c r="K44" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L44" s="8">
         <v>1</v>
       </c>
       <c r="M44" s="8" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="N44" s="8">
         <v>0</v>
@@ -2991,95 +3419,155 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A45" s="9">
         <v>2024101775</v>
       </c>
       <c r="B45" s="8">
         <v>0.80137254901960775</v>
       </c>
-      <c r="C45" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="D45" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="E45" s="8"/>
-      <c r="F45" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="G45" s="8"/>
-      <c r="H45" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="I45" s="8"/>
-      <c r="J45" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="K45" s="8"/>
-      <c r="L45" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="M45" s="8"/>
-      <c r="N45" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="O45" s="8"/>
-      <c r="P45" s="8"/>
-      <c r="Q45" s="8"/>
-      <c r="R45" s="8"/>
-      <c r="S45" s="8"/>
-      <c r="T45" s="8"/>
-      <c r="U45" s="8"/>
-      <c r="V45" s="8"/>
-      <c r="W45" s="8"/>
-      <c r="X45" s="8"/>
-    </row>
-    <row r="46" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="C45" s="8">
+        <v>9.9513725490196077</v>
+      </c>
+      <c r="D45" s="8">
+        <v>9.1499999999999986</v>
+      </c>
+      <c r="E45" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F45" s="8">
+        <v>0.60000000000000009</v>
+      </c>
+      <c r="G45" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H45" s="8">
+        <v>1</v>
+      </c>
+      <c r="I45" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J45" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="K45" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L45" s="8">
+        <v>1</v>
+      </c>
+      <c r="M45" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="N45" s="8">
+        <v>0.6</v>
+      </c>
+      <c r="O45" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="P45" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="Q45" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="R45" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="S45" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="T45" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="U45" s="8">
+        <v>0.25</v>
+      </c>
+      <c r="V45" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="W45" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="X45" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A46" s="7">
         <v>2024103187</v>
       </c>
       <c r="B46" s="8">
         <v>0.59222222222222221</v>
       </c>
-      <c r="C46" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="D46" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="E46" s="8"/>
-      <c r="F46" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="G46" s="8"/>
-      <c r="H46" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="I46" s="8"/>
-      <c r="J46" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="K46" s="8"/>
-      <c r="L46" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="M46" s="8"/>
-      <c r="N46" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="O46" s="8"/>
-      <c r="P46" s="8"/>
-      <c r="Q46" s="8"/>
-      <c r="R46" s="8"/>
-      <c r="S46" s="8"/>
-      <c r="T46" s="8"/>
-      <c r="U46" s="8"/>
-      <c r="V46" s="8"/>
-      <c r="W46" s="8"/>
-      <c r="X46" s="8"/>
-    </row>
-    <row r="47" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="C46" s="8">
+        <v>8.492222222222221</v>
+      </c>
+      <c r="D46" s="8">
+        <v>7.9</v>
+      </c>
+      <c r="E46" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F46" s="8">
+        <v>0.60000000000000009</v>
+      </c>
+      <c r="G46" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H46" s="8">
+        <v>1</v>
+      </c>
+      <c r="I46" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="J46" s="8">
+        <v>0.6</v>
+      </c>
+      <c r="K46" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="L46" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M46" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="N46" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="O46" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="P46" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="Q46" s="8">
+        <v>0.25</v>
+      </c>
+      <c r="R46" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="S46" s="8">
+        <v>0.25</v>
+      </c>
+      <c r="T46" s="8">
+        <v>0.25</v>
+      </c>
+      <c r="U46" s="8">
+        <v>0.25</v>
+      </c>
+      <c r="V46" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="W46" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="X46" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="47" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A47" s="9">
         <v>2023102386</v>
       </c>
@@ -3093,31 +3581,31 @@
         <v>9</v>
       </c>
       <c r="E47" s="8" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F47" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G47" s="8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H47" s="8">
         <v>1</v>
       </c>
       <c r="I47" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J47" s="8">
         <v>1.2</v>
       </c>
       <c r="K47" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L47" s="8">
         <v>1</v>
       </c>
       <c r="M47" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="N47" s="8">
         <v>1.2</v>
@@ -3153,7 +3641,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="48" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A48" s="7">
         <v>2020101654</v>
       </c>
@@ -3197,7 +3685,7 @@
       <c r="W48" s="8"/>
       <c r="X48" s="8"/>
     </row>
-    <row r="49" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A49" s="9">
         <v>2022201082</v>
       </c>
@@ -3211,31 +3699,31 @@
         <v>9.65</v>
       </c>
       <c r="E49" s="8" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F49" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G49" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H49" s="8">
         <v>0.9</v>
       </c>
       <c r="I49" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J49" s="8">
         <v>1.2</v>
       </c>
       <c r="K49" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L49" s="8">
         <v>1</v>
       </c>
       <c r="M49" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="N49" s="8">
         <v>1.2</v>
@@ -3271,95 +3759,155 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="50" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A50" s="7">
         <v>2024101769</v>
       </c>
       <c r="B50" s="8">
         <v>0.92555555555555569</v>
       </c>
-      <c r="C50" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="D50" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="E50" s="8"/>
-      <c r="F50" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="G50" s="8"/>
-      <c r="H50" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="I50" s="8"/>
-      <c r="J50" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="K50" s="8"/>
-      <c r="L50" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="M50" s="8"/>
-      <c r="N50" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="O50" s="8"/>
-      <c r="P50" s="8"/>
-      <c r="Q50" s="8"/>
-      <c r="R50" s="8"/>
-      <c r="S50" s="8"/>
-      <c r="T50" s="8"/>
-      <c r="U50" s="8"/>
-      <c r="V50" s="8"/>
-      <c r="W50" s="8"/>
-      <c r="X50" s="8"/>
-    </row>
-    <row r="51" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="C50" s="8">
+        <v>9.8255555555555567</v>
+      </c>
+      <c r="D50" s="8">
+        <v>8.8999999999999986</v>
+      </c>
+      <c r="E50" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F50" s="8">
+        <v>0.60000000000000009</v>
+      </c>
+      <c r="G50" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H50" s="8">
+        <v>1</v>
+      </c>
+      <c r="I50" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J50" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="K50" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L50" s="8">
+        <v>1</v>
+      </c>
+      <c r="M50" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="N50" s="8">
+        <v>0.6</v>
+      </c>
+      <c r="O50" s="8">
+        <v>0</v>
+      </c>
+      <c r="P50" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="Q50" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="R50" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="S50" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="T50" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="U50" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="V50" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="W50" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="X50" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="51" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A51" s="9">
         <v>2024101154</v>
       </c>
       <c r="B51" s="8">
         <v>0.48055555555555551</v>
       </c>
-      <c r="C51" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="D51" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="E51" s="8"/>
-      <c r="F51" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="G51" s="8"/>
-      <c r="H51" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="I51" s="8"/>
-      <c r="J51" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="K51" s="8"/>
-      <c r="L51" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="M51" s="8"/>
-      <c r="N51" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="O51" s="8"/>
-      <c r="P51" s="8"/>
-      <c r="Q51" s="8"/>
-      <c r="R51" s="8"/>
-      <c r="S51" s="8"/>
-      <c r="T51" s="8"/>
-      <c r="U51" s="8"/>
-      <c r="V51" s="8"/>
-      <c r="W51" s="8"/>
-      <c r="X51" s="8"/>
-    </row>
-    <row r="52" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="C51" s="8">
+        <v>8.530555555555555</v>
+      </c>
+      <c r="D51" s="8">
+        <v>8.0500000000000007</v>
+      </c>
+      <c r="E51" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F51" s="8">
+        <v>0.60000000000000009</v>
+      </c>
+      <c r="G51" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H51" s="8">
+        <v>1</v>
+      </c>
+      <c r="I51" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="J51" s="8">
+        <v>0.6</v>
+      </c>
+      <c r="K51" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="L51" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M51" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="N51" s="8">
+        <v>0.6</v>
+      </c>
+      <c r="O51" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="P51" s="8">
+        <v>0.25</v>
+      </c>
+      <c r="Q51" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="R51" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="S51" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="T51" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="U51" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="V51" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="W51" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="X51" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="52" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A52" s="7">
         <v>2022102045</v>
       </c>
@@ -3373,31 +3921,31 @@
         <v>7.8000000000000007</v>
       </c>
       <c r="E52" s="8" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F52" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G52" s="8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H52" s="8">
         <v>1</v>
       </c>
       <c r="I52" s="8" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J52" s="8">
         <v>0.6</v>
       </c>
       <c r="K52" s="8" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="L52" s="8">
         <v>0.5</v>
       </c>
       <c r="M52" s="8" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="N52" s="8">
         <v>0.6</v>
@@ -3433,51 +3981,81 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="53" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A53" s="9">
         <v>2023101690</v>
       </c>
       <c r="B53" s="8">
         <v>0.31481481481481477</v>
       </c>
-      <c r="C53" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="D53" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="E53" s="8"/>
-      <c r="F53" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="G53" s="8"/>
-      <c r="H53" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="I53" s="8"/>
-      <c r="J53" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="K53" s="8"/>
-      <c r="L53" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="M53" s="8"/>
-      <c r="N53" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="O53" s="8"/>
-      <c r="P53" s="8"/>
-      <c r="Q53" s="8"/>
-      <c r="R53" s="8"/>
-      <c r="S53" s="8"/>
-      <c r="T53" s="8"/>
-      <c r="U53" s="8"/>
-      <c r="V53" s="8"/>
-      <c r="W53" s="8"/>
-      <c r="X53" s="8"/>
-    </row>
-    <row r="54" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="C53" s="8">
+        <v>9.0648148148148149</v>
+      </c>
+      <c r="D53" s="8">
+        <v>8.75</v>
+      </c>
+      <c r="E53" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F53" s="8">
+        <v>0.60000000000000009</v>
+      </c>
+      <c r="G53" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H53" s="8">
+        <v>1</v>
+      </c>
+      <c r="I53" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J53" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="K53" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L53" s="8">
+        <v>1</v>
+      </c>
+      <c r="M53" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="N53" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="O53" s="8">
+        <v>0</v>
+      </c>
+      <c r="P53" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="Q53" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="R53" s="8">
+        <v>0.25</v>
+      </c>
+      <c r="S53" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="T53" s="8">
+        <v>0.25</v>
+      </c>
+      <c r="U53" s="8">
+        <v>0.25</v>
+      </c>
+      <c r="V53" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="W53" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="X53" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="54" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A54" s="7">
         <v>2023100954</v>
       </c>
@@ -3521,7 +4099,7 @@
       <c r="W54" s="8"/>
       <c r="X54" s="8"/>
     </row>
-    <row r="55" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A55" s="9">
         <v>2024202997</v>
       </c>
@@ -3535,31 +4113,31 @@
         <v>7.65</v>
       </c>
       <c r="E55" s="8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F55" s="8">
         <v>0</v>
       </c>
       <c r="G55" s="8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H55" s="8">
         <v>1</v>
       </c>
       <c r="I55" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J55" s="8">
         <v>1.2</v>
       </c>
       <c r="K55" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L55" s="8">
         <v>1</v>
       </c>
       <c r="M55" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="N55" s="8">
         <v>1.2</v>
@@ -3595,7 +4173,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A56" s="7">
         <v>2020101573</v>
       </c>
@@ -3639,7 +4217,7 @@
       <c r="W56" s="8"/>
       <c r="X56" s="8"/>
     </row>
-    <row r="57" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A57" s="9">
         <v>2024101785</v>
       </c>
@@ -3683,51 +4261,81 @@
       <c r="W57" s="8"/>
       <c r="X57" s="8"/>
     </row>
-    <row r="58" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A58" s="7">
         <v>2021201017</v>
       </c>
       <c r="B58" s="8">
         <v>0.6755773420479303</v>
       </c>
-      <c r="C58" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="D58" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="E58" s="8"/>
-      <c r="F58" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="G58" s="8"/>
-      <c r="H58" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="I58" s="8"/>
-      <c r="J58" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="K58" s="8"/>
-      <c r="L58" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="M58" s="8"/>
-      <c r="N58" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="O58" s="8"/>
-      <c r="P58" s="8"/>
-      <c r="Q58" s="8"/>
-      <c r="R58" s="8"/>
-      <c r="S58" s="8"/>
-      <c r="T58" s="8"/>
-      <c r="U58" s="8"/>
-      <c r="V58" s="8"/>
-      <c r="W58" s="8"/>
-      <c r="X58" s="8"/>
-    </row>
-    <row r="59" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="C58" s="8">
+        <v>7.7255773420479308</v>
+      </c>
+      <c r="D58" s="8">
+        <v>7.05</v>
+      </c>
+      <c r="E58" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F58" s="8">
+        <v>0.60000000000000009</v>
+      </c>
+      <c r="G58" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H58" s="8">
+        <v>1</v>
+      </c>
+      <c r="I58" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J58" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="K58" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L58" s="8">
+        <v>1</v>
+      </c>
+      <c r="M58" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="N58" s="8">
+        <v>0</v>
+      </c>
+      <c r="O58" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="P58" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="8">
+        <v>0.25</v>
+      </c>
+      <c r="R58" s="8">
+        <v>0</v>
+      </c>
+      <c r="S58" s="8">
+        <v>0.25</v>
+      </c>
+      <c r="T58" s="8">
+        <v>0.25</v>
+      </c>
+      <c r="U58" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="V58" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="W58" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="X58" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="59" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A59" s="9">
         <v>2023101691</v>
       </c>
@@ -3771,7 +4379,7 @@
       <c r="W59" s="8"/>
       <c r="X59" s="8"/>
     </row>
-    <row r="60" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A60" s="7">
         <v>2024101770</v>
       </c>
@@ -3815,7 +4423,7 @@
       <c r="W60" s="8"/>
       <c r="X60" s="8"/>
     </row>
-    <row r="61" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A61" s="9">
         <v>2022200727</v>
       </c>
@@ -3829,31 +4437,31 @@
         <v>9.5</v>
       </c>
       <c r="E61" s="8" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F61" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G61" s="8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H61" s="8">
         <v>1</v>
       </c>
       <c r="I61" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J61" s="8">
         <v>1.2</v>
       </c>
       <c r="K61" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L61" s="8">
         <v>1</v>
       </c>
       <c r="M61" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="N61" s="8">
         <v>1.2</v>
@@ -3889,7 +4497,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="62" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A62" s="7">
         <v>2023101729</v>
       </c>
@@ -3903,31 +4511,31 @@
         <v>6.05</v>
       </c>
       <c r="E62" s="8" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F62" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G62" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H62" s="8">
         <v>0.9</v>
       </c>
       <c r="I62" s="8" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J62" s="8">
         <v>0.6</v>
       </c>
       <c r="K62" s="8" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="L62" s="8">
         <v>0.5</v>
       </c>
       <c r="M62" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="N62" s="8">
         <v>1.2</v>
@@ -3963,7 +4571,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A63" s="9">
         <v>2023100965</v>
       </c>
@@ -3977,31 +4585,31 @@
         <v>6.6499999999999995</v>
       </c>
       <c r="E63" s="8" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F63" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G63" s="8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H63" s="8">
         <v>1</v>
       </c>
       <c r="I63" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J63" s="8">
         <v>1.2</v>
       </c>
       <c r="K63" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L63" s="8">
         <v>1</v>
       </c>
       <c r="M63" s="8" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="N63" s="8">
         <v>0.6</v>
@@ -4037,93 +4645,153 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A64" s="7">
         <v>2024101155</v>
       </c>
       <c r="B64" s="8">
         <v>0.78740740740740744</v>
       </c>
-      <c r="C64" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="D64" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="E64" s="8"/>
-      <c r="F64" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="G64" s="8"/>
-      <c r="H64" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="I64" s="8"/>
-      <c r="J64" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="K64" s="8"/>
-      <c r="L64" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="M64" s="8"/>
-      <c r="N64" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="O64" s="8"/>
-      <c r="P64" s="8"/>
-      <c r="Q64" s="8"/>
-      <c r="R64" s="8"/>
-      <c r="S64" s="8"/>
-      <c r="T64" s="8"/>
-      <c r="U64" s="8"/>
-      <c r="V64" s="8"/>
-      <c r="W64" s="8"/>
-      <c r="X64" s="8"/>
-    </row>
-    <row r="65" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="C64" s="8">
+        <v>9.6874074074074059</v>
+      </c>
+      <c r="D64" s="8">
+        <v>8.8999999999999986</v>
+      </c>
+      <c r="E64" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F64" s="8">
+        <v>0.60000000000000009</v>
+      </c>
+      <c r="G64" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H64" s="8">
+        <v>1</v>
+      </c>
+      <c r="I64" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J64" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="K64" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L64" s="8">
+        <v>1</v>
+      </c>
+      <c r="M64" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="N64" s="8">
+        <v>0.6</v>
+      </c>
+      <c r="O64" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="P64" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="Q64" s="8">
+        <v>0.25</v>
+      </c>
+      <c r="R64" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="S64" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="T64" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="U64" s="8">
+        <v>0.25</v>
+      </c>
+      <c r="V64" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="W64" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="X64" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="65" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A65" s="9">
         <v>2023200064</v>
       </c>
       <c r="B65" s="8">
         <v>0.71650326797385622</v>
       </c>
-      <c r="C65" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="D65" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="E65" s="8"/>
-      <c r="F65" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="G65" s="8"/>
-      <c r="H65" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="I65" s="8"/>
-      <c r="J65" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="K65" s="8"/>
-      <c r="L65" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="M65" s="8"/>
-      <c r="N65" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="O65" s="8"/>
-      <c r="P65" s="8"/>
-      <c r="Q65" s="8"/>
-      <c r="R65" s="8"/>
-      <c r="S65" s="8"/>
-      <c r="T65" s="8"/>
-      <c r="U65" s="8"/>
-      <c r="V65" s="8"/>
-      <c r="W65" s="8"/>
-      <c r="X65" s="8"/>
+      <c r="C65" s="8">
+        <v>10.216503267973856</v>
+      </c>
+      <c r="D65" s="8">
+        <v>9.5</v>
+      </c>
+      <c r="E65" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F65" s="8">
+        <v>0.60000000000000009</v>
+      </c>
+      <c r="G65" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H65" s="8">
+        <v>1</v>
+      </c>
+      <c r="I65" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J65" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="K65" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L65" s="8">
+        <v>1</v>
+      </c>
+      <c r="M65" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="N65" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="O65" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="P65" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="Q65" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="R65" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="S65" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="T65" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="U65" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="V65" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="W65" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="X65" s="8">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/notas.xlsx
+++ b/notas.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11109"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuário\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/daniloas.com/projetos/FertilidadeSoloAlegreUFES/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76C81D95-47DC-404F-90DC-8C81499912D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE31F0EC-75C6-F24E-9246-714133F03918}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11310" xr2:uid="{BB9E0E1E-73DF-4AB6-A949-07A69840CAF7}"/>
+    <workbookView xWindow="0" yWindow="620" windowWidth="20740" windowHeight="11320" xr2:uid="{BB9E0E1E-73DF-4AB6-A949-07A69840CAF7}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -42,14 +42,6 @@
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="24">
   <si>
     <t>Matrícula</t>
-  </si>
-  <si>
-    <t>Pontuação 
-dos exercícios extras</t>
-  </si>
-  <si>
-    <t>Pontuação total
-(Prova + Extra)</t>
   </si>
   <si>
     <t>Item a</t>
@@ -113,6 +105,12 @@
   </si>
   <si>
     <t>0/0</t>
+  </si>
+  <si>
+    <t>Pontuação dos exercícios extras</t>
+  </si>
+  <si>
+    <t>Pontuação total (Prova + Extra)</t>
   </si>
 </sst>
 </file>
@@ -573,91 +571,91 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCC50A17-1BAD-4261-9C73-1273FB998B6D}">
   <dimension ref="A1:X65"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.28515625" customWidth="1"/>
+    <col min="2" max="2" width="16.33203125" customWidth="1"/>
     <col min="3" max="3" width="17" customWidth="1"/>
-    <col min="4" max="4" width="26.5703125" customWidth="1"/>
+    <col min="4" max="4" width="26.5" customWidth="1"/>
     <col min="5" max="5" width="7" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:24" ht="33" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="H1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="I1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="J1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="K1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="L1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="O1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="P1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="R1" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="S1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="T1" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="U1" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="V1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="W1" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="X1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="K1" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="L1" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N1" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="O1" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="P1" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q1" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="R1" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="S1" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="T1" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="U1" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="V1" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="W1" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="X1" s="6" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A2" s="7">
         <v>2023200939</v>
       </c>
@@ -671,31 +669,31 @@
         <v>9.1999999999999993</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F2" s="8">
         <v>0.4</v>
       </c>
       <c r="G2" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2" s="8">
+        <v>1</v>
+      </c>
+      <c r="I2" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="J2" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="K2" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="L2" s="8">
+        <v>1</v>
+      </c>
+      <c r="M2" s="8" t="s">
         <v>12</v>
-      </c>
-      <c r="H2" s="8">
-        <v>1</v>
-      </c>
-      <c r="I2" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="J2" s="8">
-        <v>1.2</v>
-      </c>
-      <c r="K2" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="L2" s="8">
-        <v>1</v>
-      </c>
-      <c r="M2" s="8" t="s">
-        <v>14</v>
       </c>
       <c r="N2" s="8">
         <v>0.6</v>
@@ -731,7 +729,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A3" s="9">
         <v>2023100005</v>
       </c>
@@ -745,31 +743,31 @@
         <v>8.6999999999999993</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F3" s="8">
         <v>0.4</v>
       </c>
       <c r="G3" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H3" s="8">
+        <v>1</v>
+      </c>
+      <c r="I3" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="J3" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="K3" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="L3" s="8">
+        <v>1</v>
+      </c>
+      <c r="M3" s="8" t="s">
         <v>12</v>
-      </c>
-      <c r="H3" s="8">
-        <v>1</v>
-      </c>
-      <c r="I3" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="J3" s="8">
-        <v>1.2</v>
-      </c>
-      <c r="K3" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="L3" s="8">
-        <v>1</v>
-      </c>
-      <c r="M3" s="8" t="s">
-        <v>14</v>
       </c>
       <c r="N3" s="8">
         <v>0.6</v>
@@ -805,7 +803,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A4" s="7">
         <v>2021101895</v>
       </c>
@@ -819,31 +817,31 @@
         <v>8.75</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F4" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H4" s="8">
         <v>1</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J4" s="8">
         <v>1.2</v>
       </c>
       <c r="K4" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L4" s="8">
         <v>1</v>
       </c>
       <c r="M4" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="N4" s="8">
         <v>1.2</v>
@@ -879,7 +877,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="9">
         <v>2024101156</v>
       </c>
@@ -893,31 +891,31 @@
         <v>9</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F5" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H5" s="8">
         <v>1</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J5" s="8">
         <v>1.2</v>
       </c>
       <c r="K5" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L5" s="8">
         <v>1</v>
       </c>
       <c r="M5" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="N5" s="8">
         <v>1.2</v>
@@ -953,7 +951,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A6" s="7">
         <v>2023200783</v>
       </c>
@@ -997,7 +995,7 @@
       <c r="W6" s="8"/>
       <c r="X6" s="8"/>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A7" s="9">
         <v>2022200360</v>
       </c>
@@ -1011,31 +1009,31 @@
         <v>9.3999999999999986</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F7" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G7" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H7" s="8">
+        <v>1</v>
+      </c>
+      <c r="I7" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="J7" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="K7" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="L7" s="8">
+        <v>1</v>
+      </c>
+      <c r="M7" s="8" t="s">
         <v>12</v>
-      </c>
-      <c r="H7" s="8">
-        <v>1</v>
-      </c>
-      <c r="I7" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="J7" s="8">
-        <v>1.2</v>
-      </c>
-      <c r="K7" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="L7" s="8">
-        <v>1</v>
-      </c>
-      <c r="M7" s="8" t="s">
-        <v>14</v>
       </c>
       <c r="N7" s="8">
         <v>0.6</v>
@@ -1071,7 +1069,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A8" s="7">
         <v>2024101774</v>
       </c>
@@ -1085,31 +1083,31 @@
         <v>9.75</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F8" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H8" s="8">
         <v>1</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J8" s="8">
         <v>1.2</v>
       </c>
       <c r="K8" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L8" s="8">
         <v>1</v>
       </c>
       <c r="M8" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="N8" s="8">
         <v>1.2</v>
@@ -1145,7 +1143,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A9" s="9">
         <v>2024203414</v>
       </c>
@@ -1159,31 +1157,31 @@
         <v>8.75</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F9" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H9" s="8">
         <v>1</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J9" s="8">
         <v>1.2</v>
       </c>
       <c r="K9" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L9" s="8">
         <v>1</v>
       </c>
       <c r="M9" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="N9" s="8">
         <v>1.2</v>
@@ -1219,7 +1217,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A10" s="7">
         <v>2023101046</v>
       </c>
@@ -1263,7 +1261,7 @@
       <c r="W10" s="8"/>
       <c r="X10" s="8"/>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A11" s="9">
         <v>2019109848</v>
       </c>
@@ -1307,7 +1305,7 @@
       <c r="W11" s="8"/>
       <c r="X11" s="8"/>
     </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A12" s="7">
         <v>2023102012</v>
       </c>
@@ -1321,31 +1319,31 @@
         <v>4.45</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F12" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G12" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H12" s="8">
+        <v>1</v>
+      </c>
+      <c r="I12" s="8" t="s">
         <v>12</v>
-      </c>
-      <c r="H12" s="8">
-        <v>1</v>
-      </c>
-      <c r="I12" s="8" t="s">
-        <v>14</v>
       </c>
       <c r="J12" s="8">
         <v>0.6</v>
       </c>
       <c r="K12" s="8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="L12" s="8">
         <v>0</v>
       </c>
       <c r="M12" s="8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="N12" s="8">
         <v>0</v>
@@ -1381,7 +1379,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A13" s="9">
         <v>2024101768</v>
       </c>
@@ -1425,7 +1423,7 @@
       <c r="W13" s="8"/>
       <c r="X13" s="8"/>
     </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A14" s="7">
         <v>2018104222</v>
       </c>
@@ -1439,31 +1437,31 @@
         <v>3.6</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F14" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H14" s="8">
         <v>1</v>
       </c>
       <c r="I14" s="8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J14" s="8">
         <v>0</v>
       </c>
       <c r="K14" s="8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="L14" s="8">
         <v>0</v>
       </c>
       <c r="M14" s="8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="N14" s="8">
         <v>0</v>
@@ -1499,7 +1497,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A15" s="9">
         <v>2017102706</v>
       </c>
@@ -1543,7 +1541,7 @@
       <c r="W15" s="8"/>
       <c r="X15" s="8"/>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A16" s="7">
         <v>2024103491</v>
       </c>
@@ -1557,31 +1555,31 @@
         <v>9.5</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F16" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G16" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H16" s="8">
+        <v>1</v>
+      </c>
+      <c r="I16" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="J16" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="K16" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="H16" s="8">
-        <v>1</v>
-      </c>
-      <c r="I16" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="J16" s="8">
-        <v>1.2</v>
-      </c>
-      <c r="K16" s="8" t="s">
-        <v>14</v>
-      </c>
       <c r="L16" s="8">
         <v>0.5</v>
       </c>
       <c r="M16" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="N16" s="8">
         <v>1.2</v>
@@ -1617,7 +1615,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A17" s="9">
         <v>2023100158</v>
       </c>
@@ -1631,31 +1629,31 @@
         <v>8.3999999999999986</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F17" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G17" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H17" s="8">
+        <v>1</v>
+      </c>
+      <c r="I17" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="J17" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="K17" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="L17" s="8">
+        <v>1</v>
+      </c>
+      <c r="M17" s="8" t="s">
         <v>12</v>
-      </c>
-      <c r="H17" s="8">
-        <v>1</v>
-      </c>
-      <c r="I17" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="J17" s="8">
-        <v>1.2</v>
-      </c>
-      <c r="K17" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="L17" s="8">
-        <v>1</v>
-      </c>
-      <c r="M17" s="8" t="s">
-        <v>14</v>
       </c>
       <c r="N17" s="8">
         <v>0.6</v>
@@ -1691,7 +1689,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A18" s="7">
         <v>2024101776</v>
       </c>
@@ -1735,7 +1733,7 @@
       <c r="W18" s="8"/>
       <c r="X18" s="8"/>
     </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A19" s="9">
         <v>2020102895</v>
       </c>
@@ -1779,7 +1777,7 @@
       <c r="W19" s="8"/>
       <c r="X19" s="8"/>
     </row>
-    <row r="20" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A20" s="7">
         <v>2018104240</v>
       </c>
@@ -1793,31 +1791,31 @@
         <v>5.7</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F20" s="8">
         <v>0</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H20" s="8">
         <v>1</v>
       </c>
       <c r="I20" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J20" s="8">
         <v>1.2</v>
       </c>
       <c r="K20" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L20" s="8">
         <v>1</v>
       </c>
       <c r="M20" s="8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="N20" s="8">
         <v>0</v>
@@ -1853,7 +1851,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A21" s="9">
         <v>2024101764</v>
       </c>
@@ -1867,31 +1865,31 @@
         <v>8.8999999999999986</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F21" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G21" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H21" s="8">
+        <v>1</v>
+      </c>
+      <c r="I21" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="J21" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="K21" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="L21" s="8">
+        <v>1</v>
+      </c>
+      <c r="M21" s="8" t="s">
         <v>12</v>
-      </c>
-      <c r="H21" s="8">
-        <v>1</v>
-      </c>
-      <c r="I21" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="J21" s="8">
-        <v>1.2</v>
-      </c>
-      <c r="K21" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="L21" s="8">
-        <v>1</v>
-      </c>
-      <c r="M21" s="8" t="s">
-        <v>14</v>
       </c>
       <c r="N21" s="8">
         <v>0.6</v>
@@ -1927,7 +1925,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="22" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A22" s="7">
         <v>2022102060</v>
       </c>
@@ -1971,7 +1969,7 @@
       <c r="W22" s="8"/>
       <c r="X22" s="8"/>
     </row>
-    <row r="23" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A23" s="9">
         <v>2024103490</v>
       </c>
@@ -1985,31 +1983,31 @@
         <v>9.1499999999999986</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F23" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G23" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H23" s="8">
+        <v>1</v>
+      </c>
+      <c r="I23" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="J23" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="K23" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="L23" s="8">
+        <v>1</v>
+      </c>
+      <c r="M23" s="8" t="s">
         <v>12</v>
-      </c>
-      <c r="H23" s="8">
-        <v>1</v>
-      </c>
-      <c r="I23" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="J23" s="8">
-        <v>1.2</v>
-      </c>
-      <c r="K23" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="L23" s="8">
-        <v>1</v>
-      </c>
-      <c r="M23" s="8" t="s">
-        <v>14</v>
       </c>
       <c r="N23" s="8">
         <v>0.6</v>
@@ -2045,7 +2043,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="24" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A24" s="7">
         <v>2023100771</v>
       </c>
@@ -2059,31 +2057,31 @@
         <v>6.35</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F24" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G24" s="8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H24" s="8">
         <v>1</v>
       </c>
       <c r="I24" s="8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J24" s="8">
         <v>0</v>
       </c>
       <c r="K24" s="8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="L24" s="8">
         <v>0</v>
       </c>
       <c r="M24" s="8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="N24" s="8">
         <v>0</v>
@@ -2119,7 +2117,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="25" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A25" s="9">
         <v>2023100962</v>
       </c>
@@ -2163,7 +2161,7 @@
       <c r="W25" s="8"/>
       <c r="X25" s="8"/>
     </row>
-    <row r="26" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A26" s="7">
         <v>2021101361</v>
       </c>
@@ -2177,31 +2175,31 @@
         <v>7.3</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F26" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G26" s="8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H26" s="8">
         <v>1</v>
       </c>
       <c r="I26" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J26" s="8">
         <v>1.2</v>
       </c>
       <c r="K26" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L26" s="8">
         <v>1</v>
       </c>
       <c r="M26" s="8" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="N26" s="8">
         <v>0</v>
@@ -2237,7 +2235,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A27" s="9">
         <v>2023201341</v>
       </c>
@@ -2251,31 +2249,31 @@
         <v>8.65</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F27" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G27" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H27" s="8">
+        <v>1</v>
+      </c>
+      <c r="I27" s="8" t="s">
         <v>12</v>
-      </c>
-      <c r="H27" s="8">
-        <v>1</v>
-      </c>
-      <c r="I27" s="8" t="s">
-        <v>14</v>
       </c>
       <c r="J27" s="8">
         <v>0.6</v>
       </c>
       <c r="K27" s="8" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L27" s="8">
         <v>0.5</v>
       </c>
       <c r="M27" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="N27" s="8">
         <v>1.2</v>
@@ -2311,7 +2309,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="28" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A28" s="7">
         <v>2023101463</v>
       </c>
@@ -2325,31 +2323,31 @@
         <v>6.5500000000000007</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F28" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G28" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H28" s="8">
+        <v>1</v>
+      </c>
+      <c r="I28" s="8" t="s">
         <v>12</v>
-      </c>
-      <c r="H28" s="8">
-        <v>1</v>
-      </c>
-      <c r="I28" s="8" t="s">
-        <v>14</v>
       </c>
       <c r="J28" s="8">
         <v>0.6</v>
       </c>
       <c r="K28" s="8" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L28" s="8">
         <v>0.5</v>
       </c>
       <c r="M28" s="8" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N28" s="8">
         <v>0.6</v>
@@ -2385,7 +2383,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A29" s="9">
         <v>2022201037</v>
       </c>
@@ -2399,31 +2397,31 @@
         <v>9.25</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F29" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G29" s="8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H29" s="8">
         <v>1</v>
       </c>
       <c r="I29" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J29" s="8">
         <v>1.2</v>
       </c>
       <c r="K29" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L29" s="8">
         <v>1</v>
       </c>
       <c r="M29" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="N29" s="8">
         <v>1.2</v>
@@ -2459,7 +2457,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="30" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A30" s="7">
         <v>2021101896</v>
       </c>
@@ -2473,31 +2471,31 @@
         <v>10</v>
       </c>
       <c r="E30" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F30" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G30" s="8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H30" s="8">
         <v>1</v>
       </c>
       <c r="I30" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J30" s="8">
         <v>1.2</v>
       </c>
       <c r="K30" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L30" s="8">
         <v>1</v>
       </c>
       <c r="M30" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="N30" s="8">
         <v>1.2</v>
@@ -2533,7 +2531,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="31" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A31" s="9">
         <v>2022201042</v>
       </c>
@@ -2577,7 +2575,7 @@
       <c r="W31" s="8"/>
       <c r="X31" s="8"/>
     </row>
-    <row r="32" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A32" s="7">
         <v>2020102888</v>
       </c>
@@ -2591,31 +2589,31 @@
         <v>7.95</v>
       </c>
       <c r="E32" s="8" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F32" s="8">
         <v>0.2</v>
       </c>
       <c r="G32" s="8" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H32" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="I32" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J32" s="8">
         <v>1.2</v>
       </c>
       <c r="K32" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L32" s="8">
         <v>1</v>
       </c>
       <c r="M32" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="N32" s="8">
         <v>1.2</v>
@@ -2651,7 +2649,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A33" s="9">
         <v>2024101765</v>
       </c>
@@ -2665,31 +2663,31 @@
         <v>8.3000000000000007</v>
       </c>
       <c r="E33" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F33" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G33" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H33" s="8">
+        <v>1</v>
+      </c>
+      <c r="I33" s="8" t="s">
         <v>12</v>
-      </c>
-      <c r="H33" s="8">
-        <v>1</v>
-      </c>
-      <c r="I33" s="8" t="s">
-        <v>14</v>
       </c>
       <c r="J33" s="8">
         <v>0.6</v>
       </c>
       <c r="K33" s="8" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L33" s="8">
         <v>0.5</v>
       </c>
       <c r="M33" s="8" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N33" s="8">
         <v>0.6</v>
@@ -2725,7 +2723,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="34" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A34" s="7">
         <v>2022100612</v>
       </c>
@@ -2769,7 +2767,7 @@
       <c r="W34" s="8"/>
       <c r="X34" s="8"/>
     </row>
-    <row r="35" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A35" s="9">
         <v>2023101467</v>
       </c>
@@ -2813,7 +2811,7 @@
       <c r="W35" s="8"/>
       <c r="X35" s="8"/>
     </row>
-    <row r="36" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A36" s="7">
         <v>2022100511</v>
       </c>
@@ -2827,31 +2825,31 @@
         <v>6.35</v>
       </c>
       <c r="E36" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F36" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G36" s="8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H36" s="8">
         <v>1</v>
       </c>
       <c r="I36" s="8" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J36" s="8">
         <v>0</v>
       </c>
       <c r="K36" s="8" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="L36" s="8">
         <v>0</v>
       </c>
       <c r="M36" s="8" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N36" s="8">
         <v>0</v>
@@ -2887,7 +2885,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="37" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A37" s="9">
         <v>2023200147</v>
       </c>
@@ -2901,31 +2899,31 @@
         <v>10</v>
       </c>
       <c r="E37" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F37" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G37" s="8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H37" s="8">
         <v>1</v>
       </c>
       <c r="I37" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J37" s="8">
         <v>1.2</v>
       </c>
       <c r="K37" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L37" s="8">
         <v>1</v>
       </c>
       <c r="M37" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="N37" s="8">
         <v>1.2</v>
@@ -2961,7 +2959,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="38" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A38" s="7">
         <v>2023100776</v>
       </c>
@@ -2975,31 +2973,31 @@
         <v>9.5</v>
       </c>
       <c r="E38" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F38" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G38" s="8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H38" s="8">
         <v>1</v>
       </c>
       <c r="I38" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J38" s="8">
         <v>1.2</v>
       </c>
       <c r="K38" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L38" s="8">
         <v>1</v>
       </c>
       <c r="M38" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="N38" s="8">
         <v>1.2</v>
@@ -3035,7 +3033,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="39" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A39" s="9">
         <v>2024101158</v>
       </c>
@@ -3049,31 +3047,31 @@
         <v>10</v>
       </c>
       <c r="E39" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F39" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G39" s="8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H39" s="8">
         <v>1</v>
       </c>
       <c r="I39" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J39" s="8">
         <v>1.2</v>
       </c>
       <c r="K39" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L39" s="8">
         <v>1</v>
       </c>
       <c r="M39" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="N39" s="8">
         <v>1.2</v>
@@ -3109,7 +3107,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="40" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A40" s="7">
         <v>2024101773</v>
       </c>
@@ -3123,31 +3121,31 @@
         <v>9.75</v>
       </c>
       <c r="E40" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F40" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G40" s="8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H40" s="8">
         <v>1</v>
       </c>
       <c r="I40" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J40" s="8">
         <v>1.2</v>
       </c>
       <c r="K40" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L40" s="8">
         <v>1</v>
       </c>
       <c r="M40" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="N40" s="8">
         <v>1.2</v>
@@ -3183,7 +3181,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="41" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A41" s="9">
         <v>2023100068</v>
       </c>
@@ -3227,7 +3225,7 @@
       <c r="W41" s="8"/>
       <c r="X41" s="8"/>
     </row>
-    <row r="42" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A42" s="7">
         <v>2023200790</v>
       </c>
@@ -3271,7 +3269,7 @@
       <c r="W42" s="8"/>
       <c r="X42" s="8"/>
     </row>
-    <row r="43" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A43" s="9">
         <v>2022200719</v>
       </c>
@@ -3285,31 +3283,31 @@
         <v>9.75</v>
       </c>
       <c r="E43" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F43" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G43" s="8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H43" s="8">
         <v>1</v>
       </c>
       <c r="I43" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J43" s="8">
         <v>1.2</v>
       </c>
       <c r="K43" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L43" s="8">
         <v>1</v>
       </c>
       <c r="M43" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="N43" s="8">
         <v>1.2</v>
@@ -3345,7 +3343,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="44" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A44" s="8">
         <v>2025201178</v>
       </c>
@@ -3359,31 +3357,31 @@
         <v>6.05</v>
       </c>
       <c r="E44" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F44" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G44" s="8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H44" s="8">
         <v>1</v>
       </c>
       <c r="I44" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J44" s="8">
         <v>1.2</v>
       </c>
       <c r="K44" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L44" s="8">
         <v>1</v>
       </c>
       <c r="M44" s="8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="N44" s="8">
         <v>0</v>
@@ -3419,7 +3417,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A45" s="9">
         <v>2024101775</v>
       </c>
@@ -3433,31 +3431,31 @@
         <v>9.1499999999999986</v>
       </c>
       <c r="E45" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F45" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G45" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H45" s="8">
+        <v>1</v>
+      </c>
+      <c r="I45" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="J45" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="K45" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="L45" s="8">
+        <v>1</v>
+      </c>
+      <c r="M45" s="8" t="s">
         <v>12</v>
-      </c>
-      <c r="H45" s="8">
-        <v>1</v>
-      </c>
-      <c r="I45" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="J45" s="8">
-        <v>1.2</v>
-      </c>
-      <c r="K45" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="L45" s="8">
-        <v>1</v>
-      </c>
-      <c r="M45" s="8" t="s">
-        <v>14</v>
       </c>
       <c r="N45" s="8">
         <v>0.6</v>
@@ -3493,7 +3491,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="46" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A46" s="7">
         <v>2024103187</v>
       </c>
@@ -3507,31 +3505,31 @@
         <v>7.9</v>
       </c>
       <c r="E46" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F46" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G46" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H46" s="8">
+        <v>1</v>
+      </c>
+      <c r="I46" s="8" t="s">
         <v>12</v>
-      </c>
-      <c r="H46" s="8">
-        <v>1</v>
-      </c>
-      <c r="I46" s="8" t="s">
-        <v>14</v>
       </c>
       <c r="J46" s="8">
         <v>0.6</v>
       </c>
       <c r="K46" s="8" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L46" s="8">
         <v>0.5</v>
       </c>
       <c r="M46" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="N46" s="8">
         <v>1.2</v>
@@ -3567,7 +3565,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="47" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A47" s="9">
         <v>2023102386</v>
       </c>
@@ -3581,31 +3579,31 @@
         <v>9</v>
       </c>
       <c r="E47" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F47" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G47" s="8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H47" s="8">
         <v>1</v>
       </c>
       <c r="I47" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J47" s="8">
         <v>1.2</v>
       </c>
       <c r="K47" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L47" s="8">
         <v>1</v>
       </c>
       <c r="M47" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="N47" s="8">
         <v>1.2</v>
@@ -3641,7 +3639,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="48" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A48" s="7">
         <v>2020101654</v>
       </c>
@@ -3685,7 +3683,7 @@
       <c r="W48" s="8"/>
       <c r="X48" s="8"/>
     </row>
-    <row r="49" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A49" s="9">
         <v>2022201082</v>
       </c>
@@ -3699,31 +3697,31 @@
         <v>9.65</v>
       </c>
       <c r="E49" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F49" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G49" s="8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H49" s="8">
         <v>0.9</v>
       </c>
       <c r="I49" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J49" s="8">
         <v>1.2</v>
       </c>
       <c r="K49" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L49" s="8">
         <v>1</v>
       </c>
       <c r="M49" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="N49" s="8">
         <v>1.2</v>
@@ -3759,7 +3757,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="50" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A50" s="7">
         <v>2024101769</v>
       </c>
@@ -3773,31 +3771,31 @@
         <v>8.8999999999999986</v>
       </c>
       <c r="E50" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F50" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G50" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H50" s="8">
+        <v>1</v>
+      </c>
+      <c r="I50" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="J50" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="K50" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="L50" s="8">
+        <v>1</v>
+      </c>
+      <c r="M50" s="8" t="s">
         <v>12</v>
-      </c>
-      <c r="H50" s="8">
-        <v>1</v>
-      </c>
-      <c r="I50" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="J50" s="8">
-        <v>1.2</v>
-      </c>
-      <c r="K50" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="L50" s="8">
-        <v>1</v>
-      </c>
-      <c r="M50" s="8" t="s">
-        <v>14</v>
       </c>
       <c r="N50" s="8">
         <v>0.6</v>
@@ -3833,7 +3831,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="51" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A51" s="9">
         <v>2024101154</v>
       </c>
@@ -3847,31 +3845,31 @@
         <v>8.0500000000000007</v>
       </c>
       <c r="E51" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F51" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G51" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H51" s="8">
+        <v>1</v>
+      </c>
+      <c r="I51" s="8" t="s">
         <v>12</v>
-      </c>
-      <c r="H51" s="8">
-        <v>1</v>
-      </c>
-      <c r="I51" s="8" t="s">
-        <v>14</v>
       </c>
       <c r="J51" s="8">
         <v>0.6</v>
       </c>
       <c r="K51" s="8" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L51" s="8">
         <v>0.5</v>
       </c>
       <c r="M51" s="8" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N51" s="8">
         <v>0.6</v>
@@ -3907,7 +3905,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="52" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A52" s="7">
         <v>2022102045</v>
       </c>
@@ -3921,31 +3919,31 @@
         <v>7.8000000000000007</v>
       </c>
       <c r="E52" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F52" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G52" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H52" s="8">
+        <v>1</v>
+      </c>
+      <c r="I52" s="8" t="s">
         <v>12</v>
-      </c>
-      <c r="H52" s="8">
-        <v>1</v>
-      </c>
-      <c r="I52" s="8" t="s">
-        <v>14</v>
       </c>
       <c r="J52" s="8">
         <v>0.6</v>
       </c>
       <c r="K52" s="8" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L52" s="8">
         <v>0.5</v>
       </c>
       <c r="M52" s="8" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N52" s="8">
         <v>0.6</v>
@@ -3981,7 +3979,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="53" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A53" s="9">
         <v>2023101690</v>
       </c>
@@ -3995,31 +3993,31 @@
         <v>8.75</v>
       </c>
       <c r="E53" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F53" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G53" s="8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H53" s="8">
         <v>1</v>
       </c>
       <c r="I53" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J53" s="8">
         <v>1.2</v>
       </c>
       <c r="K53" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L53" s="8">
         <v>1</v>
       </c>
       <c r="M53" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="N53" s="8">
         <v>1.2</v>
@@ -4055,7 +4053,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="54" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A54" s="7">
         <v>2023100954</v>
       </c>
@@ -4099,7 +4097,7 @@
       <c r="W54" s="8"/>
       <c r="X54" s="8"/>
     </row>
-    <row r="55" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A55" s="9">
         <v>2024202997</v>
       </c>
@@ -4113,31 +4111,31 @@
         <v>7.65</v>
       </c>
       <c r="E55" s="8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F55" s="8">
         <v>0</v>
       </c>
       <c r="G55" s="8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H55" s="8">
         <v>1</v>
       </c>
       <c r="I55" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J55" s="8">
         <v>1.2</v>
       </c>
       <c r="K55" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L55" s="8">
         <v>1</v>
       </c>
       <c r="M55" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="N55" s="8">
         <v>1.2</v>
@@ -4173,7 +4171,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A56" s="7">
         <v>2020101573</v>
       </c>
@@ -4217,7 +4215,7 @@
       <c r="W56" s="8"/>
       <c r="X56" s="8"/>
     </row>
-    <row r="57" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A57" s="9">
         <v>2024101785</v>
       </c>
@@ -4261,7 +4259,7 @@
       <c r="W57" s="8"/>
       <c r="X57" s="8"/>
     </row>
-    <row r="58" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A58" s="7">
         <v>2021201017</v>
       </c>
@@ -4275,31 +4273,31 @@
         <v>7.05</v>
       </c>
       <c r="E58" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F58" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G58" s="8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H58" s="8">
         <v>1</v>
       </c>
       <c r="I58" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J58" s="8">
         <v>1.2</v>
       </c>
       <c r="K58" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L58" s="8">
         <v>1</v>
       </c>
       <c r="M58" s="8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="N58" s="8">
         <v>0</v>
@@ -4335,7 +4333,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="59" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A59" s="9">
         <v>2023101691</v>
       </c>
@@ -4379,7 +4377,7 @@
       <c r="W59" s="8"/>
       <c r="X59" s="8"/>
     </row>
-    <row r="60" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A60" s="7">
         <v>2024101770</v>
       </c>
@@ -4423,7 +4421,7 @@
       <c r="W60" s="8"/>
       <c r="X60" s="8"/>
     </row>
-    <row r="61" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A61" s="9">
         <v>2022200727</v>
       </c>
@@ -4437,31 +4435,31 @@
         <v>9.5</v>
       </c>
       <c r="E61" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F61" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G61" s="8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H61" s="8">
         <v>1</v>
       </c>
       <c r="I61" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J61" s="8">
         <v>1.2</v>
       </c>
       <c r="K61" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L61" s="8">
         <v>1</v>
       </c>
       <c r="M61" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="N61" s="8">
         <v>1.2</v>
@@ -4497,7 +4495,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="62" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A62" s="7">
         <v>2023101729</v>
       </c>
@@ -4511,31 +4509,31 @@
         <v>6.05</v>
       </c>
       <c r="E62" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F62" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G62" s="8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H62" s="8">
         <v>0.9</v>
       </c>
       <c r="I62" s="8" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J62" s="8">
         <v>0.6</v>
       </c>
       <c r="K62" s="8" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L62" s="8">
         <v>0.5</v>
       </c>
       <c r="M62" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="N62" s="8">
         <v>1.2</v>
@@ -4571,7 +4569,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A63" s="9">
         <v>2023100965</v>
       </c>
@@ -4585,31 +4583,31 @@
         <v>6.6499999999999995</v>
       </c>
       <c r="E63" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F63" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G63" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H63" s="8">
+        <v>1</v>
+      </c>
+      <c r="I63" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="J63" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="K63" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="L63" s="8">
+        <v>1</v>
+      </c>
+      <c r="M63" s="8" t="s">
         <v>12</v>
-      </c>
-      <c r="H63" s="8">
-        <v>1</v>
-      </c>
-      <c r="I63" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="J63" s="8">
-        <v>1.2</v>
-      </c>
-      <c r="K63" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="L63" s="8">
-        <v>1</v>
-      </c>
-      <c r="M63" s="8" t="s">
-        <v>14</v>
       </c>
       <c r="N63" s="8">
         <v>0.6</v>
@@ -4645,7 +4643,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A64" s="7">
         <v>2024101155</v>
       </c>
@@ -4659,31 +4657,31 @@
         <v>8.8999999999999986</v>
       </c>
       <c r="E64" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F64" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G64" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H64" s="8">
+        <v>1</v>
+      </c>
+      <c r="I64" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="J64" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="K64" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="L64" s="8">
+        <v>1</v>
+      </c>
+      <c r="M64" s="8" t="s">
         <v>12</v>
-      </c>
-      <c r="H64" s="8">
-        <v>1</v>
-      </c>
-      <c r="I64" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="J64" s="8">
-        <v>1.2</v>
-      </c>
-      <c r="K64" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="L64" s="8">
-        <v>1</v>
-      </c>
-      <c r="M64" s="8" t="s">
-        <v>14</v>
       </c>
       <c r="N64" s="8">
         <v>0.6</v>
@@ -4719,7 +4717,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="65" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A65" s="9">
         <v>2023200064</v>
       </c>
@@ -4733,31 +4731,31 @@
         <v>9.5</v>
       </c>
       <c r="E65" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F65" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G65" s="8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H65" s="8">
         <v>1</v>
       </c>
       <c r="I65" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J65" s="8">
         <v>1.2</v>
       </c>
       <c r="K65" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L65" s="8">
         <v>1</v>
       </c>
       <c r="M65" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="N65" s="8">
         <v>1.2</v>

--- a/notas.xlsx
+++ b/notas.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11109"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/daniloas.com/projetos/FertilidadeSoloAlegreUFES/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuário\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE31F0EC-75C6-F24E-9246-714133F03918}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AF233E4-7BB1-4179-830E-6CD66077B15C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="620" windowWidth="20740" windowHeight="11320" xr2:uid="{BB9E0E1E-73DF-4AB6-A949-07A69840CAF7}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11310" xr2:uid="{BB9E0E1E-73DF-4AB6-A949-07A69840CAF7}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -39,9 +39,17 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="27">
   <si>
     <t>Matrícula</t>
+  </si>
+  <si>
+    <t>Pontuação 
+dos exercícios extras</t>
+  </si>
+  <si>
+    <t>Pontuação total
+(Prova + Extra)</t>
   </si>
   <si>
     <t>Item a</t>
@@ -107,10 +115,13 @@
     <t>0/0</t>
   </si>
   <si>
-    <t>Pontuação dos exercícios extras</t>
+    <t>0/10</t>
   </si>
   <si>
-    <t>Pontuação total (Prova + Extra)</t>
+    <t>5/10</t>
+  </si>
+  <si>
+    <t>7/10</t>
   </si>
 </sst>
 </file>
@@ -571,91 +582,91 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCC50A17-1BAD-4261-9C73-1273FB998B6D}">
   <dimension ref="A1:X65"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.33203125" customWidth="1"/>
+    <col min="2" max="2" width="16.28515625" customWidth="1"/>
     <col min="3" max="3" width="17" customWidth="1"/>
-    <col min="4" max="4" width="26.5" customWidth="1"/>
+    <col min="4" max="4" width="26.5703125" customWidth="1"/>
     <col min="5" max="5" width="7" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="33" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="O1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="K1" s="3" t="s">
+      <c r="P1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="L1" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="M1" s="3" t="s">
+      <c r="Q1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="N1" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="O1" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="P1" s="5" t="s">
+      <c r="R1" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="S1" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="T1" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="U1" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="V1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="Q1" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="R1" s="5" t="s">
+      <c r="W1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="S1" s="5" t="s">
+      <c r="X1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="T1" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="U1" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="V1" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="W1" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="X1" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A2" s="7">
         <v>2023200939</v>
       </c>
@@ -669,31 +680,31 @@
         <v>9.1999999999999993</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F2" s="8">
         <v>0.4</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H2" s="8">
         <v>1</v>
       </c>
       <c r="I2" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J2" s="8">
         <v>1.2</v>
       </c>
       <c r="K2" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L2" s="8">
         <v>1</v>
       </c>
       <c r="M2" s="8" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="N2" s="8">
         <v>0.6</v>
@@ -729,7 +740,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A3" s="9">
         <v>2023100005</v>
       </c>
@@ -743,31 +754,31 @@
         <v>8.6999999999999993</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F3" s="8">
         <v>0.4</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H3" s="8">
         <v>1</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J3" s="8">
         <v>1.2</v>
       </c>
       <c r="K3" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L3" s="8">
         <v>1</v>
       </c>
       <c r="M3" s="8" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="N3" s="8">
         <v>0.6</v>
@@ -803,7 +814,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A4" s="7">
         <v>2021101895</v>
       </c>
@@ -817,31 +828,31 @@
         <v>8.75</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F4" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H4" s="8">
         <v>1</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J4" s="8">
         <v>1.2</v>
       </c>
       <c r="K4" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L4" s="8">
         <v>1</v>
       </c>
       <c r="M4" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="N4" s="8">
         <v>1.2</v>
@@ -877,7 +888,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A5" s="9">
         <v>2024101156</v>
       </c>
@@ -891,31 +902,31 @@
         <v>9</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F5" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H5" s="8">
         <v>1</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J5" s="8">
         <v>1.2</v>
       </c>
       <c r="K5" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L5" s="8">
         <v>1</v>
       </c>
       <c r="M5" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="N5" s="8">
         <v>1.2</v>
@@ -951,51 +962,81 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A6" s="7">
         <v>2023200783</v>
       </c>
       <c r="B6" s="8">
         <v>0.9061111111111112</v>
       </c>
-      <c r="C6" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="D6" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="G6" s="8"/>
-      <c r="H6" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="I6" s="8"/>
-      <c r="J6" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="K6" s="8"/>
-      <c r="L6" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="M6" s="8"/>
-      <c r="N6" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="O6" s="8"/>
-      <c r="P6" s="8"/>
-      <c r="Q6" s="8"/>
-      <c r="R6" s="8"/>
-      <c r="S6" s="8"/>
-      <c r="T6" s="8"/>
-      <c r="U6" s="8"/>
-      <c r="V6" s="8"/>
-      <c r="W6" s="8"/>
-      <c r="X6" s="8"/>
-    </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="C6" s="8">
+        <v>10.406111111111112</v>
+      </c>
+      <c r="D6" s="8">
+        <v>9.5</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F6" s="8">
+        <v>0.60000000000000009</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H6" s="8">
+        <v>1</v>
+      </c>
+      <c r="I6" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J6" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="K6" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L6" s="8">
+        <v>1</v>
+      </c>
+      <c r="M6" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="N6" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="O6" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="P6" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="Q6" s="8">
+        <v>0.25</v>
+      </c>
+      <c r="R6" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="S6" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="T6" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="U6" s="8">
+        <v>0.25</v>
+      </c>
+      <c r="V6" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="W6" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="X6" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A7" s="9">
         <v>2022200360</v>
       </c>
@@ -1009,31 +1050,31 @@
         <v>9.3999999999999986</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F7" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H7" s="8">
         <v>1</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J7" s="8">
         <v>1.2</v>
       </c>
       <c r="K7" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L7" s="8">
         <v>1</v>
       </c>
       <c r="M7" s="8" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="N7" s="8">
         <v>0.6</v>
@@ -1069,7 +1110,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A8" s="7">
         <v>2024101774</v>
       </c>
@@ -1083,31 +1124,31 @@
         <v>9.75</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F8" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H8" s="8">
         <v>1</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J8" s="8">
         <v>1.2</v>
       </c>
       <c r="K8" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L8" s="8">
         <v>1</v>
       </c>
       <c r="M8" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="N8" s="8">
         <v>1.2</v>
@@ -1143,7 +1184,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A9" s="9">
         <v>2024203414</v>
       </c>
@@ -1157,31 +1198,31 @@
         <v>8.75</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F9" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H9" s="8">
         <v>1</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J9" s="8">
         <v>1.2</v>
       </c>
       <c r="K9" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L9" s="8">
         <v>1</v>
       </c>
       <c r="M9" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="N9" s="8">
         <v>1.2</v>
@@ -1217,51 +1258,81 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A10" s="7">
         <v>2023101046</v>
       </c>
       <c r="B10" s="8">
         <v>0.68316993464052289</v>
       </c>
-      <c r="C10" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="D10" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="G10" s="8"/>
-      <c r="H10" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="I10" s="8"/>
-      <c r="J10" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="K10" s="8"/>
-      <c r="L10" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="M10" s="8"/>
-      <c r="N10" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="O10" s="8"/>
-      <c r="P10" s="8"/>
-      <c r="Q10" s="8"/>
-      <c r="R10" s="8"/>
-      <c r="S10" s="8"/>
-      <c r="T10" s="8"/>
-      <c r="U10" s="8"/>
-      <c r="V10" s="8"/>
-      <c r="W10" s="8"/>
-      <c r="X10" s="8"/>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="C10" s="8">
+        <v>10.183169934640524</v>
+      </c>
+      <c r="D10" s="8">
+        <v>9.5</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F10" s="8">
+        <v>0.60000000000000009</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H10" s="8">
+        <v>1</v>
+      </c>
+      <c r="I10" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J10" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="K10" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L10" s="8">
+        <v>1</v>
+      </c>
+      <c r="M10" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="N10" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="O10" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="P10" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="Q10" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="R10" s="8">
+        <v>0.25</v>
+      </c>
+      <c r="S10" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="T10" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="U10" s="8">
+        <v>0.25</v>
+      </c>
+      <c r="V10" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="W10" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="X10" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A11" s="9">
         <v>2019109848</v>
       </c>
@@ -1305,7 +1376,7 @@
       <c r="W11" s="8"/>
       <c r="X11" s="8"/>
     </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A12" s="7">
         <v>2023102012</v>
       </c>
@@ -1319,31 +1390,31 @@
         <v>4.45</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F12" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H12" s="8">
         <v>1</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J12" s="8">
         <v>0.6</v>
       </c>
       <c r="K12" s="8" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="L12" s="8">
         <v>0</v>
       </c>
       <c r="M12" s="8" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="N12" s="8">
         <v>0</v>
@@ -1379,51 +1450,81 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A13" s="9">
         <v>2024101768</v>
       </c>
       <c r="B13" s="8">
         <v>0.72259259259259256</v>
       </c>
-      <c r="C13" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="D13" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="E13" s="8"/>
-      <c r="F13" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="G13" s="8"/>
-      <c r="H13" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="I13" s="8"/>
-      <c r="J13" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="K13" s="8"/>
-      <c r="L13" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="M13" s="8"/>
-      <c r="N13" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="O13" s="8"/>
-      <c r="P13" s="8"/>
-      <c r="Q13" s="8"/>
-      <c r="R13" s="8"/>
-      <c r="S13" s="8"/>
-      <c r="T13" s="8"/>
-      <c r="U13" s="8"/>
-      <c r="V13" s="8"/>
-      <c r="W13" s="8"/>
-      <c r="X13" s="8"/>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="C13" s="8">
+        <v>10.472592592592592</v>
+      </c>
+      <c r="D13" s="8">
+        <v>9.75</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F13" s="8">
+        <v>0.60000000000000009</v>
+      </c>
+      <c r="G13" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H13" s="8">
+        <v>1</v>
+      </c>
+      <c r="I13" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J13" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="K13" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L13" s="8">
+        <v>1</v>
+      </c>
+      <c r="M13" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="N13" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="O13" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="P13" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="Q13" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="R13" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="S13" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="T13" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="U13" s="8">
+        <v>0.25</v>
+      </c>
+      <c r="V13" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="W13" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="X13" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A14" s="7">
         <v>2018104222</v>
       </c>
@@ -1437,31 +1538,31 @@
         <v>3.6</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F14" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H14" s="8">
         <v>1</v>
       </c>
       <c r="I14" s="8" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J14" s="8">
         <v>0</v>
       </c>
       <c r="K14" s="8" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="L14" s="8">
         <v>0</v>
       </c>
       <c r="M14" s="8" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="N14" s="8">
         <v>0</v>
@@ -1497,51 +1598,81 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A15" s="9">
         <v>2017102706</v>
       </c>
       <c r="B15" s="8">
         <v>0.80681732026143782</v>
       </c>
-      <c r="C15" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="D15" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="E15" s="8"/>
-      <c r="F15" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="G15" s="8"/>
-      <c r="H15" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="I15" s="8"/>
-      <c r="J15" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="K15" s="8"/>
-      <c r="L15" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="M15" s="8"/>
-      <c r="N15" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="O15" s="8"/>
-      <c r="P15" s="8"/>
-      <c r="Q15" s="8"/>
-      <c r="R15" s="8"/>
-      <c r="S15" s="8"/>
-      <c r="T15" s="8"/>
-      <c r="U15" s="8"/>
-      <c r="V15" s="8"/>
-      <c r="W15" s="8"/>
-      <c r="X15" s="8"/>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="C15" s="8">
+        <v>5.3068173202614375</v>
+      </c>
+      <c r="D15" s="8">
+        <v>4.5</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="F15" s="8">
+        <v>0</v>
+      </c>
+      <c r="G15" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="H15" s="8">
+        <v>0</v>
+      </c>
+      <c r="I15" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="J15" s="8">
+        <v>0</v>
+      </c>
+      <c r="K15" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="L15" s="8">
+        <v>0</v>
+      </c>
+      <c r="M15" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="N15" s="8">
+        <v>0</v>
+      </c>
+      <c r="O15" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="P15" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="Q15" s="8">
+        <v>0.25</v>
+      </c>
+      <c r="R15" s="8">
+        <v>0.25</v>
+      </c>
+      <c r="S15" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="T15" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="U15" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="V15" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="W15" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="X15" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A16" s="7">
         <v>2024103491</v>
       </c>
@@ -1555,31 +1686,31 @@
         <v>9.5</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F16" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H16" s="8">
         <v>1</v>
       </c>
       <c r="I16" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J16" s="8">
         <v>1.2</v>
       </c>
       <c r="K16" s="8" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="L16" s="8">
         <v>0.5</v>
       </c>
       <c r="M16" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="N16" s="8">
         <v>1.2</v>
@@ -1615,7 +1746,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A17" s="9">
         <v>2023100158</v>
       </c>
@@ -1629,31 +1760,31 @@
         <v>8.3999999999999986</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F17" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H17" s="8">
         <v>1</v>
       </c>
       <c r="I17" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J17" s="8">
         <v>1.2</v>
       </c>
       <c r="K17" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L17" s="8">
         <v>1</v>
       </c>
       <c r="M17" s="8" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="N17" s="8">
         <v>0.6</v>
@@ -1689,95 +1820,155 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A18" s="7">
         <v>2024101776</v>
       </c>
       <c r="B18" s="8">
         <v>0.80248366013071892</v>
       </c>
-      <c r="C18" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="D18" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="E18" s="8"/>
-      <c r="F18" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="G18" s="8"/>
-      <c r="H18" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="I18" s="8"/>
-      <c r="J18" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="K18" s="8"/>
-      <c r="L18" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="M18" s="8"/>
-      <c r="N18" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="O18" s="8"/>
-      <c r="P18" s="8"/>
-      <c r="Q18" s="8"/>
-      <c r="R18" s="8"/>
-      <c r="S18" s="8"/>
-      <c r="T18" s="8"/>
-      <c r="U18" s="8"/>
-      <c r="V18" s="8"/>
-      <c r="W18" s="8"/>
-      <c r="X18" s="8"/>
-    </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="C18" s="8">
+        <v>9.5524836601307186</v>
+      </c>
+      <c r="D18" s="8">
+        <v>8.75</v>
+      </c>
+      <c r="E18" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F18" s="8">
+        <v>0.60000000000000009</v>
+      </c>
+      <c r="G18" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H18" s="8">
+        <v>1</v>
+      </c>
+      <c r="I18" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J18" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="K18" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L18" s="8">
+        <v>1</v>
+      </c>
+      <c r="M18" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="N18" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="O18" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="P18" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="Q18" s="8">
+        <v>0.25</v>
+      </c>
+      <c r="R18" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="S18" s="8">
+        <v>0.25</v>
+      </c>
+      <c r="T18" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="U18" s="8">
+        <v>0.25</v>
+      </c>
+      <c r="V18" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="W18" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="X18" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A19" s="9">
         <v>2020102895</v>
       </c>
       <c r="B19" s="8">
         <v>0.77559912854030499</v>
       </c>
-      <c r="C19" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="D19" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="E19" s="8"/>
-      <c r="F19" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="G19" s="8"/>
-      <c r="H19" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="I19" s="8"/>
-      <c r="J19" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="K19" s="8"/>
-      <c r="L19" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="M19" s="8"/>
-      <c r="N19" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="O19" s="8"/>
-      <c r="P19" s="8"/>
-      <c r="Q19" s="8"/>
-      <c r="R19" s="8"/>
-      <c r="S19" s="8"/>
-      <c r="T19" s="8"/>
-      <c r="U19" s="8"/>
-      <c r="V19" s="8"/>
-      <c r="W19" s="8"/>
-      <c r="X19" s="8"/>
-    </row>
-    <row r="20" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="C19" s="8">
+        <v>5.1255991285403049</v>
+      </c>
+      <c r="D19" s="8">
+        <v>4.3499999999999996</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F19" s="8">
+        <v>0.60000000000000009</v>
+      </c>
+      <c r="G19" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H19" s="8">
+        <v>1</v>
+      </c>
+      <c r="I19" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="J19" s="8">
+        <v>0</v>
+      </c>
+      <c r="K19" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="L19" s="8">
+        <v>0</v>
+      </c>
+      <c r="M19" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="N19" s="8">
+        <v>0</v>
+      </c>
+      <c r="O19" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="P19" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="Q19" s="8">
+        <v>0.25</v>
+      </c>
+      <c r="R19" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="S19" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="T19" s="8">
+        <v>0.25</v>
+      </c>
+      <c r="U19" s="8">
+        <v>0.25</v>
+      </c>
+      <c r="V19" s="8">
+        <v>0</v>
+      </c>
+      <c r="W19" s="8">
+        <v>0</v>
+      </c>
+      <c r="X19" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A20" s="7">
         <v>2018104240</v>
       </c>
@@ -1791,31 +1982,31 @@
         <v>5.7</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F20" s="8">
         <v>0</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H20" s="8">
         <v>1</v>
       </c>
       <c r="I20" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J20" s="8">
         <v>1.2</v>
       </c>
       <c r="K20" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L20" s="8">
         <v>1</v>
       </c>
       <c r="M20" s="8" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="N20" s="8">
         <v>0</v>
@@ -1851,7 +2042,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A21" s="9">
         <v>2024101764</v>
       </c>
@@ -1865,31 +2056,31 @@
         <v>8.8999999999999986</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F21" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H21" s="8">
         <v>1</v>
       </c>
       <c r="I21" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J21" s="8">
         <v>1.2</v>
       </c>
       <c r="K21" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L21" s="8">
         <v>1</v>
       </c>
       <c r="M21" s="8" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="N21" s="8">
         <v>0.6</v>
@@ -1925,51 +2116,81 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="22" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A22" s="7">
         <v>2022102060</v>
       </c>
       <c r="B22" s="8">
         <v>0.21296296296296297</v>
       </c>
-      <c r="C22" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="D22" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="E22" s="8"/>
-      <c r="F22" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="G22" s="8"/>
-      <c r="H22" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="I22" s="8"/>
-      <c r="J22" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="K22" s="8"/>
-      <c r="L22" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="M22" s="8"/>
-      <c r="N22" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="O22" s="8"/>
-      <c r="P22" s="8"/>
-      <c r="Q22" s="8"/>
-      <c r="R22" s="8"/>
-      <c r="S22" s="8"/>
-      <c r="T22" s="8"/>
-      <c r="U22" s="8"/>
-      <c r="V22" s="8"/>
-      <c r="W22" s="8"/>
-      <c r="X22" s="8"/>
-    </row>
-    <row r="23" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="C22" s="8">
+        <v>1.962962962962963</v>
+      </c>
+      <c r="D22" s="8">
+        <v>1.75</v>
+      </c>
+      <c r="E22" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="F22" s="8">
+        <v>0</v>
+      </c>
+      <c r="G22" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="H22" s="8">
+        <v>0</v>
+      </c>
+      <c r="I22" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="J22" s="8">
+        <v>0</v>
+      </c>
+      <c r="K22" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="L22" s="8">
+        <v>0</v>
+      </c>
+      <c r="M22" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="N22" s="8">
+        <v>0</v>
+      </c>
+      <c r="O22" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="P22" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="Q22" s="8">
+        <v>0.25</v>
+      </c>
+      <c r="R22" s="8">
+        <v>0</v>
+      </c>
+      <c r="S22" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="T22" s="8">
+        <v>0</v>
+      </c>
+      <c r="U22" s="8">
+        <v>0</v>
+      </c>
+      <c r="V22" s="8">
+        <v>0</v>
+      </c>
+      <c r="W22" s="8">
+        <v>0</v>
+      </c>
+      <c r="X22" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A23" s="9">
         <v>2024103490</v>
       </c>
@@ -1983,31 +2204,31 @@
         <v>9.1499999999999986</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F23" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H23" s="8">
         <v>1</v>
       </c>
       <c r="I23" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J23" s="8">
         <v>1.2</v>
       </c>
       <c r="K23" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L23" s="8">
         <v>1</v>
       </c>
       <c r="M23" s="8" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="N23" s="8">
         <v>0.6</v>
@@ -2043,7 +2264,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="24" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A24" s="7">
         <v>2023100771</v>
       </c>
@@ -2057,31 +2278,31 @@
         <v>6.35</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F24" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G24" s="8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H24" s="8">
         <v>1</v>
       </c>
       <c r="I24" s="8" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J24" s="8">
         <v>0</v>
       </c>
       <c r="K24" s="8" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="L24" s="8">
         <v>0</v>
       </c>
       <c r="M24" s="8" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="N24" s="8">
         <v>0</v>
@@ -2117,51 +2338,81 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="25" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A25" s="9">
         <v>2023100962</v>
       </c>
       <c r="B25" s="8">
         <v>0.96333333333333349</v>
       </c>
-      <c r="C25" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="D25" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="E25" s="8"/>
-      <c r="F25" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="G25" s="8"/>
-      <c r="H25" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="I25" s="8"/>
-      <c r="J25" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="K25" s="8"/>
-      <c r="L25" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="M25" s="8"/>
-      <c r="N25" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="O25" s="8"/>
-      <c r="P25" s="8"/>
-      <c r="Q25" s="8"/>
-      <c r="R25" s="8"/>
-      <c r="S25" s="8"/>
-      <c r="T25" s="8"/>
-      <c r="U25" s="8"/>
-      <c r="V25" s="8"/>
-      <c r="W25" s="8"/>
-      <c r="X25" s="8"/>
-    </row>
-    <row r="26" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="C25" s="8">
+        <v>7.2633333333333336</v>
+      </c>
+      <c r="D25" s="8">
+        <v>6.3000000000000007</v>
+      </c>
+      <c r="E25" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F25" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="G25" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="H25" s="8">
+        <v>0.60000000000000009</v>
+      </c>
+      <c r="I25" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J25" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="K25" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L25" s="8">
+        <v>1</v>
+      </c>
+      <c r="M25" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="N25" s="8">
+        <v>0.6</v>
+      </c>
+      <c r="O25" s="8">
+        <v>0</v>
+      </c>
+      <c r="P25" s="8">
+        <v>0.25</v>
+      </c>
+      <c r="Q25" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="R25" s="8">
+        <v>0</v>
+      </c>
+      <c r="S25" s="8">
+        <v>0</v>
+      </c>
+      <c r="T25" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="U25" s="8">
+        <v>0.25</v>
+      </c>
+      <c r="V25" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="W25" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="X25" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A26" s="7">
         <v>2021101361</v>
       </c>
@@ -2175,31 +2426,31 @@
         <v>7.3</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F26" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G26" s="8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H26" s="8">
         <v>1</v>
       </c>
       <c r="I26" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J26" s="8">
         <v>1.2</v>
       </c>
       <c r="K26" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L26" s="8">
         <v>1</v>
       </c>
       <c r="M26" s="8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="N26" s="8">
         <v>0</v>
@@ -2235,7 +2486,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A27" s="9">
         <v>2023201341</v>
       </c>
@@ -2249,31 +2500,31 @@
         <v>8.65</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F27" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G27" s="8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H27" s="8">
         <v>1</v>
       </c>
       <c r="I27" s="8" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J27" s="8">
         <v>0.6</v>
       </c>
       <c r="K27" s="8" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="L27" s="8">
         <v>0.5</v>
       </c>
       <c r="M27" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="N27" s="8">
         <v>1.2</v>
@@ -2309,7 +2560,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="28" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A28" s="7">
         <v>2023101463</v>
       </c>
@@ -2323,31 +2574,31 @@
         <v>6.5500000000000007</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F28" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G28" s="8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H28" s="8">
         <v>1</v>
       </c>
       <c r="I28" s="8" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J28" s="8">
         <v>0.6</v>
       </c>
       <c r="K28" s="8" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="L28" s="8">
         <v>0.5</v>
       </c>
       <c r="M28" s="8" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="N28" s="8">
         <v>0.6</v>
@@ -2383,7 +2634,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A29" s="9">
         <v>2022201037</v>
       </c>
@@ -2397,31 +2648,31 @@
         <v>9.25</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F29" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G29" s="8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H29" s="8">
         <v>1</v>
       </c>
       <c r="I29" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J29" s="8">
         <v>1.2</v>
       </c>
       <c r="K29" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L29" s="8">
         <v>1</v>
       </c>
       <c r="M29" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="N29" s="8">
         <v>1.2</v>
@@ -2457,7 +2708,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="30" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A30" s="7">
         <v>2021101896</v>
       </c>
@@ -2471,31 +2722,31 @@
         <v>10</v>
       </c>
       <c r="E30" s="8" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F30" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G30" s="8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H30" s="8">
         <v>1</v>
       </c>
       <c r="I30" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J30" s="8">
         <v>1.2</v>
       </c>
       <c r="K30" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L30" s="8">
         <v>1</v>
       </c>
       <c r="M30" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="N30" s="8">
         <v>1.2</v>
@@ -2531,51 +2782,81 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="31" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A31" s="9">
         <v>2022201042</v>
       </c>
       <c r="B31" s="8">
         <v>0.92555555555555569</v>
       </c>
-      <c r="C31" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="D31" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="E31" s="8"/>
-      <c r="F31" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="G31" s="8"/>
-      <c r="H31" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="I31" s="8"/>
-      <c r="J31" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="K31" s="8"/>
-      <c r="L31" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="M31" s="8"/>
-      <c r="N31" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="O31" s="8"/>
-      <c r="P31" s="8"/>
-      <c r="Q31" s="8"/>
-      <c r="R31" s="8"/>
-      <c r="S31" s="8"/>
-      <c r="T31" s="8"/>
-      <c r="U31" s="8"/>
-      <c r="V31" s="8"/>
-      <c r="W31" s="8"/>
-      <c r="X31" s="8"/>
-    </row>
-    <row r="32" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="C31" s="8">
+        <v>10.175555555555556</v>
+      </c>
+      <c r="D31" s="8">
+        <v>9.25</v>
+      </c>
+      <c r="E31" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F31" s="8">
+        <v>0.60000000000000009</v>
+      </c>
+      <c r="G31" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H31" s="8">
+        <v>1</v>
+      </c>
+      <c r="I31" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J31" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="K31" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L31" s="8">
+        <v>1</v>
+      </c>
+      <c r="M31" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="N31" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="O31" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="P31" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="Q31" s="8">
+        <v>0.25</v>
+      </c>
+      <c r="R31" s="8">
+        <v>0.25</v>
+      </c>
+      <c r="S31" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="T31" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="U31" s="8">
+        <v>0.25</v>
+      </c>
+      <c r="V31" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="W31" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="X31" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A32" s="7">
         <v>2020102888</v>
       </c>
@@ -2589,31 +2870,31 @@
         <v>7.95</v>
       </c>
       <c r="E32" s="8" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F32" s="8">
         <v>0.2</v>
       </c>
       <c r="G32" s="8" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H32" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="I32" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J32" s="8">
         <v>1.2</v>
       </c>
       <c r="K32" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L32" s="8">
         <v>1</v>
       </c>
       <c r="M32" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="N32" s="8">
         <v>1.2</v>
@@ -2649,7 +2930,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A33" s="9">
         <v>2024101765</v>
       </c>
@@ -2663,31 +2944,31 @@
         <v>8.3000000000000007</v>
       </c>
       <c r="E33" s="8" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F33" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G33" s="8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H33" s="8">
         <v>1</v>
       </c>
       <c r="I33" s="8" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J33" s="8">
         <v>0.6</v>
       </c>
       <c r="K33" s="8" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="L33" s="8">
         <v>0.5</v>
       </c>
       <c r="M33" s="8" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="N33" s="8">
         <v>0.6</v>
@@ -2723,95 +3004,155 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="34" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A34" s="7">
         <v>2022100612</v>
       </c>
       <c r="B34" s="8">
         <v>0.533834422657952</v>
       </c>
-      <c r="C34" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="D34" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="E34" s="8"/>
-      <c r="F34" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="G34" s="8"/>
-      <c r="H34" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="I34" s="8"/>
-      <c r="J34" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="K34" s="8"/>
-      <c r="L34" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="M34" s="8"/>
-      <c r="N34" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="O34" s="8"/>
-      <c r="P34" s="8"/>
-      <c r="Q34" s="8"/>
-      <c r="R34" s="8"/>
-      <c r="S34" s="8"/>
-      <c r="T34" s="8"/>
-      <c r="U34" s="8"/>
-      <c r="V34" s="8"/>
-      <c r="W34" s="8"/>
-      <c r="X34" s="8"/>
-    </row>
-    <row r="35" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="C34" s="8">
+        <v>9.5338344226579519</v>
+      </c>
+      <c r="D34" s="8">
+        <v>9</v>
+      </c>
+      <c r="E34" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F34" s="8">
+        <v>0.60000000000000009</v>
+      </c>
+      <c r="G34" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="H34" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="I34" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J34" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="K34" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L34" s="8">
+        <v>1</v>
+      </c>
+      <c r="M34" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="N34" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="O34" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="P34" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="Q34" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="R34" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="S34" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="T34" s="8">
+        <v>0.25</v>
+      </c>
+      <c r="U34" s="8">
+        <v>0.25</v>
+      </c>
+      <c r="V34" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="W34" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="X34" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A35" s="9">
         <v>2023101467</v>
       </c>
       <c r="B35" s="8">
         <v>0.75816993464052285</v>
       </c>
-      <c r="C35" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="D35" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="E35" s="8"/>
-      <c r="F35" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="G35" s="8"/>
-      <c r="H35" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="I35" s="8"/>
-      <c r="J35" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="K35" s="8"/>
-      <c r="L35" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="M35" s="8"/>
-      <c r="N35" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="O35" s="8"/>
-      <c r="P35" s="8"/>
-      <c r="Q35" s="8"/>
-      <c r="R35" s="8"/>
-      <c r="S35" s="8"/>
-      <c r="T35" s="8"/>
-      <c r="U35" s="8"/>
-      <c r="V35" s="8"/>
-      <c r="W35" s="8"/>
-      <c r="X35" s="8"/>
-    </row>
-    <row r="36" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="C35" s="8">
+        <v>8.0581699346405227</v>
+      </c>
+      <c r="D35" s="8">
+        <v>7.3</v>
+      </c>
+      <c r="E35" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F35" s="8">
+        <v>0.60000000000000009</v>
+      </c>
+      <c r="G35" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="H35" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="I35" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="J35" s="8">
+        <v>0</v>
+      </c>
+      <c r="K35" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="L35" s="8">
+        <v>0</v>
+      </c>
+      <c r="M35" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="N35" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="O35" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="P35" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="Q35" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="R35" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="S35" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="T35" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="U35" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="V35" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="W35" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="X35" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="36" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A36" s="7">
         <v>2022100511</v>
       </c>
@@ -2825,31 +3166,31 @@
         <v>6.35</v>
       </c>
       <c r="E36" s="8" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F36" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G36" s="8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H36" s="8">
         <v>1</v>
       </c>
       <c r="I36" s="8" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J36" s="8">
         <v>0</v>
       </c>
       <c r="K36" s="8" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="L36" s="8">
         <v>0</v>
       </c>
       <c r="M36" s="8" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N36" s="8">
         <v>0</v>
@@ -2885,7 +3226,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="37" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A37" s="9">
         <v>2023200147</v>
       </c>
@@ -2899,31 +3240,31 @@
         <v>10</v>
       </c>
       <c r="E37" s="8" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F37" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G37" s="8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H37" s="8">
         <v>1</v>
       </c>
       <c r="I37" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J37" s="8">
         <v>1.2</v>
       </c>
       <c r="K37" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L37" s="8">
         <v>1</v>
       </c>
       <c r="M37" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="N37" s="8">
         <v>1.2</v>
@@ -2959,7 +3300,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="38" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A38" s="7">
         <v>2023100776</v>
       </c>
@@ -2973,31 +3314,31 @@
         <v>9.5</v>
       </c>
       <c r="E38" s="8" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F38" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G38" s="8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H38" s="8">
         <v>1</v>
       </c>
       <c r="I38" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J38" s="8">
         <v>1.2</v>
       </c>
       <c r="K38" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L38" s="8">
         <v>1</v>
       </c>
       <c r="M38" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="N38" s="8">
         <v>1.2</v>
@@ -3033,7 +3374,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="39" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A39" s="9">
         <v>2024101158</v>
       </c>
@@ -3047,31 +3388,31 @@
         <v>10</v>
       </c>
       <c r="E39" s="8" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F39" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G39" s="8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H39" s="8">
         <v>1</v>
       </c>
       <c r="I39" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J39" s="8">
         <v>1.2</v>
       </c>
       <c r="K39" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L39" s="8">
         <v>1</v>
       </c>
       <c r="M39" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="N39" s="8">
         <v>1.2</v>
@@ -3107,7 +3448,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="40" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A40" s="7">
         <v>2024101773</v>
       </c>
@@ -3121,31 +3462,31 @@
         <v>9.75</v>
       </c>
       <c r="E40" s="8" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F40" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G40" s="8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H40" s="8">
         <v>1</v>
       </c>
       <c r="I40" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J40" s="8">
         <v>1.2</v>
       </c>
       <c r="K40" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L40" s="8">
         <v>1</v>
       </c>
       <c r="M40" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="N40" s="8">
         <v>1.2</v>
@@ -3181,95 +3522,155 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="41" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A41" s="9">
         <v>2023100068</v>
       </c>
       <c r="B41" s="8">
         <v>0.32407407407407407</v>
       </c>
-      <c r="C41" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="D41" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="E41" s="8"/>
-      <c r="F41" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="G41" s="8"/>
-      <c r="H41" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="I41" s="8"/>
-      <c r="J41" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="K41" s="8"/>
-      <c r="L41" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="M41" s="8"/>
-      <c r="N41" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="O41" s="8"/>
-      <c r="P41" s="8"/>
-      <c r="Q41" s="8"/>
-      <c r="R41" s="8"/>
-      <c r="S41" s="8"/>
-      <c r="T41" s="8"/>
-      <c r="U41" s="8"/>
-      <c r="V41" s="8"/>
-      <c r="W41" s="8"/>
-      <c r="X41" s="8"/>
-    </row>
-    <row r="42" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="C41" s="8">
+        <v>8.924074074074074</v>
+      </c>
+      <c r="D41" s="8">
+        <v>8.6000000000000014</v>
+      </c>
+      <c r="E41" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F41" s="8">
+        <v>0.60000000000000009</v>
+      </c>
+      <c r="G41" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="H41" s="8">
+        <v>0.70000000000000007</v>
+      </c>
+      <c r="I41" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="J41" s="8">
+        <v>0.6</v>
+      </c>
+      <c r="K41" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="L41" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M41" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="N41" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="O41" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="P41" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="Q41" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="R41" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="S41" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="T41" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="U41" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="V41" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="W41" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="X41" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="42" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A42" s="7">
         <v>2023200790</v>
       </c>
       <c r="B42" s="8">
         <v>0.85222222222222221</v>
       </c>
-      <c r="C42" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="D42" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="E42" s="8"/>
-      <c r="F42" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="G42" s="8"/>
-      <c r="H42" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="I42" s="8"/>
-      <c r="J42" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="K42" s="8"/>
-      <c r="L42" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="M42" s="8"/>
-      <c r="N42" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="O42" s="8"/>
-      <c r="P42" s="8"/>
-      <c r="Q42" s="8"/>
-      <c r="R42" s="8"/>
-      <c r="S42" s="8"/>
-      <c r="T42" s="8"/>
-      <c r="U42" s="8"/>
-      <c r="V42" s="8"/>
-      <c r="W42" s="8"/>
-      <c r="X42" s="8"/>
-    </row>
-    <row r="43" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="C42" s="8">
+        <v>6.2522222222222217</v>
+      </c>
+      <c r="D42" s="8">
+        <v>5.3999999999999995</v>
+      </c>
+      <c r="E42" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F42" s="8">
+        <v>0.60000000000000009</v>
+      </c>
+      <c r="G42" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H42" s="8">
+        <v>1</v>
+      </c>
+      <c r="I42" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J42" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="K42" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L42" s="8">
+        <v>1</v>
+      </c>
+      <c r="M42" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="N42" s="8">
+        <v>0.6</v>
+      </c>
+      <c r="O42" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="P42" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="Q42" s="8">
+        <v>0</v>
+      </c>
+      <c r="R42" s="8">
+        <v>0</v>
+      </c>
+      <c r="S42" s="8">
+        <v>0</v>
+      </c>
+      <c r="T42" s="8">
+        <v>0</v>
+      </c>
+      <c r="U42" s="8">
+        <v>0</v>
+      </c>
+      <c r="V42" s="8">
+        <v>0</v>
+      </c>
+      <c r="W42" s="8">
+        <v>0</v>
+      </c>
+      <c r="X42" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A43" s="9">
         <v>2022200719</v>
       </c>
@@ -3283,31 +3684,31 @@
         <v>9.75</v>
       </c>
       <c r="E43" s="8" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F43" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G43" s="8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H43" s="8">
         <v>1</v>
       </c>
       <c r="I43" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J43" s="8">
         <v>1.2</v>
       </c>
       <c r="K43" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L43" s="8">
         <v>1</v>
       </c>
       <c r="M43" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="N43" s="8">
         <v>1.2</v>
@@ -3343,7 +3744,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="44" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A44" s="8">
         <v>2025201178</v>
       </c>
@@ -3357,31 +3758,31 @@
         <v>6.05</v>
       </c>
       <c r="E44" s="8" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F44" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G44" s="8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H44" s="8">
         <v>1</v>
       </c>
       <c r="I44" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J44" s="8">
         <v>1.2</v>
       </c>
       <c r="K44" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L44" s="8">
         <v>1</v>
       </c>
       <c r="M44" s="8" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="N44" s="8">
         <v>0</v>
@@ -3417,7 +3818,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A45" s="9">
         <v>2024101775</v>
       </c>
@@ -3431,31 +3832,31 @@
         <v>9.1499999999999986</v>
       </c>
       <c r="E45" s="8" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F45" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G45" s="8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H45" s="8">
         <v>1</v>
       </c>
       <c r="I45" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J45" s="8">
         <v>1.2</v>
       </c>
       <c r="K45" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L45" s="8">
         <v>1</v>
       </c>
       <c r="M45" s="8" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="N45" s="8">
         <v>0.6</v>
@@ -3491,7 +3892,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="46" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A46" s="7">
         <v>2024103187</v>
       </c>
@@ -3505,31 +3906,31 @@
         <v>7.9</v>
       </c>
       <c r="E46" s="8" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F46" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G46" s="8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H46" s="8">
         <v>1</v>
       </c>
       <c r="I46" s="8" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J46" s="8">
         <v>0.6</v>
       </c>
       <c r="K46" s="8" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="L46" s="8">
         <v>0.5</v>
       </c>
       <c r="M46" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="N46" s="8">
         <v>1.2</v>
@@ -3565,7 +3966,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="47" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A47" s="9">
         <v>2023102386</v>
       </c>
@@ -3579,31 +3980,31 @@
         <v>9</v>
       </c>
       <c r="E47" s="8" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F47" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G47" s="8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H47" s="8">
         <v>1</v>
       </c>
       <c r="I47" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J47" s="8">
         <v>1.2</v>
       </c>
       <c r="K47" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L47" s="8">
         <v>1</v>
       </c>
       <c r="M47" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="N47" s="8">
         <v>1.2</v>
@@ -3639,51 +4040,81 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="48" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A48" s="7">
         <v>2020101654</v>
       </c>
       <c r="B48" s="8">
         <v>0.22222222222222221</v>
       </c>
-      <c r="C48" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="D48" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="E48" s="8"/>
-      <c r="F48" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="G48" s="8"/>
-      <c r="H48" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="I48" s="8"/>
-      <c r="J48" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="K48" s="8"/>
-      <c r="L48" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="M48" s="8"/>
-      <c r="N48" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="O48" s="8"/>
-      <c r="P48" s="8"/>
-      <c r="Q48" s="8"/>
-      <c r="R48" s="8"/>
-      <c r="S48" s="8"/>
-      <c r="T48" s="8"/>
-      <c r="U48" s="8"/>
-      <c r="V48" s="8"/>
-      <c r="W48" s="8"/>
-      <c r="X48" s="8"/>
-    </row>
-    <row r="49" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="C48" s="8">
+        <v>8.1222222222222236</v>
+      </c>
+      <c r="D48" s="8">
+        <v>7.9</v>
+      </c>
+      <c r="E48" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F48" s="8">
+        <v>0.60000000000000009</v>
+      </c>
+      <c r="G48" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="H48" s="8">
+        <v>0.60000000000000009</v>
+      </c>
+      <c r="I48" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="J48" s="8">
+        <v>0.6</v>
+      </c>
+      <c r="K48" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="L48" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M48" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="N48" s="8">
+        <v>0.6</v>
+      </c>
+      <c r="O48" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="P48" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="Q48" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="R48" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="S48" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="T48" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="U48" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="V48" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="W48" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="X48" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="49" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A49" s="9">
         <v>2022201082</v>
       </c>
@@ -3697,31 +4128,31 @@
         <v>9.65</v>
       </c>
       <c r="E49" s="8" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F49" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G49" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H49" s="8">
         <v>0.9</v>
       </c>
       <c r="I49" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J49" s="8">
         <v>1.2</v>
       </c>
       <c r="K49" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L49" s="8">
         <v>1</v>
       </c>
       <c r="M49" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="N49" s="8">
         <v>1.2</v>
@@ -3757,7 +4188,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="50" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A50" s="7">
         <v>2024101769</v>
       </c>
@@ -3771,31 +4202,31 @@
         <v>8.8999999999999986</v>
       </c>
       <c r="E50" s="8" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F50" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G50" s="8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H50" s="8">
         <v>1</v>
       </c>
       <c r="I50" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J50" s="8">
         <v>1.2</v>
       </c>
       <c r="K50" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L50" s="8">
         <v>1</v>
       </c>
       <c r="M50" s="8" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="N50" s="8">
         <v>0.6</v>
@@ -3831,7 +4262,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="51" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A51" s="9">
         <v>2024101154</v>
       </c>
@@ -3845,31 +4276,31 @@
         <v>8.0500000000000007</v>
       </c>
       <c r="E51" s="8" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F51" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G51" s="8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H51" s="8">
         <v>1</v>
       </c>
       <c r="I51" s="8" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J51" s="8">
         <v>0.6</v>
       </c>
       <c r="K51" s="8" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="L51" s="8">
         <v>0.5</v>
       </c>
       <c r="M51" s="8" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="N51" s="8">
         <v>0.6</v>
@@ -3905,7 +4336,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="52" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A52" s="7">
         <v>2022102045</v>
       </c>
@@ -3919,31 +4350,31 @@
         <v>7.8000000000000007</v>
       </c>
       <c r="E52" s="8" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F52" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G52" s="8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H52" s="8">
         <v>1</v>
       </c>
       <c r="I52" s="8" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J52" s="8">
         <v>0.6</v>
       </c>
       <c r="K52" s="8" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="L52" s="8">
         <v>0.5</v>
       </c>
       <c r="M52" s="8" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="N52" s="8">
         <v>0.6</v>
@@ -3979,7 +4410,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="53" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A53" s="9">
         <v>2023101690</v>
       </c>
@@ -3993,31 +4424,31 @@
         <v>8.75</v>
       </c>
       <c r="E53" s="8" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F53" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G53" s="8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H53" s="8">
         <v>1</v>
       </c>
       <c r="I53" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J53" s="8">
         <v>1.2</v>
       </c>
       <c r="K53" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L53" s="8">
         <v>1</v>
       </c>
       <c r="M53" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="N53" s="8">
         <v>1.2</v>
@@ -4053,51 +4484,81 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="54" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A54" s="7">
         <v>2023100954</v>
       </c>
       <c r="B54" s="8">
         <v>0.32407407407407407</v>
       </c>
-      <c r="C54" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="D54" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="E54" s="8"/>
-      <c r="F54" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="G54" s="8"/>
-      <c r="H54" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="I54" s="8"/>
-      <c r="J54" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="K54" s="8"/>
-      <c r="L54" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="M54" s="8"/>
-      <c r="N54" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="O54" s="8"/>
-      <c r="P54" s="8"/>
-      <c r="Q54" s="8"/>
-      <c r="R54" s="8"/>
-      <c r="S54" s="8"/>
-      <c r="T54" s="8"/>
-      <c r="U54" s="8"/>
-      <c r="V54" s="8"/>
-      <c r="W54" s="8"/>
-      <c r="X54" s="8"/>
-    </row>
-    <row r="55" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="C54" s="8">
+        <v>8.7240740740740748</v>
+      </c>
+      <c r="D54" s="8">
+        <v>8.3999999999999986</v>
+      </c>
+      <c r="E54" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F54" s="8">
+        <v>0.60000000000000009</v>
+      </c>
+      <c r="G54" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H54" s="8">
+        <v>1</v>
+      </c>
+      <c r="I54" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J54" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="K54" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L54" s="8">
+        <v>1</v>
+      </c>
+      <c r="M54" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="N54" s="8">
+        <v>0.6</v>
+      </c>
+      <c r="O54" s="8">
+        <v>0</v>
+      </c>
+      <c r="P54" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="Q54" s="8">
+        <v>0.25</v>
+      </c>
+      <c r="R54" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="S54" s="8">
+        <v>0.25</v>
+      </c>
+      <c r="T54" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="U54" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="V54" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="W54" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="X54" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="55" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A55" s="9">
         <v>2024202997</v>
       </c>
@@ -4111,31 +4572,31 @@
         <v>7.65</v>
       </c>
       <c r="E55" s="8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F55" s="8">
         <v>0</v>
       </c>
       <c r="G55" s="8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H55" s="8">
         <v>1</v>
       </c>
       <c r="I55" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J55" s="8">
         <v>1.2</v>
       </c>
       <c r="K55" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L55" s="8">
         <v>1</v>
       </c>
       <c r="M55" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="N55" s="8">
         <v>1.2</v>
@@ -4171,95 +4632,155 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A56" s="7">
         <v>2020101573</v>
       </c>
       <c r="B56" s="8">
         <v>0.43333333333333329</v>
       </c>
-      <c r="C56" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="D56" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="E56" s="8"/>
-      <c r="F56" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="G56" s="8"/>
-      <c r="H56" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="I56" s="8"/>
-      <c r="J56" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="K56" s="8"/>
-      <c r="L56" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="M56" s="8"/>
-      <c r="N56" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="O56" s="8"/>
-      <c r="P56" s="8"/>
-      <c r="Q56" s="8"/>
-      <c r="R56" s="8"/>
-      <c r="S56" s="8"/>
-      <c r="T56" s="8"/>
-      <c r="U56" s="8"/>
-      <c r="V56" s="8"/>
-      <c r="W56" s="8"/>
-      <c r="X56" s="8"/>
-    </row>
-    <row r="57" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="C56" s="8">
+        <v>5.0333333333333332</v>
+      </c>
+      <c r="D56" s="8">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="E56" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F56" s="8">
+        <v>0.4</v>
+      </c>
+      <c r="G56" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H56" s="8">
+        <v>1</v>
+      </c>
+      <c r="I56" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="J56" s="8">
+        <v>0.6</v>
+      </c>
+      <c r="K56" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="L56" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M56" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="N56" s="8">
+        <v>0.6</v>
+      </c>
+      <c r="O56" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="P56" s="8">
+        <v>0.25</v>
+      </c>
+      <c r="Q56" s="8">
+        <v>0</v>
+      </c>
+      <c r="R56" s="8">
+        <v>0</v>
+      </c>
+      <c r="S56" s="8">
+        <v>0.25</v>
+      </c>
+      <c r="T56" s="8">
+        <v>0.25</v>
+      </c>
+      <c r="U56" s="8">
+        <v>0.25</v>
+      </c>
+      <c r="V56" s="8">
+        <v>0</v>
+      </c>
+      <c r="W56" s="8">
+        <v>0</v>
+      </c>
+      <c r="X56" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A57" s="9">
         <v>2024101785</v>
       </c>
       <c r="B57" s="8">
         <v>0.69679738562091498</v>
       </c>
-      <c r="C57" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="D57" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="E57" s="8"/>
-      <c r="F57" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="G57" s="8"/>
-      <c r="H57" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="I57" s="8"/>
-      <c r="J57" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="K57" s="8"/>
-      <c r="L57" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="M57" s="8"/>
-      <c r="N57" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="O57" s="8"/>
-      <c r="P57" s="8"/>
-      <c r="Q57" s="8"/>
-      <c r="R57" s="8"/>
-      <c r="S57" s="8"/>
-      <c r="T57" s="8"/>
-      <c r="U57" s="8"/>
-      <c r="V57" s="8"/>
-      <c r="W57" s="8"/>
-      <c r="X57" s="8"/>
-    </row>
-    <row r="58" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="C57" s="8">
+        <v>10.446797385620915</v>
+      </c>
+      <c r="D57" s="8">
+        <v>9.75</v>
+      </c>
+      <c r="E57" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F57" s="8">
+        <v>0.60000000000000009</v>
+      </c>
+      <c r="G57" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H57" s="8">
+        <v>1</v>
+      </c>
+      <c r="I57" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J57" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="K57" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L57" s="8">
+        <v>1</v>
+      </c>
+      <c r="M57" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="N57" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="O57" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="P57" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="Q57" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="R57" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="S57" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="T57" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="U57" s="8">
+        <v>0.25</v>
+      </c>
+      <c r="V57" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="W57" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="X57" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="58" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A58" s="7">
         <v>2021201017</v>
       </c>
@@ -4273,31 +4794,31 @@
         <v>7.05</v>
       </c>
       <c r="E58" s="8" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F58" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G58" s="8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H58" s="8">
         <v>1</v>
       </c>
       <c r="I58" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J58" s="8">
         <v>1.2</v>
       </c>
       <c r="K58" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L58" s="8">
         <v>1</v>
       </c>
       <c r="M58" s="8" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="N58" s="8">
         <v>0</v>
@@ -4333,95 +4854,155 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="59" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A59" s="9">
         <v>2023101691</v>
       </c>
       <c r="B59" s="8">
         <v>0.62575163398692812</v>
       </c>
-      <c r="C59" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="D59" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="E59" s="8"/>
-      <c r="F59" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="G59" s="8"/>
-      <c r="H59" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="I59" s="8"/>
-      <c r="J59" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="K59" s="8"/>
-      <c r="L59" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="M59" s="8"/>
-      <c r="N59" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="O59" s="8"/>
-      <c r="P59" s="8"/>
-      <c r="Q59" s="8"/>
-      <c r="R59" s="8"/>
-      <c r="S59" s="8"/>
-      <c r="T59" s="8"/>
-      <c r="U59" s="8"/>
-      <c r="V59" s="8"/>
-      <c r="W59" s="8"/>
-      <c r="X59" s="8"/>
-    </row>
-    <row r="60" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="C59" s="8">
+        <v>9.875751633986928</v>
+      </c>
+      <c r="D59" s="8">
+        <v>9.25</v>
+      </c>
+      <c r="E59" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F59" s="8">
+        <v>0.60000000000000009</v>
+      </c>
+      <c r="G59" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H59" s="8">
+        <v>1</v>
+      </c>
+      <c r="I59" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J59" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="K59" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L59" s="8">
+        <v>1</v>
+      </c>
+      <c r="M59" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="N59" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="O59" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="P59" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="Q59" s="8">
+        <v>0.25</v>
+      </c>
+      <c r="R59" s="8">
+        <v>0.25</v>
+      </c>
+      <c r="S59" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="T59" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="U59" s="8">
+        <v>0.25</v>
+      </c>
+      <c r="V59" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="W59" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="X59" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="60" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A60" s="7">
         <v>2024101770</v>
       </c>
       <c r="B60" s="8">
         <v>0.94481481481481489</v>
       </c>
-      <c r="C60" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="D60" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="E60" s="8"/>
-      <c r="F60" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="G60" s="8"/>
-      <c r="H60" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="I60" s="8"/>
-      <c r="J60" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="K60" s="8"/>
-      <c r="L60" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="M60" s="8"/>
-      <c r="N60" s="8" t="e">
-        <v>#VALUE!</v>
-      </c>
-      <c r="O60" s="8"/>
-      <c r="P60" s="8"/>
-      <c r="Q60" s="8"/>
-      <c r="R60" s="8"/>
-      <c r="S60" s="8"/>
-      <c r="T60" s="8"/>
-      <c r="U60" s="8"/>
-      <c r="V60" s="8"/>
-      <c r="W60" s="8"/>
-      <c r="X60" s="8"/>
-    </row>
-    <row r="61" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="C60" s="8">
+        <v>10.694814814814816</v>
+      </c>
+      <c r="D60" s="8">
+        <v>9.75</v>
+      </c>
+      <c r="E60" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F60" s="8">
+        <v>0.60000000000000009</v>
+      </c>
+      <c r="G60" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H60" s="8">
+        <v>1</v>
+      </c>
+      <c r="I60" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J60" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="K60" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L60" s="8">
+        <v>1</v>
+      </c>
+      <c r="M60" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="N60" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="O60" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="P60" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="Q60" s="8">
+        <v>0.25</v>
+      </c>
+      <c r="R60" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="S60" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="T60" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="U60" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="V60" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="W60" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="X60" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="61" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A61" s="9">
         <v>2022200727</v>
       </c>
@@ -4435,31 +5016,31 @@
         <v>9.5</v>
       </c>
       <c r="E61" s="8" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F61" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G61" s="8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H61" s="8">
         <v>1</v>
       </c>
       <c r="I61" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J61" s="8">
         <v>1.2</v>
       </c>
       <c r="K61" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L61" s="8">
         <v>1</v>
       </c>
       <c r="M61" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="N61" s="8">
         <v>1.2</v>
@@ -4495,7 +5076,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="62" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A62" s="7">
         <v>2023101729</v>
       </c>
@@ -4509,31 +5090,31 @@
         <v>6.05</v>
       </c>
       <c r="E62" s="8" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F62" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G62" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H62" s="8">
         <v>0.9</v>
       </c>
       <c r="I62" s="8" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J62" s="8">
         <v>0.6</v>
       </c>
       <c r="K62" s="8" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="L62" s="8">
         <v>0.5</v>
       </c>
       <c r="M62" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="N62" s="8">
         <v>1.2</v>
@@ -4569,7 +5150,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A63" s="9">
         <v>2023100965</v>
       </c>
@@ -4583,31 +5164,31 @@
         <v>6.6499999999999995</v>
       </c>
       <c r="E63" s="8" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F63" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G63" s="8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H63" s="8">
         <v>1</v>
       </c>
       <c r="I63" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J63" s="8">
         <v>1.2</v>
       </c>
       <c r="K63" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L63" s="8">
         <v>1</v>
       </c>
       <c r="M63" s="8" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="N63" s="8">
         <v>0.6</v>
@@ -4643,7 +5224,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A64" s="7">
         <v>2024101155</v>
       </c>
@@ -4657,31 +5238,31 @@
         <v>8.8999999999999986</v>
       </c>
       <c r="E64" s="8" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F64" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G64" s="8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H64" s="8">
         <v>1</v>
       </c>
       <c r="I64" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J64" s="8">
         <v>1.2</v>
       </c>
       <c r="K64" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L64" s="8">
         <v>1</v>
       </c>
       <c r="M64" s="8" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="N64" s="8">
         <v>0.6</v>
@@ -4717,7 +5298,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="65" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A65" s="9">
         <v>2023200064</v>
       </c>
@@ -4731,31 +5312,31 @@
         <v>9.5</v>
       </c>
       <c r="E65" s="8" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F65" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G65" s="8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H65" s="8">
         <v>1</v>
       </c>
       <c r="I65" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J65" s="8">
         <v>1.2</v>
       </c>
       <c r="K65" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L65" s="8">
         <v>1</v>
       </c>
       <c r="M65" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="N65" s="8">
         <v>1.2</v>

--- a/notas.xlsx
+++ b/notas.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11109"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuário\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/daniloas.com/projetos/FertilidadeSoloAlegreUFES/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AF233E4-7BB1-4179-830E-6CD66077B15C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8378485E-6BC2-DC43-8592-8770D726C9EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11310" xr2:uid="{BB9E0E1E-73DF-4AB6-A949-07A69840CAF7}"/>
+    <workbookView xWindow="0" yWindow="620" windowWidth="20740" windowHeight="11320" xr2:uid="{BB9E0E1E-73DF-4AB6-A949-07A69840CAF7}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -582,17 +582,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCC50A17-1BAD-4261-9C73-1273FB998B6D}">
   <dimension ref="A1:X65"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.28515625" customWidth="1"/>
+    <col min="2" max="2" width="16.33203125" customWidth="1"/>
     <col min="3" max="3" width="17" customWidth="1"/>
-    <col min="4" max="4" width="26.5703125" customWidth="1"/>
+    <col min="4" max="4" width="26.5" customWidth="1"/>
     <col min="5" max="5" width="7" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:24" ht="33" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -666,7 +666,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A2" s="7">
         <v>2023200939</v>
       </c>
@@ -740,7 +740,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A3" s="9">
         <v>2023100005</v>
       </c>
@@ -814,7 +814,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A4" s="7">
         <v>2021101895</v>
       </c>
@@ -888,7 +888,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="9">
         <v>2024101156</v>
       </c>
@@ -962,7 +962,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A6" s="7">
         <v>2023200783</v>
       </c>
@@ -1036,7 +1036,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A7" s="9">
         <v>2022200360</v>
       </c>
@@ -1110,7 +1110,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A8" s="7">
         <v>2024101774</v>
       </c>
@@ -1184,7 +1184,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A9" s="9">
         <v>2024203414</v>
       </c>
@@ -1258,7 +1258,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A10" s="7">
         <v>2023101046</v>
       </c>
@@ -1332,7 +1332,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A11" s="9">
         <v>2019109848</v>
       </c>
@@ -1376,7 +1376,7 @@
       <c r="W11" s="8"/>
       <c r="X11" s="8"/>
     </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A12" s="7">
         <v>2023102012</v>
       </c>
@@ -1450,7 +1450,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A13" s="9">
         <v>2024101768</v>
       </c>
@@ -1524,7 +1524,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A14" s="7">
         <v>2018104222</v>
       </c>
@@ -1598,7 +1598,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A15" s="9">
         <v>2017102706</v>
       </c>
@@ -1672,7 +1672,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A16" s="7">
         <v>2024103491</v>
       </c>
@@ -1746,7 +1746,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A17" s="9">
         <v>2023100158</v>
       </c>
@@ -1820,7 +1820,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A18" s="7">
         <v>2024101776</v>
       </c>
@@ -1894,7 +1894,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A19" s="9">
         <v>2020102895</v>
       </c>
@@ -1968,7 +1968,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A20" s="7">
         <v>2018104240</v>
       </c>
@@ -2042,7 +2042,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A21" s="9">
         <v>2024101764</v>
       </c>
@@ -2116,7 +2116,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="22" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A22" s="7">
         <v>2022102060</v>
       </c>
@@ -2190,7 +2190,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A23" s="9">
         <v>2024103490</v>
       </c>
@@ -2264,7 +2264,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="24" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A24" s="7">
         <v>2023100771</v>
       </c>
@@ -2338,7 +2338,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="25" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A25" s="9">
         <v>2023100962</v>
       </c>
@@ -2412,7 +2412,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A26" s="7">
         <v>2021101361</v>
       </c>
@@ -2486,7 +2486,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A27" s="9">
         <v>2023201341</v>
       </c>
@@ -2560,7 +2560,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="28" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A28" s="7">
         <v>2023101463</v>
       </c>
@@ -2634,7 +2634,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A29" s="9">
         <v>2022201037</v>
       </c>
@@ -2708,7 +2708,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="30" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A30" s="7">
         <v>2021101896</v>
       </c>
@@ -2782,7 +2782,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="31" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A31" s="9">
         <v>2022201042</v>
       </c>
@@ -2856,7 +2856,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="32" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A32" s="7">
         <v>2020102888</v>
       </c>
@@ -2930,7 +2930,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A33" s="9">
         <v>2024101765</v>
       </c>
@@ -3004,7 +3004,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="34" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A34" s="7">
         <v>2022100612</v>
       </c>
@@ -3078,7 +3078,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="35" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A35" s="9">
         <v>2023101467</v>
       </c>
@@ -3152,7 +3152,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="36" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A36" s="7">
         <v>2022100511</v>
       </c>
@@ -3226,7 +3226,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="37" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A37" s="9">
         <v>2023200147</v>
       </c>
@@ -3300,7 +3300,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="38" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A38" s="7">
         <v>2023100776</v>
       </c>
@@ -3374,7 +3374,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="39" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A39" s="9">
         <v>2024101158</v>
       </c>
@@ -3448,7 +3448,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="40" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A40" s="7">
         <v>2024101773</v>
       </c>
@@ -3522,7 +3522,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="41" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A41" s="9">
         <v>2023100068</v>
       </c>
@@ -3596,7 +3596,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="42" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A42" s="7">
         <v>2023200790</v>
       </c>
@@ -3670,7 +3670,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A43" s="9">
         <v>2022200719</v>
       </c>
@@ -3744,7 +3744,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="44" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A44" s="8">
         <v>2025201178</v>
       </c>
@@ -3818,7 +3818,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A45" s="9">
         <v>2024101775</v>
       </c>
@@ -3892,7 +3892,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="46" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A46" s="7">
         <v>2024103187</v>
       </c>
@@ -3966,7 +3966,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="47" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A47" s="9">
         <v>2023102386</v>
       </c>
@@ -4040,7 +4040,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="48" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A48" s="7">
         <v>2020101654</v>
       </c>
@@ -4114,7 +4114,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="49" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A49" s="9">
         <v>2022201082</v>
       </c>
@@ -4188,7 +4188,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="50" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A50" s="7">
         <v>2024101769</v>
       </c>
@@ -4262,7 +4262,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="51" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A51" s="9">
         <v>2024101154</v>
       </c>
@@ -4336,7 +4336,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="52" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A52" s="7">
         <v>2022102045</v>
       </c>
@@ -4410,7 +4410,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="53" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A53" s="9">
         <v>2023101690</v>
       </c>
@@ -4484,7 +4484,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="54" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A54" s="7">
         <v>2023100954</v>
       </c>
@@ -4558,7 +4558,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="55" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A55" s="9">
         <v>2024202997</v>
       </c>
@@ -4632,7 +4632,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A56" s="7">
         <v>2020101573</v>
       </c>
@@ -4706,7 +4706,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A57" s="9">
         <v>2024101785</v>
       </c>
@@ -4780,7 +4780,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="58" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A58" s="7">
         <v>2021201017</v>
       </c>
@@ -4854,7 +4854,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="59" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A59" s="9">
         <v>2023101691</v>
       </c>
@@ -4928,7 +4928,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="60" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A60" s="7">
         <v>2024101770</v>
       </c>
@@ -5002,7 +5002,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="61" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A61" s="9">
         <v>2022200727</v>
       </c>
@@ -5076,7 +5076,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="62" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A62" s="7">
         <v>2023101729</v>
       </c>
@@ -5150,7 +5150,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A63" s="9">
         <v>2023100965</v>
       </c>
@@ -5224,7 +5224,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A64" s="7">
         <v>2024101155</v>
       </c>
@@ -5298,7 +5298,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="65" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A65" s="9">
         <v>2023200064</v>
       </c>

--- a/notas.xlsx
+++ b/notas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/daniloas.com/projetos/FertilidadeSoloAlegreUFES/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8378485E-6BC2-DC43-8592-8770D726C9EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45274F46-49EE-4F40-9153-73939FB3F4FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="20740" windowHeight="11320" xr2:uid="{BB9E0E1E-73DF-4AB6-A949-07A69840CAF7}"/>
   </bookViews>
@@ -42,14 +42,6 @@
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="27">
   <si>
     <t>Matrícula</t>
-  </si>
-  <si>
-    <t>Pontuação 
-dos exercícios extras</t>
-  </si>
-  <si>
-    <t>Pontuação total
-(Prova + Extra)</t>
   </si>
   <si>
     <t>Item a</t>
@@ -122,6 +114,12 @@
   </si>
   <si>
     <t>7/10</t>
+  </si>
+  <si>
+    <t>Pontuação dos exercícios extras</t>
+  </si>
+  <si>
+    <t>Pontuação total (Prova + Extra)</t>
   </si>
 </sst>
 </file>
@@ -597,73 +595,73 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="H1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="I1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="J1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="K1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="L1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="O1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="P1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="R1" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="S1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="T1" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="U1" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="V1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="W1" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="X1" s="6" t="s">
         <v>4</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="L1" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N1" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="O1" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="P1" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q1" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="R1" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="S1" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="T1" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="U1" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="V1" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="W1" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="X1" s="6" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.2">
@@ -680,31 +678,31 @@
         <v>9.1999999999999993</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F2" s="8">
         <v>0.4</v>
       </c>
       <c r="G2" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2" s="8">
+        <v>1</v>
+      </c>
+      <c r="I2" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="J2" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="K2" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="L2" s="8">
+        <v>1</v>
+      </c>
+      <c r="M2" s="8" t="s">
         <v>12</v>
-      </c>
-      <c r="H2" s="8">
-        <v>1</v>
-      </c>
-      <c r="I2" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="J2" s="8">
-        <v>1.2</v>
-      </c>
-      <c r="K2" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="L2" s="8">
-        <v>1</v>
-      </c>
-      <c r="M2" s="8" t="s">
-        <v>14</v>
       </c>
       <c r="N2" s="8">
         <v>0.6</v>
@@ -754,31 +752,31 @@
         <v>8.6999999999999993</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F3" s="8">
         <v>0.4</v>
       </c>
       <c r="G3" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H3" s="8">
+        <v>1</v>
+      </c>
+      <c r="I3" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="J3" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="K3" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="L3" s="8">
+        <v>1</v>
+      </c>
+      <c r="M3" s="8" t="s">
         <v>12</v>
-      </c>
-      <c r="H3" s="8">
-        <v>1</v>
-      </c>
-      <c r="I3" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="J3" s="8">
-        <v>1.2</v>
-      </c>
-      <c r="K3" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="L3" s="8">
-        <v>1</v>
-      </c>
-      <c r="M3" s="8" t="s">
-        <v>14</v>
       </c>
       <c r="N3" s="8">
         <v>0.6</v>
@@ -828,31 +826,31 @@
         <v>8.75</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F4" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H4" s="8">
         <v>1</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J4" s="8">
         <v>1.2</v>
       </c>
       <c r="K4" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L4" s="8">
         <v>1</v>
       </c>
       <c r="M4" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="N4" s="8">
         <v>1.2</v>
@@ -902,31 +900,31 @@
         <v>9</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F5" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H5" s="8">
         <v>1</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J5" s="8">
         <v>1.2</v>
       </c>
       <c r="K5" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L5" s="8">
         <v>1</v>
       </c>
       <c r="M5" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="N5" s="8">
         <v>1.2</v>
@@ -976,31 +974,31 @@
         <v>9.5</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F6" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H6" s="8">
         <v>1</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J6" s="8">
         <v>1.2</v>
       </c>
       <c r="K6" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L6" s="8">
         <v>1</v>
       </c>
       <c r="M6" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="N6" s="8">
         <v>1.2</v>
@@ -1050,31 +1048,31 @@
         <v>9.3999999999999986</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F7" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G7" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H7" s="8">
+        <v>1</v>
+      </c>
+      <c r="I7" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="J7" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="K7" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="L7" s="8">
+        <v>1</v>
+      </c>
+      <c r="M7" s="8" t="s">
         <v>12</v>
-      </c>
-      <c r="H7" s="8">
-        <v>1</v>
-      </c>
-      <c r="I7" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="J7" s="8">
-        <v>1.2</v>
-      </c>
-      <c r="K7" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="L7" s="8">
-        <v>1</v>
-      </c>
-      <c r="M7" s="8" t="s">
-        <v>14</v>
       </c>
       <c r="N7" s="8">
         <v>0.6</v>
@@ -1124,31 +1122,31 @@
         <v>9.75</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F8" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H8" s="8">
         <v>1</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J8" s="8">
         <v>1.2</v>
       </c>
       <c r="K8" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L8" s="8">
         <v>1</v>
       </c>
       <c r="M8" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="N8" s="8">
         <v>1.2</v>
@@ -1198,31 +1196,31 @@
         <v>8.75</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F9" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H9" s="8">
         <v>1</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J9" s="8">
         <v>1.2</v>
       </c>
       <c r="K9" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L9" s="8">
         <v>1</v>
       </c>
       <c r="M9" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="N9" s="8">
         <v>1.2</v>
@@ -1272,31 +1270,31 @@
         <v>9.5</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F10" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H10" s="8">
         <v>1</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J10" s="8">
         <v>1.2</v>
       </c>
       <c r="K10" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L10" s="8">
         <v>1</v>
       </c>
       <c r="M10" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="N10" s="8">
         <v>1.2</v>
@@ -1390,31 +1388,31 @@
         <v>4.45</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F12" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G12" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H12" s="8">
+        <v>1</v>
+      </c>
+      <c r="I12" s="8" t="s">
         <v>12</v>
-      </c>
-      <c r="H12" s="8">
-        <v>1</v>
-      </c>
-      <c r="I12" s="8" t="s">
-        <v>14</v>
       </c>
       <c r="J12" s="8">
         <v>0.6</v>
       </c>
       <c r="K12" s="8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="L12" s="8">
         <v>0</v>
       </c>
       <c r="M12" s="8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="N12" s="8">
         <v>0</v>
@@ -1464,31 +1462,31 @@
         <v>9.75</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F13" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H13" s="8">
         <v>1</v>
       </c>
       <c r="I13" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J13" s="8">
         <v>1.2</v>
       </c>
       <c r="K13" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L13" s="8">
         <v>1</v>
       </c>
       <c r="M13" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="N13" s="8">
         <v>1.2</v>
@@ -1538,31 +1536,31 @@
         <v>3.6</v>
       </c>
       <c r="E14" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F14" s="8">
+        <v>0.60000000000000009</v>
+      </c>
+      <c r="G14" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H14" s="8">
+        <v>1</v>
+      </c>
+      <c r="I14" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F14" s="8">
-        <v>0.60000000000000009</v>
-      </c>
-      <c r="G14" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="H14" s="8">
-        <v>1</v>
-      </c>
-      <c r="I14" s="8" t="s">
-        <v>17</v>
-      </c>
       <c r="J14" s="8">
         <v>0</v>
       </c>
       <c r="K14" s="8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="L14" s="8">
         <v>0</v>
       </c>
       <c r="M14" s="8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="N14" s="8">
         <v>0</v>
@@ -1612,31 +1610,31 @@
         <v>4.5</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F15" s="8">
         <v>0</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H15" s="8">
         <v>0</v>
       </c>
       <c r="I15" s="8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J15" s="8">
         <v>0</v>
       </c>
       <c r="K15" s="8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="L15" s="8">
         <v>0</v>
       </c>
       <c r="M15" s="8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="N15" s="8">
         <v>0</v>
@@ -1686,31 +1684,31 @@
         <v>9.5</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F16" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G16" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H16" s="8">
+        <v>1</v>
+      </c>
+      <c r="I16" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="J16" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="K16" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="H16" s="8">
-        <v>1</v>
-      </c>
-      <c r="I16" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="J16" s="8">
-        <v>1.2</v>
-      </c>
-      <c r="K16" s="8" t="s">
-        <v>14</v>
-      </c>
       <c r="L16" s="8">
         <v>0.5</v>
       </c>
       <c r="M16" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="N16" s="8">
         <v>1.2</v>
@@ -1760,31 +1758,31 @@
         <v>8.3999999999999986</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F17" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G17" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H17" s="8">
+        <v>1</v>
+      </c>
+      <c r="I17" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="J17" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="K17" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="L17" s="8">
+        <v>1</v>
+      </c>
+      <c r="M17" s="8" t="s">
         <v>12</v>
-      </c>
-      <c r="H17" s="8">
-        <v>1</v>
-      </c>
-      <c r="I17" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="J17" s="8">
-        <v>1.2</v>
-      </c>
-      <c r="K17" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="L17" s="8">
-        <v>1</v>
-      </c>
-      <c r="M17" s="8" t="s">
-        <v>14</v>
       </c>
       <c r="N17" s="8">
         <v>0.6</v>
@@ -1834,31 +1832,31 @@
         <v>8.75</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F18" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H18" s="8">
         <v>1</v>
       </c>
       <c r="I18" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J18" s="8">
         <v>1.2</v>
       </c>
       <c r="K18" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L18" s="8">
         <v>1</v>
       </c>
       <c r="M18" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="N18" s="8">
         <v>1.2</v>
@@ -1908,31 +1906,31 @@
         <v>4.3499999999999996</v>
       </c>
       <c r="E19" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F19" s="8">
+        <v>0.60000000000000009</v>
+      </c>
+      <c r="G19" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H19" s="8">
+        <v>1</v>
+      </c>
+      <c r="I19" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F19" s="8">
-        <v>0.60000000000000009</v>
-      </c>
-      <c r="G19" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="H19" s="8">
-        <v>1</v>
-      </c>
-      <c r="I19" s="8" t="s">
-        <v>17</v>
-      </c>
       <c r="J19" s="8">
         <v>0</v>
       </c>
       <c r="K19" s="8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="L19" s="8">
         <v>0</v>
       </c>
       <c r="M19" s="8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="N19" s="8">
         <v>0</v>
@@ -1982,31 +1980,31 @@
         <v>5.7</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F20" s="8">
         <v>0</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H20" s="8">
         <v>1</v>
       </c>
       <c r="I20" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J20" s="8">
         <v>1.2</v>
       </c>
       <c r="K20" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L20" s="8">
         <v>1</v>
       </c>
       <c r="M20" s="8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="N20" s="8">
         <v>0</v>
@@ -2056,31 +2054,31 @@
         <v>8.8999999999999986</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F21" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G21" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H21" s="8">
+        <v>1</v>
+      </c>
+      <c r="I21" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="J21" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="K21" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="L21" s="8">
+        <v>1</v>
+      </c>
+      <c r="M21" s="8" t="s">
         <v>12</v>
-      </c>
-      <c r="H21" s="8">
-        <v>1</v>
-      </c>
-      <c r="I21" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="J21" s="8">
-        <v>1.2</v>
-      </c>
-      <c r="K21" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="L21" s="8">
-        <v>1</v>
-      </c>
-      <c r="M21" s="8" t="s">
-        <v>14</v>
       </c>
       <c r="N21" s="8">
         <v>0.6</v>
@@ -2130,31 +2128,31 @@
         <v>1.75</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F22" s="8">
         <v>0</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H22" s="8">
         <v>0</v>
       </c>
       <c r="I22" s="8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J22" s="8">
         <v>0</v>
       </c>
       <c r="K22" s="8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="L22" s="8">
         <v>0</v>
       </c>
       <c r="M22" s="8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="N22" s="8">
         <v>0</v>
@@ -2204,31 +2202,31 @@
         <v>9.1499999999999986</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F23" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G23" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H23" s="8">
+        <v>1</v>
+      </c>
+      <c r="I23" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="J23" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="K23" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="L23" s="8">
+        <v>1</v>
+      </c>
+      <c r="M23" s="8" t="s">
         <v>12</v>
-      </c>
-      <c r="H23" s="8">
-        <v>1</v>
-      </c>
-      <c r="I23" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="J23" s="8">
-        <v>1.2</v>
-      </c>
-      <c r="K23" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="L23" s="8">
-        <v>1</v>
-      </c>
-      <c r="M23" s="8" t="s">
-        <v>14</v>
       </c>
       <c r="N23" s="8">
         <v>0.6</v>
@@ -2278,31 +2276,31 @@
         <v>6.35</v>
       </c>
       <c r="E24" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F24" s="8">
+        <v>0.60000000000000009</v>
+      </c>
+      <c r="G24" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H24" s="8">
+        <v>1</v>
+      </c>
+      <c r="I24" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F24" s="8">
-        <v>0.60000000000000009</v>
-      </c>
-      <c r="G24" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="H24" s="8">
-        <v>1</v>
-      </c>
-      <c r="I24" s="8" t="s">
-        <v>17</v>
-      </c>
       <c r="J24" s="8">
         <v>0</v>
       </c>
       <c r="K24" s="8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="L24" s="8">
         <v>0</v>
       </c>
       <c r="M24" s="8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="N24" s="8">
         <v>0</v>
@@ -2352,31 +2350,31 @@
         <v>6.3000000000000007</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F25" s="8">
         <v>0.4</v>
       </c>
       <c r="G25" s="8" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H25" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="I25" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J25" s="8">
         <v>1.2</v>
       </c>
       <c r="K25" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L25" s="8">
         <v>1</v>
       </c>
       <c r="M25" s="8" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N25" s="8">
         <v>0.6</v>
@@ -2426,31 +2424,31 @@
         <v>7.3</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F26" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G26" s="8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H26" s="8">
         <v>1</v>
       </c>
       <c r="I26" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J26" s="8">
         <v>1.2</v>
       </c>
       <c r="K26" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L26" s="8">
         <v>1</v>
       </c>
       <c r="M26" s="8" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="N26" s="8">
         <v>0</v>
@@ -2500,31 +2498,31 @@
         <v>8.65</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F27" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G27" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H27" s="8">
+        <v>1</v>
+      </c>
+      <c r="I27" s="8" t="s">
         <v>12</v>
-      </c>
-      <c r="H27" s="8">
-        <v>1</v>
-      </c>
-      <c r="I27" s="8" t="s">
-        <v>14</v>
       </c>
       <c r="J27" s="8">
         <v>0.6</v>
       </c>
       <c r="K27" s="8" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L27" s="8">
         <v>0.5</v>
       </c>
       <c r="M27" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="N27" s="8">
         <v>1.2</v>
@@ -2574,31 +2572,31 @@
         <v>6.5500000000000007</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F28" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G28" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H28" s="8">
+        <v>1</v>
+      </c>
+      <c r="I28" s="8" t="s">
         <v>12</v>
-      </c>
-      <c r="H28" s="8">
-        <v>1</v>
-      </c>
-      <c r="I28" s="8" t="s">
-        <v>14</v>
       </c>
       <c r="J28" s="8">
         <v>0.6</v>
       </c>
       <c r="K28" s="8" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L28" s="8">
         <v>0.5</v>
       </c>
       <c r="M28" s="8" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N28" s="8">
         <v>0.6</v>
@@ -2648,31 +2646,31 @@
         <v>9.25</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F29" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G29" s="8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H29" s="8">
         <v>1</v>
       </c>
       <c r="I29" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J29" s="8">
         <v>1.2</v>
       </c>
       <c r="K29" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L29" s="8">
         <v>1</v>
       </c>
       <c r="M29" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="N29" s="8">
         <v>1.2</v>
@@ -2722,31 +2720,31 @@
         <v>10</v>
       </c>
       <c r="E30" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F30" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G30" s="8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H30" s="8">
         <v>1</v>
       </c>
       <c r="I30" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J30" s="8">
         <v>1.2</v>
       </c>
       <c r="K30" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L30" s="8">
         <v>1</v>
       </c>
       <c r="M30" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="N30" s="8">
         <v>1.2</v>
@@ -2796,31 +2794,31 @@
         <v>9.25</v>
       </c>
       <c r="E31" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F31" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G31" s="8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H31" s="8">
         <v>1</v>
       </c>
       <c r="I31" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J31" s="8">
         <v>1.2</v>
       </c>
       <c r="K31" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L31" s="8">
         <v>1</v>
       </c>
       <c r="M31" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="N31" s="8">
         <v>1.2</v>
@@ -2870,31 +2868,31 @@
         <v>7.95</v>
       </c>
       <c r="E32" s="8" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F32" s="8">
         <v>0.2</v>
       </c>
       <c r="G32" s="8" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H32" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="I32" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J32" s="8">
         <v>1.2</v>
       </c>
       <c r="K32" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L32" s="8">
         <v>1</v>
       </c>
       <c r="M32" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="N32" s="8">
         <v>1.2</v>
@@ -2944,31 +2942,31 @@
         <v>8.3000000000000007</v>
       </c>
       <c r="E33" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F33" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G33" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H33" s="8">
+        <v>1</v>
+      </c>
+      <c r="I33" s="8" t="s">
         <v>12</v>
-      </c>
-      <c r="H33" s="8">
-        <v>1</v>
-      </c>
-      <c r="I33" s="8" t="s">
-        <v>14</v>
       </c>
       <c r="J33" s="8">
         <v>0.6</v>
       </c>
       <c r="K33" s="8" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L33" s="8">
         <v>0.5</v>
       </c>
       <c r="M33" s="8" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N33" s="8">
         <v>0.6</v>
@@ -3018,31 +3016,31 @@
         <v>9</v>
       </c>
       <c r="E34" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F34" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G34" s="8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H34" s="8">
         <v>0.5</v>
       </c>
       <c r="I34" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J34" s="8">
         <v>1.2</v>
       </c>
       <c r="K34" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L34" s="8">
         <v>1</v>
       </c>
       <c r="M34" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="N34" s="8">
         <v>1.2</v>
@@ -3092,31 +3090,31 @@
         <v>7.3</v>
       </c>
       <c r="E35" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F35" s="8">
+        <v>0.60000000000000009</v>
+      </c>
+      <c r="G35" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="H35" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="I35" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F35" s="8">
-        <v>0.60000000000000009</v>
-      </c>
-      <c r="G35" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="H35" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="I35" s="8" t="s">
-        <v>17</v>
-      </c>
       <c r="J35" s="8">
         <v>0</v>
       </c>
       <c r="K35" s="8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="L35" s="8">
         <v>0</v>
       </c>
       <c r="M35" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="N35" s="8">
         <v>1.2</v>
@@ -3166,31 +3164,31 @@
         <v>6.35</v>
       </c>
       <c r="E36" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F36" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G36" s="8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H36" s="8">
         <v>1</v>
       </c>
       <c r="I36" s="8" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J36" s="8">
         <v>0</v>
       </c>
       <c r="K36" s="8" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="L36" s="8">
         <v>0</v>
       </c>
       <c r="M36" s="8" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N36" s="8">
         <v>0</v>
@@ -3240,31 +3238,31 @@
         <v>10</v>
       </c>
       <c r="E37" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F37" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G37" s="8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H37" s="8">
         <v>1</v>
       </c>
       <c r="I37" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J37" s="8">
         <v>1.2</v>
       </c>
       <c r="K37" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L37" s="8">
         <v>1</v>
       </c>
       <c r="M37" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="N37" s="8">
         <v>1.2</v>
@@ -3314,31 +3312,31 @@
         <v>9.5</v>
       </c>
       <c r="E38" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F38" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G38" s="8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H38" s="8">
         <v>1</v>
       </c>
       <c r="I38" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J38" s="8">
         <v>1.2</v>
       </c>
       <c r="K38" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L38" s="8">
         <v>1</v>
       </c>
       <c r="M38" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="N38" s="8">
         <v>1.2</v>
@@ -3388,31 +3386,31 @@
         <v>10</v>
       </c>
       <c r="E39" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F39" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G39" s="8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H39" s="8">
         <v>1</v>
       </c>
       <c r="I39" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J39" s="8">
         <v>1.2</v>
       </c>
       <c r="K39" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L39" s="8">
         <v>1</v>
       </c>
       <c r="M39" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="N39" s="8">
         <v>1.2</v>
@@ -3462,31 +3460,31 @@
         <v>9.75</v>
       </c>
       <c r="E40" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F40" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G40" s="8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H40" s="8">
         <v>1</v>
       </c>
       <c r="I40" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J40" s="8">
         <v>1.2</v>
       </c>
       <c r="K40" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L40" s="8">
         <v>1</v>
       </c>
       <c r="M40" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="N40" s="8">
         <v>1.2</v>
@@ -3536,31 +3534,31 @@
         <v>8.6000000000000014</v>
       </c>
       <c r="E41" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F41" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G41" s="8" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H41" s="8">
         <v>0.70000000000000007</v>
       </c>
       <c r="I41" s="8" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J41" s="8">
         <v>0.6</v>
       </c>
       <c r="K41" s="8" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L41" s="8">
         <v>0.5</v>
       </c>
       <c r="M41" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="N41" s="8">
         <v>1.2</v>
@@ -3610,31 +3608,31 @@
         <v>5.3999999999999995</v>
       </c>
       <c r="E42" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F42" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G42" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H42" s="8">
+        <v>1</v>
+      </c>
+      <c r="I42" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="J42" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="K42" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="L42" s="8">
+        <v>1</v>
+      </c>
+      <c r="M42" s="8" t="s">
         <v>12</v>
-      </c>
-      <c r="H42" s="8">
-        <v>1</v>
-      </c>
-      <c r="I42" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="J42" s="8">
-        <v>1.2</v>
-      </c>
-      <c r="K42" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="L42" s="8">
-        <v>1</v>
-      </c>
-      <c r="M42" s="8" t="s">
-        <v>14</v>
       </c>
       <c r="N42" s="8">
         <v>0.6</v>
@@ -3684,31 +3682,31 @@
         <v>9.75</v>
       </c>
       <c r="E43" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F43" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G43" s="8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H43" s="8">
         <v>1</v>
       </c>
       <c r="I43" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J43" s="8">
         <v>1.2</v>
       </c>
       <c r="K43" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L43" s="8">
         <v>1</v>
       </c>
       <c r="M43" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="N43" s="8">
         <v>1.2</v>
@@ -3758,31 +3756,31 @@
         <v>6.05</v>
       </c>
       <c r="E44" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F44" s="8">
+        <v>0.60000000000000009</v>
+      </c>
+      <c r="G44" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H44" s="8">
+        <v>1</v>
+      </c>
+      <c r="I44" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="J44" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="K44" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="L44" s="8">
+        <v>1</v>
+      </c>
+      <c r="M44" s="8" t="s">
         <v>15</v>
-      </c>
-      <c r="F44" s="8">
-        <v>0.60000000000000009</v>
-      </c>
-      <c r="G44" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="H44" s="8">
-        <v>1</v>
-      </c>
-      <c r="I44" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="J44" s="8">
-        <v>1.2</v>
-      </c>
-      <c r="K44" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="L44" s="8">
-        <v>1</v>
-      </c>
-      <c r="M44" s="8" t="s">
-        <v>17</v>
       </c>
       <c r="N44" s="8">
         <v>0</v>
@@ -3832,31 +3830,31 @@
         <v>9.1499999999999986</v>
       </c>
       <c r="E45" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F45" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G45" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H45" s="8">
+        <v>1</v>
+      </c>
+      <c r="I45" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="J45" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="K45" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="L45" s="8">
+        <v>1</v>
+      </c>
+      <c r="M45" s="8" t="s">
         <v>12</v>
-      </c>
-      <c r="H45" s="8">
-        <v>1</v>
-      </c>
-      <c r="I45" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="J45" s="8">
-        <v>1.2</v>
-      </c>
-      <c r="K45" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="L45" s="8">
-        <v>1</v>
-      </c>
-      <c r="M45" s="8" t="s">
-        <v>14</v>
       </c>
       <c r="N45" s="8">
         <v>0.6</v>
@@ -3906,31 +3904,31 @@
         <v>7.9</v>
       </c>
       <c r="E46" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F46" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G46" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H46" s="8">
+        <v>1</v>
+      </c>
+      <c r="I46" s="8" t="s">
         <v>12</v>
-      </c>
-      <c r="H46" s="8">
-        <v>1</v>
-      </c>
-      <c r="I46" s="8" t="s">
-        <v>14</v>
       </c>
       <c r="J46" s="8">
         <v>0.6</v>
       </c>
       <c r="K46" s="8" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L46" s="8">
         <v>0.5</v>
       </c>
       <c r="M46" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="N46" s="8">
         <v>1.2</v>
@@ -3980,31 +3978,31 @@
         <v>9</v>
       </c>
       <c r="E47" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F47" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G47" s="8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H47" s="8">
         <v>1</v>
       </c>
       <c r="I47" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J47" s="8">
         <v>1.2</v>
       </c>
       <c r="K47" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L47" s="8">
         <v>1</v>
       </c>
       <c r="M47" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="N47" s="8">
         <v>1.2</v>
@@ -4054,31 +4052,31 @@
         <v>7.9</v>
       </c>
       <c r="E48" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F48" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G48" s="8" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H48" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="I48" s="8" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J48" s="8">
         <v>0.6</v>
       </c>
       <c r="K48" s="8" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L48" s="8">
         <v>0.5</v>
       </c>
       <c r="M48" s="8" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N48" s="8">
         <v>0.6</v>
@@ -4128,31 +4126,31 @@
         <v>9.65</v>
       </c>
       <c r="E49" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F49" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G49" s="8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H49" s="8">
         <v>0.9</v>
       </c>
       <c r="I49" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J49" s="8">
         <v>1.2</v>
       </c>
       <c r="K49" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L49" s="8">
         <v>1</v>
       </c>
       <c r="M49" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="N49" s="8">
         <v>1.2</v>
@@ -4202,31 +4200,31 @@
         <v>8.8999999999999986</v>
       </c>
       <c r="E50" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F50" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G50" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H50" s="8">
+        <v>1</v>
+      </c>
+      <c r="I50" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="J50" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="K50" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="L50" s="8">
+        <v>1</v>
+      </c>
+      <c r="M50" s="8" t="s">
         <v>12</v>
-      </c>
-      <c r="H50" s="8">
-        <v>1</v>
-      </c>
-      <c r="I50" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="J50" s="8">
-        <v>1.2</v>
-      </c>
-      <c r="K50" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="L50" s="8">
-        <v>1</v>
-      </c>
-      <c r="M50" s="8" t="s">
-        <v>14</v>
       </c>
       <c r="N50" s="8">
         <v>0.6</v>
@@ -4276,31 +4274,31 @@
         <v>8.0500000000000007</v>
       </c>
       <c r="E51" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F51" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G51" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H51" s="8">
+        <v>1</v>
+      </c>
+      <c r="I51" s="8" t="s">
         <v>12</v>
-      </c>
-      <c r="H51" s="8">
-        <v>1</v>
-      </c>
-      <c r="I51" s="8" t="s">
-        <v>14</v>
       </c>
       <c r="J51" s="8">
         <v>0.6</v>
       </c>
       <c r="K51" s="8" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L51" s="8">
         <v>0.5</v>
       </c>
       <c r="M51" s="8" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N51" s="8">
         <v>0.6</v>
@@ -4350,31 +4348,31 @@
         <v>7.8000000000000007</v>
       </c>
       <c r="E52" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F52" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G52" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H52" s="8">
+        <v>1</v>
+      </c>
+      <c r="I52" s="8" t="s">
         <v>12</v>
-      </c>
-      <c r="H52" s="8">
-        <v>1</v>
-      </c>
-      <c r="I52" s="8" t="s">
-        <v>14</v>
       </c>
       <c r="J52" s="8">
         <v>0.6</v>
       </c>
       <c r="K52" s="8" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L52" s="8">
         <v>0.5</v>
       </c>
       <c r="M52" s="8" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N52" s="8">
         <v>0.6</v>
@@ -4424,31 +4422,31 @@
         <v>8.75</v>
       </c>
       <c r="E53" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F53" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G53" s="8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H53" s="8">
         <v>1</v>
       </c>
       <c r="I53" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J53" s="8">
         <v>1.2</v>
       </c>
       <c r="K53" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L53" s="8">
         <v>1</v>
       </c>
       <c r="M53" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="N53" s="8">
         <v>1.2</v>
@@ -4498,31 +4496,31 @@
         <v>8.3999999999999986</v>
       </c>
       <c r="E54" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F54" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G54" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H54" s="8">
+        <v>1</v>
+      </c>
+      <c r="I54" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="J54" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="K54" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="L54" s="8">
+        <v>1</v>
+      </c>
+      <c r="M54" s="8" t="s">
         <v>12</v>
-      </c>
-      <c r="H54" s="8">
-        <v>1</v>
-      </c>
-      <c r="I54" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="J54" s="8">
-        <v>1.2</v>
-      </c>
-      <c r="K54" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="L54" s="8">
-        <v>1</v>
-      </c>
-      <c r="M54" s="8" t="s">
-        <v>14</v>
       </c>
       <c r="N54" s="8">
         <v>0.6</v>
@@ -4572,31 +4570,31 @@
         <v>7.65</v>
       </c>
       <c r="E55" s="8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F55" s="8">
         <v>0</v>
       </c>
       <c r="G55" s="8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H55" s="8">
         <v>1</v>
       </c>
       <c r="I55" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J55" s="8">
         <v>1.2</v>
       </c>
       <c r="K55" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L55" s="8">
         <v>1</v>
       </c>
       <c r="M55" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="N55" s="8">
         <v>1.2</v>
@@ -4646,31 +4644,31 @@
         <v>4.5999999999999996</v>
       </c>
       <c r="E56" s="8" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F56" s="8">
         <v>0.4</v>
       </c>
       <c r="G56" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H56" s="8">
+        <v>1</v>
+      </c>
+      <c r="I56" s="8" t="s">
         <v>12</v>
-      </c>
-      <c r="H56" s="8">
-        <v>1</v>
-      </c>
-      <c r="I56" s="8" t="s">
-        <v>14</v>
       </c>
       <c r="J56" s="8">
         <v>0.6</v>
       </c>
       <c r="K56" s="8" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L56" s="8">
         <v>0.5</v>
       </c>
       <c r="M56" s="8" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N56" s="8">
         <v>0.6</v>
@@ -4720,31 +4718,31 @@
         <v>9.75</v>
       </c>
       <c r="E57" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F57" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G57" s="8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H57" s="8">
         <v>1</v>
       </c>
       <c r="I57" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J57" s="8">
         <v>1.2</v>
       </c>
       <c r="K57" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L57" s="8">
         <v>1</v>
       </c>
       <c r="M57" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="N57" s="8">
         <v>1.2</v>
@@ -4794,31 +4792,31 @@
         <v>7.05</v>
       </c>
       <c r="E58" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F58" s="8">
+        <v>0.60000000000000009</v>
+      </c>
+      <c r="G58" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H58" s="8">
+        <v>1</v>
+      </c>
+      <c r="I58" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="J58" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="K58" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="L58" s="8">
+        <v>1</v>
+      </c>
+      <c r="M58" s="8" t="s">
         <v>15</v>
-      </c>
-      <c r="F58" s="8">
-        <v>0.60000000000000009</v>
-      </c>
-      <c r="G58" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="H58" s="8">
-        <v>1</v>
-      </c>
-      <c r="I58" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="J58" s="8">
-        <v>1.2</v>
-      </c>
-      <c r="K58" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="L58" s="8">
-        <v>1</v>
-      </c>
-      <c r="M58" s="8" t="s">
-        <v>17</v>
       </c>
       <c r="N58" s="8">
         <v>0</v>
@@ -4868,31 +4866,31 @@
         <v>9.25</v>
       </c>
       <c r="E59" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F59" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G59" s="8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H59" s="8">
         <v>1</v>
       </c>
       <c r="I59" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J59" s="8">
         <v>1.2</v>
       </c>
       <c r="K59" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L59" s="8">
         <v>1</v>
       </c>
       <c r="M59" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="N59" s="8">
         <v>1.2</v>
@@ -4942,31 +4940,31 @@
         <v>9.75</v>
       </c>
       <c r="E60" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F60" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G60" s="8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H60" s="8">
         <v>1</v>
       </c>
       <c r="I60" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J60" s="8">
         <v>1.2</v>
       </c>
       <c r="K60" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L60" s="8">
         <v>1</v>
       </c>
       <c r="M60" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="N60" s="8">
         <v>1.2</v>
@@ -5016,31 +5014,31 @@
         <v>9.5</v>
       </c>
       <c r="E61" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F61" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G61" s="8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H61" s="8">
         <v>1</v>
       </c>
       <c r="I61" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J61" s="8">
         <v>1.2</v>
       </c>
       <c r="K61" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L61" s="8">
         <v>1</v>
       </c>
       <c r="M61" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="N61" s="8">
         <v>1.2</v>
@@ -5090,31 +5088,31 @@
         <v>6.05</v>
       </c>
       <c r="E62" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F62" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G62" s="8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H62" s="8">
         <v>0.9</v>
       </c>
       <c r="I62" s="8" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J62" s="8">
         <v>0.6</v>
       </c>
       <c r="K62" s="8" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L62" s="8">
         <v>0.5</v>
       </c>
       <c r="M62" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="N62" s="8">
         <v>1.2</v>
@@ -5164,31 +5162,31 @@
         <v>6.6499999999999995</v>
       </c>
       <c r="E63" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F63" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G63" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H63" s="8">
+        <v>1</v>
+      </c>
+      <c r="I63" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="J63" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="K63" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="L63" s="8">
+        <v>1</v>
+      </c>
+      <c r="M63" s="8" t="s">
         <v>12</v>
-      </c>
-      <c r="H63" s="8">
-        <v>1</v>
-      </c>
-      <c r="I63" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="J63" s="8">
-        <v>1.2</v>
-      </c>
-      <c r="K63" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="L63" s="8">
-        <v>1</v>
-      </c>
-      <c r="M63" s="8" t="s">
-        <v>14</v>
       </c>
       <c r="N63" s="8">
         <v>0.6</v>
@@ -5238,31 +5236,31 @@
         <v>8.8999999999999986</v>
       </c>
       <c r="E64" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F64" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G64" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H64" s="8">
+        <v>1</v>
+      </c>
+      <c r="I64" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="J64" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="K64" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="L64" s="8">
+        <v>1</v>
+      </c>
+      <c r="M64" s="8" t="s">
         <v>12</v>
-      </c>
-      <c r="H64" s="8">
-        <v>1</v>
-      </c>
-      <c r="I64" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="J64" s="8">
-        <v>1.2</v>
-      </c>
-      <c r="K64" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="L64" s="8">
-        <v>1</v>
-      </c>
-      <c r="M64" s="8" t="s">
-        <v>14</v>
       </c>
       <c r="N64" s="8">
         <v>0.6</v>
@@ -5312,31 +5310,31 @@
         <v>9.5</v>
       </c>
       <c r="E65" s="8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F65" s="8">
         <v>0.60000000000000009</v>
       </c>
       <c r="G65" s="8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H65" s="8">
         <v>1</v>
       </c>
       <c r="I65" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J65" s="8">
         <v>1.2</v>
       </c>
       <c r="K65" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L65" s="8">
         <v>1</v>
       </c>
       <c r="M65" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="N65" s="8">
         <v>1.2</v>

--- a/notas.xlsx
+++ b/notas.xlsx
@@ -1,20 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11109"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/daniloas.com/projetos/FertilidadeSoloAlegreUFES/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuário\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45274F46-49EE-4F40-9153-73939FB3F4FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6BAF103-AE4A-418F-BD93-6B096AAB85C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="620" windowWidth="20740" windowHeight="11320" xr2:uid="{BB9E0E1E-73DF-4AB6-A949-07A69840CAF7}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11310" xr2:uid="{BB9E0E1E-73DF-4AB6-A949-07A69840CAF7}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId2"/>
+  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -39,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="28">
   <si>
     <t>Matrícula</t>
   </si>
@@ -120,6 +123,9 @@
   </si>
   <si>
     <t>Pontuação total (Prova + Extra)</t>
+  </si>
+  <si>
+    <t>Prova 01</t>
   </si>
 </sst>
 </file>
@@ -216,7 +222,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -245,6 +251,9 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -260,6 +269,532 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Planilha1"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="B2">
+            <v>2023100005</v>
+          </cell>
+          <cell r="C2">
+            <v>10</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>2023200939</v>
+          </cell>
+          <cell r="C3">
+            <v>7.5</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="B4">
+            <v>2021101895</v>
+          </cell>
+          <cell r="C4">
+            <v>9.6</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="B5">
+            <v>2024101156</v>
+          </cell>
+          <cell r="C5">
+            <v>6.15</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="B6">
+            <v>2023200783</v>
+          </cell>
+          <cell r="C6">
+            <v>5.4</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="B7">
+            <v>2022200360</v>
+          </cell>
+          <cell r="C7">
+            <v>7.91</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="B8">
+            <v>2024101774</v>
+          </cell>
+          <cell r="C8">
+            <v>9.86</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="B9">
+            <v>2024203414</v>
+          </cell>
+          <cell r="C9">
+            <v>7.2</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="B10">
+            <v>2023101046</v>
+          </cell>
+          <cell r="C10">
+            <v>9.0299999999999994</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="B11">
+            <v>2019109848</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="B12">
+            <v>2023102012</v>
+          </cell>
+          <cell r="C12">
+            <v>7.96</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="B13">
+            <v>2024101768</v>
+          </cell>
+          <cell r="C13">
+            <v>9.7100000000000009</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="B14">
+            <v>2018104222</v>
+          </cell>
+          <cell r="C14">
+            <v>8.36</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="B15">
+            <v>2017102706</v>
+          </cell>
+          <cell r="C15">
+            <v>6.49</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="B16">
+            <v>2024103491</v>
+          </cell>
+          <cell r="C16">
+            <v>8.5</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="B17">
+            <v>2023100158</v>
+          </cell>
+          <cell r="C17">
+            <v>8.64</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="B18">
+            <v>2024101776</v>
+          </cell>
+          <cell r="C18">
+            <v>9.4600000000000009</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="B19">
+            <v>2020102895</v>
+          </cell>
+          <cell r="C19">
+            <v>5.03</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="B20">
+            <v>2018104240</v>
+          </cell>
+          <cell r="C20">
+            <v>7.11</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="B21">
+            <v>2024101764</v>
+          </cell>
+          <cell r="C21">
+            <v>9.4499999999999993</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="B22">
+            <v>2022102060</v>
+          </cell>
+          <cell r="C22">
+            <v>8.86</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="B23">
+            <v>2024103490</v>
+          </cell>
+          <cell r="C23">
+            <v>6.85</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="B24">
+            <v>2023100771</v>
+          </cell>
+          <cell r="C24">
+            <v>4.5999999999999996</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="B25">
+            <v>2023100962</v>
+          </cell>
+          <cell r="C25">
+            <v>8.4600000000000009</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="B26">
+            <v>2021101361</v>
+          </cell>
+          <cell r="C26">
+            <v>6.08</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="B27">
+            <v>2023201341</v>
+          </cell>
+          <cell r="C27">
+            <v>8.0399999999999991</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="B28">
+            <v>2023101463</v>
+          </cell>
+          <cell r="C28">
+            <v>7.02</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="B29">
+            <v>2022201037</v>
+          </cell>
+          <cell r="C29">
+            <v>7.18</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="B30">
+            <v>2021101896</v>
+          </cell>
+          <cell r="C30">
+            <v>9.9</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="B31">
+            <v>2022201042</v>
+          </cell>
+          <cell r="C31">
+            <v>4.75</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="B32">
+            <v>2020102888</v>
+          </cell>
+          <cell r="C32">
+            <v>8.02</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="B33">
+            <v>2024101765</v>
+          </cell>
+          <cell r="C33">
+            <v>10</v>
+          </cell>
+        </row>
+        <row r="34">
+          <cell r="B34">
+            <v>2022100612</v>
+          </cell>
+          <cell r="C34">
+            <v>8</v>
+          </cell>
+        </row>
+        <row r="35">
+          <cell r="B35">
+            <v>2023101467</v>
+          </cell>
+          <cell r="C35">
+            <v>7.95</v>
+          </cell>
+        </row>
+        <row r="36">
+          <cell r="B36">
+            <v>2022100511</v>
+          </cell>
+          <cell r="C36">
+            <v>6.79</v>
+          </cell>
+        </row>
+        <row r="37">
+          <cell r="B37">
+            <v>2023200147</v>
+          </cell>
+          <cell r="C37">
+            <v>7.2</v>
+          </cell>
+        </row>
+        <row r="38">
+          <cell r="B38">
+            <v>2023100776</v>
+          </cell>
+          <cell r="C38">
+            <v>10</v>
+          </cell>
+        </row>
+        <row r="39">
+          <cell r="B39">
+            <v>2024101158</v>
+          </cell>
+          <cell r="C39">
+            <v>9.6</v>
+          </cell>
+        </row>
+        <row r="40">
+          <cell r="B40">
+            <v>2024101773</v>
+          </cell>
+          <cell r="C40">
+            <v>9.5500000000000007</v>
+          </cell>
+        </row>
+        <row r="41">
+          <cell r="B41">
+            <v>2023100068</v>
+          </cell>
+          <cell r="C41">
+            <v>6.56</v>
+          </cell>
+        </row>
+        <row r="42">
+          <cell r="B42">
+            <v>2023200790</v>
+          </cell>
+          <cell r="C42">
+            <v>7.74</v>
+          </cell>
+        </row>
+        <row r="43">
+          <cell r="B43">
+            <v>2022200719</v>
+          </cell>
+          <cell r="C43">
+            <v>7.25</v>
+          </cell>
+        </row>
+        <row r="44">
+          <cell r="B44">
+            <v>2025201178</v>
+          </cell>
+          <cell r="C44">
+            <v>5.52</v>
+          </cell>
+        </row>
+        <row r="45">
+          <cell r="B45">
+            <v>2024101775</v>
+          </cell>
+          <cell r="C45">
+            <v>9.15</v>
+          </cell>
+        </row>
+        <row r="46">
+          <cell r="B46">
+            <v>2024103187</v>
+          </cell>
+          <cell r="C46">
+            <v>8.7100000000000009</v>
+          </cell>
+        </row>
+        <row r="47">
+          <cell r="B47">
+            <v>2023102386</v>
+          </cell>
+          <cell r="C47">
+            <v>5.86</v>
+          </cell>
+        </row>
+        <row r="48">
+          <cell r="B48">
+            <v>2020101654</v>
+          </cell>
+          <cell r="C48">
+            <v>4.8</v>
+          </cell>
+        </row>
+        <row r="49">
+          <cell r="B49">
+            <v>2022201082</v>
+          </cell>
+          <cell r="C49">
+            <v>6.96</v>
+          </cell>
+        </row>
+        <row r="50">
+          <cell r="B50">
+            <v>2024101769</v>
+          </cell>
+          <cell r="C50">
+            <v>7.3</v>
+          </cell>
+        </row>
+        <row r="51">
+          <cell r="B51">
+            <v>2024101154</v>
+          </cell>
+          <cell r="C51">
+            <v>9.15</v>
+          </cell>
+        </row>
+        <row r="52">
+          <cell r="B52">
+            <v>2022102045</v>
+          </cell>
+          <cell r="C52">
+            <v>9.36</v>
+          </cell>
+        </row>
+        <row r="53">
+          <cell r="B53">
+            <v>2023101690</v>
+          </cell>
+          <cell r="C53">
+            <v>3.15</v>
+          </cell>
+        </row>
+        <row r="54">
+          <cell r="B54">
+            <v>2023100954</v>
+          </cell>
+          <cell r="C54">
+            <v>3.12</v>
+          </cell>
+        </row>
+        <row r="55">
+          <cell r="B55">
+            <v>2024202997</v>
+          </cell>
+          <cell r="C55">
+            <v>2.6</v>
+          </cell>
+        </row>
+        <row r="56">
+          <cell r="B56">
+            <v>2020101573</v>
+          </cell>
+          <cell r="C56">
+            <v>3.45</v>
+          </cell>
+        </row>
+        <row r="57">
+          <cell r="B57">
+            <v>2024101785</v>
+          </cell>
+          <cell r="C57">
+            <v>6.86</v>
+          </cell>
+        </row>
+        <row r="58">
+          <cell r="B58">
+            <v>2021201017</v>
+          </cell>
+          <cell r="C58">
+            <v>8.58</v>
+          </cell>
+        </row>
+        <row r="59">
+          <cell r="B59">
+            <v>2023101691</v>
+          </cell>
+          <cell r="C59">
+            <v>2.0699999999999998</v>
+          </cell>
+        </row>
+        <row r="60">
+          <cell r="B60">
+            <v>2024101770</v>
+          </cell>
+          <cell r="C60">
+            <v>8.34</v>
+          </cell>
+        </row>
+        <row r="61">
+          <cell r="B61">
+            <v>2022200727</v>
+          </cell>
+          <cell r="C61">
+            <v>5.3</v>
+          </cell>
+        </row>
+        <row r="62">
+          <cell r="B62">
+            <v>2023101729</v>
+          </cell>
+          <cell r="C62">
+            <v>8.9</v>
+          </cell>
+        </row>
+        <row r="63">
+          <cell r="B63">
+            <v>2023100965</v>
+          </cell>
+          <cell r="C63">
+            <v>6.41</v>
+          </cell>
+        </row>
+        <row r="64">
+          <cell r="B64">
+            <v>2024101155</v>
+          </cell>
+          <cell r="C64">
+            <v>9.3000000000000007</v>
+          </cell>
+        </row>
+        <row r="65">
+          <cell r="B65">
+            <v>2023200064</v>
+          </cell>
+          <cell r="C65">
+            <v>9.56</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -579,137 +1114,142 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCC50A17-1BAD-4261-9C73-1273FB998B6D}">
-  <dimension ref="A1:X65"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:Y65"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.33203125" customWidth="1"/>
-    <col min="3" max="3" width="17" customWidth="1"/>
-    <col min="4" max="4" width="26.5" customWidth="1"/>
-    <col min="5" max="5" width="7" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11" customWidth="1"/>
+    <col min="3" max="3" width="16.28515625" customWidth="1"/>
+    <col min="4" max="4" width="17" customWidth="1"/>
+    <col min="5" max="5" width="26.5703125" customWidth="1"/>
+    <col min="6" max="6" width="7" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="33" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:25" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="K1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="L1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="M1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="N1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="O1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="O1" s="5" t="s">
-        <v>1</v>
-      </c>
       <c r="P1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="Q1" s="5" t="s">
+      <c r="R1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="R1" s="5" t="s">
+      <c r="S1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="S1" s="5" t="s">
+      <c r="T1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="T1" s="5" t="s">
+      <c r="U1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="U1" s="5" t="s">
+      <c r="V1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="V1" s="6" t="s">
-        <v>1</v>
-      </c>
       <c r="W1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="X1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="X1" s="6" t="s">
+      <c r="Y1" s="6" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A2" s="7">
         <v>2023200939</v>
       </c>
-      <c r="B2" s="8">
+      <c r="B2" s="7">
+        <f>VLOOKUP(A2,[1]Planilha1!$B$2:$C$65,2,)</f>
+        <v>7.5</v>
+      </c>
+      <c r="C2" s="8">
         <v>0.83277777777777773</v>
       </c>
-      <c r="C2" s="8">
+      <c r="D2" s="8">
         <v>10.032777777777778</v>
       </c>
-      <c r="D2" s="8">
+      <c r="E2" s="8">
         <v>9.1999999999999993</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="F2" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="8">
+      <c r="G2" s="8">
         <v>0.4</v>
       </c>
-      <c r="G2" s="8" t="s">
+      <c r="H2" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="H2" s="8">
-        <v>1</v>
-      </c>
-      <c r="I2" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="J2" s="8">
-        <v>1.2</v>
-      </c>
-      <c r="K2" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="L2" s="8">
-        <v>1</v>
-      </c>
-      <c r="M2" s="8" t="s">
+      <c r="I2" s="8">
+        <v>1</v>
+      </c>
+      <c r="J2" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="K2" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="L2" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="M2" s="8">
+        <v>1</v>
+      </c>
+      <c r="N2" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="N2" s="8">
+      <c r="O2" s="8">
         <v>0.6</v>
       </c>
-      <c r="O2" s="8">
-        <v>0.5</v>
-      </c>
       <c r="P2" s="8">
         <v>0.5</v>
       </c>
@@ -737,61 +1277,65 @@
       <c r="X2" s="8">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y2" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A3" s="9">
         <v>2023100005</v>
       </c>
-      <c r="B3" s="8">
+      <c r="B3" s="9">
+        <f>VLOOKUP(A3,[1]Planilha1!$B$2:$C$65,2,)</f>
+        <v>10</v>
+      </c>
+      <c r="C3" s="8">
         <v>0.81555555555555548</v>
       </c>
-      <c r="C3" s="8">
+      <c r="D3" s="8">
         <v>9.5155555555555544</v>
       </c>
-      <c r="D3" s="8">
+      <c r="E3" s="8">
         <v>8.6999999999999993</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="F3" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="8">
+      <c r="G3" s="8">
         <v>0.4</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="H3" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="H3" s="8">
-        <v>1</v>
-      </c>
-      <c r="I3" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="J3" s="8">
-        <v>1.2</v>
-      </c>
-      <c r="K3" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="L3" s="8">
-        <v>1</v>
-      </c>
-      <c r="M3" s="8" t="s">
+      <c r="I3" s="8">
+        <v>1</v>
+      </c>
+      <c r="J3" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="K3" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="L3" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="M3" s="8">
+        <v>1</v>
+      </c>
+      <c r="N3" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="N3" s="8">
+      <c r="O3" s="8">
         <v>0.6</v>
       </c>
-      <c r="O3" s="8">
-        <v>0.5</v>
-      </c>
       <c r="P3" s="8">
         <v>0.5</v>
       </c>
       <c r="Q3" s="8">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="R3" s="8">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="S3" s="8">
         <v>0.5</v>
@@ -800,10 +1344,10 @@
         <v>0.5</v>
       </c>
       <c r="U3" s="8">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="V3" s="8">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="W3" s="8">
         <v>0.5</v>
@@ -811,64 +1355,68 @@
       <c r="X3" s="8">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y3" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A4" s="7">
         <v>2021101895</v>
       </c>
-      <c r="B4" s="8">
+      <c r="B4" s="7">
+        <f>VLOOKUP(A4,[1]Planilha1!$B$2:$C$65,2,)</f>
+        <v>9.6</v>
+      </c>
+      <c r="C4" s="8">
         <v>0.71888888888888891</v>
       </c>
-      <c r="C4" s="8">
+      <c r="D4" s="8">
         <v>9.4688888888888894</v>
       </c>
-      <c r="D4" s="8">
+      <c r="E4" s="8">
         <v>8.75</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="F4" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="F4" s="8">
+      <c r="G4" s="8">
         <v>0.60000000000000009</v>
       </c>
-      <c r="G4" s="8" t="s">
+      <c r="H4" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="H4" s="8">
-        <v>1</v>
-      </c>
-      <c r="I4" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="J4" s="8">
-        <v>1.2</v>
-      </c>
-      <c r="K4" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="L4" s="8">
-        <v>1</v>
-      </c>
-      <c r="M4" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="N4" s="8">
-        <v>1.2</v>
+      <c r="I4" s="8">
+        <v>1</v>
+      </c>
+      <c r="J4" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="K4" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="L4" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="M4" s="8">
+        <v>1</v>
+      </c>
+      <c r="N4" s="8" t="s">
+        <v>11</v>
       </c>
       <c r="O4" s="8">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="P4" s="8">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="Q4" s="8">
         <v>0.25</v>
       </c>
       <c r="R4" s="8">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="S4" s="8">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="T4" s="8">
         <v>0.25</v>
@@ -877,7 +1425,7 @@
         <v>0.25</v>
       </c>
       <c r="V4" s="8">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="W4" s="8">
         <v>0.5</v>
@@ -885,73 +1433,77 @@
       <c r="X4" s="8">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y4" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A5" s="9">
         <v>2024101156</v>
       </c>
-      <c r="B5" s="8">
+      <c r="B5" s="9">
+        <f>VLOOKUP(A5,[1]Planilha1!$B$2:$C$65,2,)</f>
+        <v>6.15</v>
+      </c>
+      <c r="C5" s="8">
         <v>0.66666666666666663</v>
       </c>
-      <c r="C5" s="8">
+      <c r="D5" s="8">
         <v>9.6666666666666679</v>
       </c>
-      <c r="D5" s="8">
+      <c r="E5" s="8">
         <v>9</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="F5" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="8">
+      <c r="G5" s="8">
         <v>0.60000000000000009</v>
       </c>
-      <c r="G5" s="8" t="s">
+      <c r="H5" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="H5" s="8">
-        <v>1</v>
-      </c>
-      <c r="I5" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="J5" s="8">
-        <v>1.2</v>
-      </c>
-      <c r="K5" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="L5" s="8">
-        <v>1</v>
-      </c>
-      <c r="M5" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="N5" s="8">
-        <v>1.2</v>
+      <c r="I5" s="8">
+        <v>1</v>
+      </c>
+      <c r="J5" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="K5" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="L5" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="M5" s="8">
+        <v>1</v>
+      </c>
+      <c r="N5" s="8" t="s">
+        <v>11</v>
       </c>
       <c r="O5" s="8">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="P5" s="8">
         <v>0.5</v>
       </c>
       <c r="Q5" s="8">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="R5" s="8">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="S5" s="8">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="T5" s="8">
         <v>0.5</v>
       </c>
       <c r="U5" s="8">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="V5" s="8">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="W5" s="8">
         <v>0.5</v>
@@ -959,61 +1511,65 @@
       <c r="X5" s="8">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y5" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A6" s="7">
         <v>2023200783</v>
       </c>
-      <c r="B6" s="8">
+      <c r="B6" s="7">
+        <f>VLOOKUP(A6,[1]Planilha1!$B$2:$C$65,2,)</f>
+        <v>5.4</v>
+      </c>
+      <c r="C6" s="8">
         <v>0.9061111111111112</v>
       </c>
-      <c r="C6" s="8">
+      <c r="D6" s="8">
         <v>10.406111111111112</v>
       </c>
-      <c r="D6" s="8">
+      <c r="E6" s="8">
         <v>9.5</v>
       </c>
-      <c r="E6" s="8" t="s">
+      <c r="F6" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="F6" s="8">
+      <c r="G6" s="8">
         <v>0.60000000000000009</v>
       </c>
-      <c r="G6" s="8" t="s">
+      <c r="H6" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="H6" s="8">
-        <v>1</v>
-      </c>
-      <c r="I6" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="J6" s="8">
-        <v>1.2</v>
-      </c>
-      <c r="K6" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="L6" s="8">
-        <v>1</v>
-      </c>
-      <c r="M6" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="N6" s="8">
-        <v>1.2</v>
+      <c r="I6" s="8">
+        <v>1</v>
+      </c>
+      <c r="J6" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="K6" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="L6" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="M6" s="8">
+        <v>1</v>
+      </c>
+      <c r="N6" s="8" t="s">
+        <v>11</v>
       </c>
       <c r="O6" s="8">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="P6" s="8">
         <v>0.5</v>
       </c>
       <c r="Q6" s="8">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="R6" s="8">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="S6" s="8">
         <v>0.5</v>
@@ -1022,10 +1578,10 @@
         <v>0.5</v>
       </c>
       <c r="U6" s="8">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="V6" s="8">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="W6" s="8">
         <v>0.5</v>
@@ -1033,53 +1589,57 @@
       <c r="X6" s="8">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y6" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A7" s="9">
         <v>2022200360</v>
       </c>
-      <c r="B7" s="8">
+      <c r="B7" s="9">
+        <f>VLOOKUP(A7,[1]Planilha1!$B$2:$C$65,2,)</f>
+        <v>7.91</v>
+      </c>
+      <c r="C7" s="8">
         <v>0.84330065359477124</v>
       </c>
-      <c r="C7" s="8">
+      <c r="D7" s="8">
         <v>10.243300653594771</v>
       </c>
-      <c r="D7" s="8">
+      <c r="E7" s="8">
         <v>9.3999999999999986</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="F7" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="F7" s="8">
+      <c r="G7" s="8">
         <v>0.60000000000000009</v>
       </c>
-      <c r="G7" s="8" t="s">
+      <c r="H7" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="H7" s="8">
-        <v>1</v>
-      </c>
-      <c r="I7" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="J7" s="8">
-        <v>1.2</v>
-      </c>
-      <c r="K7" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="L7" s="8">
-        <v>1</v>
-      </c>
-      <c r="M7" s="8" t="s">
+      <c r="I7" s="8">
+        <v>1</v>
+      </c>
+      <c r="J7" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="K7" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="L7" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="M7" s="8">
+        <v>1</v>
+      </c>
+      <c r="N7" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="N7" s="8">
+      <c r="O7" s="8">
         <v>0.6</v>
       </c>
-      <c r="O7" s="8">
-        <v>0.5</v>
-      </c>
       <c r="P7" s="8">
         <v>0.5</v>
       </c>
@@ -1107,52 +1667,56 @@
       <c r="X7" s="8">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y7" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A8" s="7">
         <v>2024101774</v>
       </c>
-      <c r="B8" s="8">
+      <c r="B8" s="7">
+        <f>VLOOKUP(A8,[1]Planilha1!$B$2:$C$65,2,)</f>
+        <v>9.86</v>
+      </c>
+      <c r="C8" s="8">
         <v>0.85692810457516333</v>
       </c>
-      <c r="C8" s="8">
+      <c r="D8" s="8">
         <v>10.606928104575164</v>
       </c>
-      <c r="D8" s="8">
+      <c r="E8" s="8">
         <v>9.75</v>
       </c>
-      <c r="E8" s="8" t="s">
+      <c r="F8" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="F8" s="8">
+      <c r="G8" s="8">
         <v>0.60000000000000009</v>
       </c>
-      <c r="G8" s="8" t="s">
+      <c r="H8" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="H8" s="8">
-        <v>1</v>
-      </c>
-      <c r="I8" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="J8" s="8">
-        <v>1.2</v>
-      </c>
-      <c r="K8" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="L8" s="8">
-        <v>1</v>
-      </c>
-      <c r="M8" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="N8" s="8">
-        <v>1.2</v>
+      <c r="I8" s="8">
+        <v>1</v>
+      </c>
+      <c r="J8" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="K8" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="L8" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="M8" s="8">
+        <v>1</v>
+      </c>
+      <c r="N8" s="8" t="s">
+        <v>11</v>
       </c>
       <c r="O8" s="8">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="P8" s="8">
         <v>0.5</v>
@@ -1170,10 +1734,10 @@
         <v>0.5</v>
       </c>
       <c r="U8" s="8">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="V8" s="8">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="W8" s="8">
         <v>0.5</v>
@@ -1181,61 +1745,65 @@
       <c r="X8" s="8">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y8" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A9" s="9">
         <v>2024203414</v>
       </c>
-      <c r="B9" s="8">
+      <c r="B9" s="9">
+        <f>VLOOKUP(A9,[1]Planilha1!$B$2:$C$65,2,)</f>
+        <v>7.2</v>
+      </c>
+      <c r="C9" s="8">
         <v>0.70796296296296291</v>
       </c>
-      <c r="C9" s="8">
+      <c r="D9" s="8">
         <v>9.4579629629629629</v>
       </c>
-      <c r="D9" s="8">
+      <c r="E9" s="8">
         <v>8.75</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="F9" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="F9" s="8">
+      <c r="G9" s="8">
         <v>0.60000000000000009</v>
       </c>
-      <c r="G9" s="8" t="s">
+      <c r="H9" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="H9" s="8">
-        <v>1</v>
-      </c>
-      <c r="I9" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="J9" s="8">
-        <v>1.2</v>
-      </c>
-      <c r="K9" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="L9" s="8">
-        <v>1</v>
-      </c>
-      <c r="M9" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="N9" s="8">
-        <v>1.2</v>
+      <c r="I9" s="8">
+        <v>1</v>
+      </c>
+      <c r="J9" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="K9" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="L9" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="M9" s="8">
+        <v>1</v>
+      </c>
+      <c r="N9" s="8" t="s">
+        <v>11</v>
       </c>
       <c r="O9" s="8">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="P9" s="8">
         <v>0.5</v>
       </c>
       <c r="Q9" s="8">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="R9" s="8">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="S9" s="8">
         <v>0.5</v>
@@ -1250,57 +1818,61 @@
         <v>0.5</v>
       </c>
       <c r="W9" s="8">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="X9" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y9" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A10" s="7">
         <v>2023101046</v>
       </c>
-      <c r="B10" s="8">
+      <c r="B10" s="7">
+        <f>VLOOKUP(A10,[1]Planilha1!$B$2:$C$65,2,)</f>
+        <v>9.0299999999999994</v>
+      </c>
+      <c r="C10" s="8">
         <v>0.68316993464052289</v>
       </c>
-      <c r="C10" s="8">
+      <c r="D10" s="8">
         <v>10.183169934640524</v>
       </c>
-      <c r="D10" s="8">
+      <c r="E10" s="8">
         <v>9.5</v>
       </c>
-      <c r="E10" s="8" t="s">
+      <c r="F10" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="F10" s="8">
+      <c r="G10" s="8">
         <v>0.60000000000000009</v>
       </c>
-      <c r="G10" s="8" t="s">
+      <c r="H10" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="H10" s="8">
-        <v>1</v>
-      </c>
-      <c r="I10" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="J10" s="8">
-        <v>1.2</v>
-      </c>
-      <c r="K10" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="L10" s="8">
-        <v>1</v>
-      </c>
-      <c r="M10" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="N10" s="8">
-        <v>1.2</v>
+      <c r="I10" s="8">
+        <v>1</v>
+      </c>
+      <c r="J10" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="K10" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="L10" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="M10" s="8">
+        <v>1</v>
+      </c>
+      <c r="N10" s="8" t="s">
+        <v>11</v>
       </c>
       <c r="O10" s="8">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="P10" s="8">
         <v>0.5</v>
@@ -1309,19 +1881,19 @@
         <v>0.5</v>
       </c>
       <c r="R10" s="8">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="S10" s="8">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="T10" s="8">
         <v>0.5</v>
       </c>
       <c r="U10" s="8">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="V10" s="8">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="W10" s="8">
         <v>0.5</v>
@@ -1329,41 +1901,47 @@
       <c r="X10" s="8">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y10" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A11" s="9">
         <v>2019109848</v>
       </c>
-      <c r="B11" s="8">
-        <v>0</v>
-      </c>
-      <c r="C11" s="8" t="e">
-        <v>#VALUE!</v>
+      <c r="B11" s="9">
+        <f>VLOOKUP(A11,[1]Planilha1!$B$2:$C$65,2,)</f>
+        <v>0</v>
+      </c>
+      <c r="C11" s="8">
+        <v>0</v>
       </c>
       <c r="D11" s="8" t="e">
         <v>#VALUE!</v>
       </c>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8" t="e">
+      <c r="E11" s="8" t="e">
         <v>#VALUE!</v>
       </c>
-      <c r="G11" s="8"/>
-      <c r="H11" s="8" t="e">
+      <c r="F11" s="8"/>
+      <c r="G11" s="8" t="e">
         <v>#VALUE!</v>
       </c>
-      <c r="I11" s="8"/>
-      <c r="J11" s="8" t="e">
+      <c r="H11" s="8"/>
+      <c r="I11" s="8" t="e">
         <v>#VALUE!</v>
       </c>
-      <c r="K11" s="8"/>
-      <c r="L11" s="8" t="e">
+      <c r="J11" s="8"/>
+      <c r="K11" s="8" t="e">
         <v>#VALUE!</v>
       </c>
-      <c r="M11" s="8"/>
-      <c r="N11" s="8" t="e">
+      <c r="L11" s="8"/>
+      <c r="M11" s="8" t="e">
         <v>#VALUE!</v>
       </c>
-      <c r="O11" s="8"/>
+      <c r="N11" s="8"/>
+      <c r="O11" s="8" t="e">
+        <v>#VALUE!</v>
+      </c>
       <c r="P11" s="8"/>
       <c r="Q11" s="8"/>
       <c r="R11" s="8"/>
@@ -1373,73 +1951,75 @@
       <c r="V11" s="8"/>
       <c r="W11" s="8"/>
       <c r="X11" s="8"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y11" s="8"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A12" s="7">
         <v>2023102012</v>
       </c>
-      <c r="B12" s="8">
+      <c r="B12" s="7">
+        <f>VLOOKUP(A12,[1]Planilha1!$B$2:$C$65,2,)</f>
+        <v>7.96</v>
+      </c>
+      <c r="C12" s="8">
         <v>0.71433551198257073</v>
       </c>
-      <c r="C12" s="8">
+      <c r="D12" s="8">
         <v>5.1643355119825713</v>
       </c>
-      <c r="D12" s="8">
+      <c r="E12" s="8">
         <v>4.45</v>
       </c>
-      <c r="E12" s="8" t="s">
+      <c r="F12" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="F12" s="8">
+      <c r="G12" s="8">
         <v>0.60000000000000009</v>
       </c>
-      <c r="G12" s="8" t="s">
+      <c r="H12" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="H12" s="8">
-        <v>1</v>
-      </c>
-      <c r="I12" s="8" t="s">
+      <c r="I12" s="8">
+        <v>1</v>
+      </c>
+      <c r="J12" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="J12" s="8">
+      <c r="K12" s="8">
         <v>0.6</v>
       </c>
-      <c r="K12" s="8" t="s">
+      <c r="L12" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="L12" s="8">
-        <v>0</v>
-      </c>
-      <c r="M12" s="8" t="s">
+      <c r="M12" s="8">
+        <v>0</v>
+      </c>
+      <c r="N12" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="N12" s="8">
-        <v>0</v>
-      </c>
       <c r="O12" s="8">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="P12" s="8">
         <v>0.5</v>
       </c>
       <c r="Q12" s="8">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="R12" s="8">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="S12" s="8">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="T12" s="8">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="U12" s="8">
         <v>0.25</v>
       </c>
       <c r="V12" s="8">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="W12" s="8">
         <v>0</v>
@@ -1447,52 +2027,56 @@
       <c r="X12" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y12" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A13" s="9">
         <v>2024101768</v>
       </c>
-      <c r="B13" s="8">
+      <c r="B13" s="9">
+        <f>VLOOKUP(A13,[1]Planilha1!$B$2:$C$65,2,)</f>
+        <v>9.7100000000000009</v>
+      </c>
+      <c r="C13" s="8">
         <v>0.72259259259259256</v>
       </c>
-      <c r="C13" s="8">
+      <c r="D13" s="8">
         <v>10.472592592592592</v>
       </c>
-      <c r="D13" s="8">
+      <c r="E13" s="8">
         <v>9.75</v>
       </c>
-      <c r="E13" s="8" t="s">
+      <c r="F13" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="F13" s="8">
+      <c r="G13" s="8">
         <v>0.60000000000000009</v>
       </c>
-      <c r="G13" s="8" t="s">
+      <c r="H13" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="H13" s="8">
-        <v>1</v>
-      </c>
-      <c r="I13" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="J13" s="8">
-        <v>1.2</v>
-      </c>
-      <c r="K13" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="L13" s="8">
-        <v>1</v>
-      </c>
-      <c r="M13" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="N13" s="8">
-        <v>1.2</v>
+      <c r="I13" s="8">
+        <v>1</v>
+      </c>
+      <c r="J13" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="K13" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="L13" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="M13" s="8">
+        <v>1</v>
+      </c>
+      <c r="N13" s="8" t="s">
+        <v>11</v>
       </c>
       <c r="O13" s="8">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="P13" s="8">
         <v>0.5</v>
@@ -1510,10 +2094,10 @@
         <v>0.5</v>
       </c>
       <c r="U13" s="8">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="V13" s="8">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="W13" s="8">
         <v>0.5</v>
@@ -1521,58 +2105,62 @@
       <c r="X13" s="8">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y13" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A14" s="7">
         <v>2018104222</v>
       </c>
-      <c r="B14" s="8">
+      <c r="B14" s="7">
+        <f>VLOOKUP(A14,[1]Planilha1!$B$2:$C$65,2,)</f>
+        <v>8.36</v>
+      </c>
+      <c r="C14" s="8">
         <v>0.51771241830065362</v>
       </c>
-      <c r="C14" s="8">
+      <c r="D14" s="8">
         <v>4.1177124183006537</v>
       </c>
-      <c r="D14" s="8">
+      <c r="E14" s="8">
         <v>3.6</v>
       </c>
-      <c r="E14" s="8" t="s">
+      <c r="F14" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="F14" s="8">
+      <c r="G14" s="8">
         <v>0.60000000000000009</v>
       </c>
-      <c r="G14" s="8" t="s">
+      <c r="H14" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="H14" s="8">
-        <v>1</v>
-      </c>
-      <c r="I14" s="8" t="s">
+      <c r="I14" s="8">
+        <v>1</v>
+      </c>
+      <c r="J14" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="J14" s="8">
-        <v>0</v>
-      </c>
-      <c r="K14" s="8" t="s">
+      <c r="K14" s="8">
+        <v>0</v>
+      </c>
+      <c r="L14" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="L14" s="8">
-        <v>0</v>
-      </c>
-      <c r="M14" s="8" t="s">
+      <c r="M14" s="8">
+        <v>0</v>
+      </c>
+      <c r="N14" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="N14" s="8">
-        <v>0</v>
-      </c>
       <c r="O14" s="8">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="P14" s="8">
         <v>0.5</v>
       </c>
       <c r="Q14" s="8">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="R14" s="8">
         <v>0.25</v>
@@ -1581,13 +2169,13 @@
         <v>0.25</v>
       </c>
       <c r="T14" s="8">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="U14" s="8">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="V14" s="8">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="W14" s="8">
         <v>0</v>
@@ -1595,64 +2183,68 @@
       <c r="X14" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y14" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A15" s="9">
         <v>2017102706</v>
       </c>
-      <c r="B15" s="8">
+      <c r="B15" s="9">
+        <f>VLOOKUP(A15,[1]Planilha1!$B$2:$C$65,2,)</f>
+        <v>6.49</v>
+      </c>
+      <c r="C15" s="8">
         <v>0.80681732026143782</v>
       </c>
-      <c r="C15" s="8">
+      <c r="D15" s="8">
         <v>5.3068173202614375</v>
       </c>
-      <c r="D15" s="8">
+      <c r="E15" s="8">
         <v>4.5</v>
       </c>
-      <c r="E15" s="8" t="s">
+      <c r="F15" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="F15" s="8">
-        <v>0</v>
-      </c>
-      <c r="G15" s="8" t="s">
+      <c r="G15" s="8">
+        <v>0</v>
+      </c>
+      <c r="H15" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="H15" s="8">
-        <v>0</v>
-      </c>
-      <c r="I15" s="8" t="s">
+      <c r="I15" s="8">
+        <v>0</v>
+      </c>
+      <c r="J15" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="J15" s="8">
-        <v>0</v>
-      </c>
-      <c r="K15" s="8" t="s">
+      <c r="K15" s="8">
+        <v>0</v>
+      </c>
+      <c r="L15" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="L15" s="8">
-        <v>0</v>
-      </c>
-      <c r="M15" s="8" t="s">
+      <c r="M15" s="8">
+        <v>0</v>
+      </c>
+      <c r="N15" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="N15" s="8">
-        <v>0</v>
-      </c>
       <c r="O15" s="8">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="P15" s="8">
         <v>0.5</v>
       </c>
       <c r="Q15" s="8">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="R15" s="8">
         <v>0.25</v>
       </c>
       <c r="S15" s="8">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="T15" s="8">
         <v>0.5</v>
@@ -1669,52 +2261,56 @@
       <c r="X15" s="8">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y15" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A16" s="7">
         <v>2024103491</v>
       </c>
-      <c r="B16" s="8">
+      <c r="B16" s="7">
+        <f>VLOOKUP(A16,[1]Planilha1!$B$2:$C$65,2,)</f>
+        <v>8.5</v>
+      </c>
+      <c r="C16" s="8">
         <v>0.93174291938997822</v>
       </c>
-      <c r="C16" s="8">
+      <c r="D16" s="8">
         <v>10.431742919389979</v>
       </c>
-      <c r="D16" s="8">
+      <c r="E16" s="8">
         <v>9.5</v>
       </c>
-      <c r="E16" s="8" t="s">
+      <c r="F16" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="F16" s="8">
+      <c r="G16" s="8">
         <v>0.60000000000000009</v>
       </c>
-      <c r="G16" s="8" t="s">
+      <c r="H16" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="H16" s="8">
-        <v>1</v>
-      </c>
-      <c r="I16" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="J16" s="8">
-        <v>1.2</v>
-      </c>
-      <c r="K16" s="8" t="s">
+      <c r="I16" s="8">
+        <v>1</v>
+      </c>
+      <c r="J16" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="K16" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="L16" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="L16" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="M16" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="N16" s="8">
-        <v>1.2</v>
+      <c r="M16" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="N16" s="8" t="s">
+        <v>11</v>
       </c>
       <c r="O16" s="8">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="P16" s="8">
         <v>0.5</v>
@@ -1743,53 +2339,57 @@
       <c r="X16" s="8">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y16" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A17" s="9">
         <v>2023100158</v>
       </c>
-      <c r="B17" s="8">
+      <c r="B17" s="9">
+        <f>VLOOKUP(A17,[1]Planilha1!$B$2:$C$65,2,)</f>
+        <v>8.64</v>
+      </c>
+      <c r="C17" s="8">
         <v>0.22222222222222221</v>
       </c>
-      <c r="C17" s="8">
+      <c r="D17" s="8">
         <v>8.6222222222222218</v>
       </c>
-      <c r="D17" s="8">
+      <c r="E17" s="8">
         <v>8.3999999999999986</v>
       </c>
-      <c r="E17" s="8" t="s">
+      <c r="F17" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="F17" s="8">
+      <c r="G17" s="8">
         <v>0.60000000000000009</v>
       </c>
-      <c r="G17" s="8" t="s">
+      <c r="H17" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="H17" s="8">
-        <v>1</v>
-      </c>
-      <c r="I17" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="J17" s="8">
-        <v>1.2</v>
-      </c>
-      <c r="K17" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="L17" s="8">
-        <v>1</v>
-      </c>
-      <c r="M17" s="8" t="s">
+      <c r="I17" s="8">
+        <v>1</v>
+      </c>
+      <c r="J17" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="K17" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="L17" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="M17" s="8">
+        <v>1</v>
+      </c>
+      <c r="N17" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="N17" s="8">
+      <c r="O17" s="8">
         <v>0.6</v>
       </c>
-      <c r="O17" s="8">
-        <v>0.5</v>
-      </c>
       <c r="P17" s="8">
         <v>0.5</v>
       </c>
@@ -1803,161 +2403,169 @@
         <v>0.5</v>
       </c>
       <c r="T17" s="8">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="U17" s="8">
         <v>0.25</v>
       </c>
       <c r="V17" s="8">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="W17" s="8">
         <v>0.5</v>
       </c>
       <c r="X17" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.2">
+        <v>0.5</v>
+      </c>
+      <c r="Y17" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A18" s="7">
         <v>2024101776</v>
       </c>
-      <c r="B18" s="8">
+      <c r="B18" s="7">
+        <f>VLOOKUP(A18,[1]Planilha1!$B$2:$C$65,2,)</f>
+        <v>9.4600000000000009</v>
+      </c>
+      <c r="C18" s="8">
         <v>0.80248366013071892</v>
       </c>
-      <c r="C18" s="8">
+      <c r="D18" s="8">
         <v>9.5524836601307186</v>
       </c>
-      <c r="D18" s="8">
+      <c r="E18" s="8">
         <v>8.75</v>
       </c>
-      <c r="E18" s="8" t="s">
+      <c r="F18" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="F18" s="8">
+      <c r="G18" s="8">
         <v>0.60000000000000009</v>
       </c>
-      <c r="G18" s="8" t="s">
+      <c r="H18" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="H18" s="8">
-        <v>1</v>
-      </c>
-      <c r="I18" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="J18" s="8">
-        <v>1.2</v>
-      </c>
-      <c r="K18" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="L18" s="8">
-        <v>1</v>
-      </c>
-      <c r="M18" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="N18" s="8">
-        <v>1.2</v>
+      <c r="I18" s="8">
+        <v>1</v>
+      </c>
+      <c r="J18" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="K18" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="L18" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="M18" s="8">
+        <v>1</v>
+      </c>
+      <c r="N18" s="8" t="s">
+        <v>11</v>
       </c>
       <c r="O18" s="8">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="P18" s="8">
         <v>0.5</v>
       </c>
       <c r="Q18" s="8">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="R18" s="8">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="S18" s="8">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="T18" s="8">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="U18" s="8">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="V18" s="8">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="W18" s="8">
         <v>0.5</v>
       </c>
       <c r="X18" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.2">
+        <v>0.5</v>
+      </c>
+      <c r="Y18" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A19" s="9">
         <v>2020102895</v>
       </c>
-      <c r="B19" s="8">
+      <c r="B19" s="9">
+        <f>VLOOKUP(A19,[1]Planilha1!$B$2:$C$65,2,)</f>
+        <v>5.03</v>
+      </c>
+      <c r="C19" s="8">
         <v>0.77559912854030499</v>
       </c>
-      <c r="C19" s="8">
+      <c r="D19" s="8">
         <v>5.1255991285403049</v>
       </c>
-      <c r="D19" s="8">
+      <c r="E19" s="8">
         <v>4.3499999999999996</v>
       </c>
-      <c r="E19" s="8" t="s">
+      <c r="F19" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="F19" s="8">
+      <c r="G19" s="8">
         <v>0.60000000000000009</v>
       </c>
-      <c r="G19" s="8" t="s">
+      <c r="H19" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="H19" s="8">
-        <v>1</v>
-      </c>
-      <c r="I19" s="8" t="s">
+      <c r="I19" s="8">
+        <v>1</v>
+      </c>
+      <c r="J19" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="J19" s="8">
-        <v>0</v>
-      </c>
-      <c r="K19" s="8" t="s">
+      <c r="K19" s="8">
+        <v>0</v>
+      </c>
+      <c r="L19" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="L19" s="8">
-        <v>0</v>
-      </c>
-      <c r="M19" s="8" t="s">
+      <c r="M19" s="8">
+        <v>0</v>
+      </c>
+      <c r="N19" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="N19" s="8">
-        <v>0</v>
-      </c>
       <c r="O19" s="8">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="P19" s="8">
         <v>0.5</v>
       </c>
       <c r="Q19" s="8">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="R19" s="8">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="S19" s="8">
         <v>0.5</v>
       </c>
       <c r="T19" s="8">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="U19" s="8">
         <v>0.25</v>
       </c>
       <c r="V19" s="8">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="W19" s="8">
         <v>0</v>
@@ -1965,61 +2573,65 @@
       <c r="X19" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y19" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A20" s="7">
         <v>2018104240</v>
       </c>
-      <c r="B20" s="8">
+      <c r="B20" s="7">
+        <f>VLOOKUP(A20,[1]Planilha1!$B$2:$C$65,2,)</f>
+        <v>7.11</v>
+      </c>
+      <c r="C20" s="8">
         <v>0.33333333333333331</v>
       </c>
-      <c r="C20" s="8">
+      <c r="D20" s="8">
         <v>6.0333333333333332</v>
       </c>
-      <c r="D20" s="8">
+      <c r="E20" s="8">
         <v>5.7</v>
       </c>
-      <c r="E20" s="8" t="s">
+      <c r="F20" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="F20" s="8">
-        <v>0</v>
-      </c>
-      <c r="G20" s="8" t="s">
+      <c r="G20" s="8">
+        <v>0</v>
+      </c>
+      <c r="H20" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="H20" s="8">
-        <v>1</v>
-      </c>
-      <c r="I20" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="J20" s="8">
-        <v>1.2</v>
-      </c>
-      <c r="K20" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="L20" s="8">
-        <v>1</v>
-      </c>
-      <c r="M20" s="8" t="s">
+      <c r="I20" s="8">
+        <v>1</v>
+      </c>
+      <c r="J20" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="K20" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="L20" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="M20" s="8">
+        <v>1</v>
+      </c>
+      <c r="N20" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="N20" s="8">
-        <v>0</v>
-      </c>
       <c r="O20" s="8">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="P20" s="8">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q20" s="8">
         <v>0</v>
       </c>
       <c r="R20" s="8">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="S20" s="8">
         <v>0.25</v>
@@ -2031,61 +2643,65 @@
         <v>0.25</v>
       </c>
       <c r="V20" s="8">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="W20" s="8">
         <v>0.5</v>
       </c>
       <c r="X20" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:24" x14ac:dyDescent="0.2">
+        <v>0.5</v>
+      </c>
+      <c r="Y20" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A21" s="9">
         <v>2024101764</v>
       </c>
-      <c r="B21" s="8">
+      <c r="B21" s="9">
+        <f>VLOOKUP(A21,[1]Planilha1!$B$2:$C$65,2,)</f>
+        <v>9.4499999999999993</v>
+      </c>
+      <c r="C21" s="8">
         <v>0.91901960784313719</v>
       </c>
-      <c r="C21" s="8">
+      <c r="D21" s="8">
         <v>9.8190196078431367</v>
       </c>
-      <c r="D21" s="8">
+      <c r="E21" s="8">
         <v>8.8999999999999986</v>
       </c>
-      <c r="E21" s="8" t="s">
+      <c r="F21" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="F21" s="8">
+      <c r="G21" s="8">
         <v>0.60000000000000009</v>
       </c>
-      <c r="G21" s="8" t="s">
+      <c r="H21" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="H21" s="8">
-        <v>1</v>
-      </c>
-      <c r="I21" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="J21" s="8">
-        <v>1.2</v>
-      </c>
-      <c r="K21" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="L21" s="8">
-        <v>1</v>
-      </c>
-      <c r="M21" s="8" t="s">
+      <c r="I21" s="8">
+        <v>1</v>
+      </c>
+      <c r="J21" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="K21" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="L21" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="M21" s="8">
+        <v>1</v>
+      </c>
+      <c r="N21" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="N21" s="8">
+      <c r="O21" s="8">
         <v>0.6</v>
       </c>
-      <c r="O21" s="8">
-        <v>0.5</v>
-      </c>
       <c r="P21" s="8">
         <v>0.5</v>
       </c>
@@ -2093,19 +2709,19 @@
         <v>0.5</v>
       </c>
       <c r="R21" s="8">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="S21" s="8">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="T21" s="8">
         <v>0.5</v>
       </c>
       <c r="U21" s="8">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="V21" s="8">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="W21" s="8">
         <v>0.5</v>
@@ -2113,67 +2729,71 @@
       <c r="X21" s="8">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="22" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y21" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A22" s="7">
         <v>2022102060</v>
       </c>
-      <c r="B22" s="8">
+      <c r="B22" s="7">
+        <f>VLOOKUP(A22,[1]Planilha1!$B$2:$C$65,2,)</f>
+        <v>8.86</v>
+      </c>
+      <c r="C22" s="8">
         <v>0.21296296296296297</v>
       </c>
-      <c r="C22" s="8">
+      <c r="D22" s="8">
         <v>1.962962962962963</v>
       </c>
-      <c r="D22" s="8">
+      <c r="E22" s="8">
         <v>1.75</v>
       </c>
-      <c r="E22" s="8" t="s">
+      <c r="F22" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="F22" s="8">
-        <v>0</v>
-      </c>
-      <c r="G22" s="8" t="s">
+      <c r="G22" s="8">
+        <v>0</v>
+      </c>
+      <c r="H22" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="H22" s="8">
-        <v>0</v>
-      </c>
-      <c r="I22" s="8" t="s">
+      <c r="I22" s="8">
+        <v>0</v>
+      </c>
+      <c r="J22" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="J22" s="8">
-        <v>0</v>
-      </c>
-      <c r="K22" s="8" t="s">
+      <c r="K22" s="8">
+        <v>0</v>
+      </c>
+      <c r="L22" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="L22" s="8">
-        <v>0</v>
-      </c>
-      <c r="M22" s="8" t="s">
+      <c r="M22" s="8">
+        <v>0</v>
+      </c>
+      <c r="N22" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="N22" s="8">
-        <v>0</v>
-      </c>
       <c r="O22" s="8">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="P22" s="8">
         <v>0.5</v>
       </c>
       <c r="Q22" s="8">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="R22" s="8">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="S22" s="8">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="T22" s="8">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="U22" s="8">
         <v>0</v>
@@ -2187,53 +2807,57 @@
       <c r="X22" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y22" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A23" s="9">
         <v>2024103490</v>
       </c>
-      <c r="B23" s="8">
+      <c r="B23" s="9">
+        <f>VLOOKUP(A23,[1]Planilha1!$B$2:$C$65,2,)</f>
+        <v>6.85</v>
+      </c>
+      <c r="C23" s="8">
         <v>0.94388888888888889</v>
       </c>
-      <c r="C23" s="8">
+      <c r="D23" s="8">
         <v>10.093888888888888</v>
       </c>
-      <c r="D23" s="8">
+      <c r="E23" s="8">
         <v>9.1499999999999986</v>
       </c>
-      <c r="E23" s="8" t="s">
+      <c r="F23" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="F23" s="8">
+      <c r="G23" s="8">
         <v>0.60000000000000009</v>
       </c>
-      <c r="G23" s="8" t="s">
+      <c r="H23" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="H23" s="8">
-        <v>1</v>
-      </c>
-      <c r="I23" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="J23" s="8">
-        <v>1.2</v>
-      </c>
-      <c r="K23" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="L23" s="8">
-        <v>1</v>
-      </c>
-      <c r="M23" s="8" t="s">
+      <c r="I23" s="8">
+        <v>1</v>
+      </c>
+      <c r="J23" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="K23" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="L23" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="M23" s="8">
+        <v>1</v>
+      </c>
+      <c r="N23" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="N23" s="8">
+      <c r="O23" s="8">
         <v>0.6</v>
       </c>
-      <c r="O23" s="8">
-        <v>0.5</v>
-      </c>
       <c r="P23" s="8">
         <v>0.5</v>
       </c>
@@ -2250,10 +2874,10 @@
         <v>0.5</v>
       </c>
       <c r="U23" s="8">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="V23" s="8">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="W23" s="8">
         <v>0.5</v>
@@ -2261,61 +2885,65 @@
       <c r="X23" s="8">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="24" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y23" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A24" s="7">
         <v>2023100771</v>
       </c>
-      <c r="B24" s="8">
+      <c r="B24" s="7">
+        <f>VLOOKUP(A24,[1]Planilha1!$B$2:$C$65,2,)</f>
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="C24" s="8">
         <v>0.60129629629629633</v>
       </c>
-      <c r="C24" s="8">
+      <c r="D24" s="8">
         <v>6.951296296296297</v>
       </c>
-      <c r="D24" s="8">
+      <c r="E24" s="8">
         <v>6.35</v>
       </c>
-      <c r="E24" s="8" t="s">
+      <c r="F24" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="F24" s="8">
+      <c r="G24" s="8">
         <v>0.60000000000000009</v>
       </c>
-      <c r="G24" s="8" t="s">
+      <c r="H24" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="H24" s="8">
-        <v>1</v>
-      </c>
-      <c r="I24" s="8" t="s">
+      <c r="I24" s="8">
+        <v>1</v>
+      </c>
+      <c r="J24" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="J24" s="8">
-        <v>0</v>
-      </c>
-      <c r="K24" s="8" t="s">
+      <c r="K24" s="8">
+        <v>0</v>
+      </c>
+      <c r="L24" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="L24" s="8">
-        <v>0</v>
-      </c>
-      <c r="M24" s="8" t="s">
+      <c r="M24" s="8">
+        <v>0</v>
+      </c>
+      <c r="N24" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="N24" s="8">
-        <v>0</v>
-      </c>
       <c r="O24" s="8">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="P24" s="8">
         <v>0.5</v>
       </c>
       <c r="Q24" s="8">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="R24" s="8">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="S24" s="8">
         <v>0.5</v>
@@ -2335,209 +2963,221 @@
       <c r="X24" s="8">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="25" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y24" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A25" s="9">
         <v>2023100962</v>
       </c>
-      <c r="B25" s="8">
+      <c r="B25" s="9">
+        <f>VLOOKUP(A25,[1]Planilha1!$B$2:$C$65,2,)</f>
+        <v>8.4600000000000009</v>
+      </c>
+      <c r="C25" s="8">
         <v>0.96333333333333349</v>
       </c>
-      <c r="C25" s="8">
+      <c r="D25" s="8">
         <v>7.2633333333333336</v>
       </c>
-      <c r="D25" s="8">
+      <c r="E25" s="8">
         <v>6.3000000000000007</v>
       </c>
-      <c r="E25" s="8" t="s">
+      <c r="F25" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="F25" s="8">
+      <c r="G25" s="8">
         <v>0.4</v>
       </c>
-      <c r="G25" s="8" t="s">
+      <c r="H25" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="H25" s="8">
+      <c r="I25" s="8">
         <v>0.60000000000000009</v>
       </c>
-      <c r="I25" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="J25" s="8">
-        <v>1.2</v>
-      </c>
-      <c r="K25" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="L25" s="8">
-        <v>1</v>
-      </c>
-      <c r="M25" s="8" t="s">
+      <c r="J25" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="K25" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="L25" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="M25" s="8">
+        <v>1</v>
+      </c>
+      <c r="N25" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="N25" s="8">
+      <c r="O25" s="8">
         <v>0.6</v>
       </c>
-      <c r="O25" s="8">
-        <v>0</v>
-      </c>
       <c r="P25" s="8">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="Q25" s="8">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="R25" s="8">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="S25" s="8">
         <v>0</v>
       </c>
       <c r="T25" s="8">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="U25" s="8">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="V25" s="8">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="W25" s="8">
         <v>0.5</v>
       </c>
       <c r="X25" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:24" x14ac:dyDescent="0.2">
+        <v>0.5</v>
+      </c>
+      <c r="Y25" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A26" s="7">
         <v>2021101361</v>
       </c>
-      <c r="B26" s="8">
+      <c r="B26" s="7">
+        <f>VLOOKUP(A26,[1]Planilha1!$B$2:$C$65,2,)</f>
+        <v>6.08</v>
+      </c>
+      <c r="C26" s="8">
         <v>0.32407407407407407</v>
       </c>
-      <c r="C26" s="8">
+      <c r="D26" s="8">
         <v>7.6240740740740742</v>
       </c>
-      <c r="D26" s="8">
+      <c r="E26" s="8">
         <v>7.3</v>
       </c>
-      <c r="E26" s="8" t="s">
+      <c r="F26" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="F26" s="8">
+      <c r="G26" s="8">
         <v>0.60000000000000009</v>
       </c>
-      <c r="G26" s="8" t="s">
+      <c r="H26" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="H26" s="8">
-        <v>1</v>
-      </c>
-      <c r="I26" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="J26" s="8">
-        <v>1.2</v>
-      </c>
-      <c r="K26" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="L26" s="8">
-        <v>1</v>
-      </c>
-      <c r="M26" s="8" t="s">
+      <c r="I26" s="8">
+        <v>1</v>
+      </c>
+      <c r="J26" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="K26" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="L26" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="M26" s="8">
+        <v>1</v>
+      </c>
+      <c r="N26" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="N26" s="8">
-        <v>0</v>
-      </c>
       <c r="O26" s="8">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="P26" s="8">
         <v>0.5</v>
       </c>
       <c r="Q26" s="8">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="R26" s="8">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="S26" s="8">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="T26" s="8">
         <v>0.5</v>
       </c>
       <c r="U26" s="8">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="V26" s="8">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="W26" s="8">
         <v>0.5</v>
       </c>
       <c r="X26" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:24" x14ac:dyDescent="0.2">
+        <v>0.5</v>
+      </c>
+      <c r="Y26" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A27" s="9">
         <v>2023201341</v>
       </c>
-      <c r="B27" s="8">
+      <c r="B27" s="9">
+        <f>VLOOKUP(A27,[1]Planilha1!$B$2:$C$65,2,)</f>
+        <v>8.0399999999999991</v>
+      </c>
+      <c r="C27" s="8">
         <v>0.86944444444444458</v>
       </c>
-      <c r="C27" s="8">
+      <c r="D27" s="8">
         <v>9.5194444444444457</v>
       </c>
-      <c r="D27" s="8">
+      <c r="E27" s="8">
         <v>8.65</v>
       </c>
-      <c r="E27" s="8" t="s">
+      <c r="F27" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="F27" s="8">
+      <c r="G27" s="8">
         <v>0.60000000000000009</v>
       </c>
-      <c r="G27" s="8" t="s">
+      <c r="H27" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="H27" s="8">
-        <v>1</v>
-      </c>
-      <c r="I27" s="8" t="s">
+      <c r="I27" s="8">
+        <v>1</v>
+      </c>
+      <c r="J27" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="J27" s="8">
+      <c r="K27" s="8">
         <v>0.6</v>
       </c>
-      <c r="K27" s="8" t="s">
+      <c r="L27" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="L27" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="M27" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="N27" s="8">
-        <v>1.2</v>
+      <c r="M27" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="N27" s="8" t="s">
+        <v>11</v>
       </c>
       <c r="O27" s="8">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="P27" s="8">
         <v>0.5</v>
       </c>
       <c r="Q27" s="8">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="R27" s="8">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="S27" s="8">
         <v>0.5</v>
@@ -2557,147 +3197,155 @@
       <c r="X27" s="8">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="28" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y27" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A28" s="7">
         <v>2023101463</v>
       </c>
-      <c r="B28" s="8">
+      <c r="B28" s="7">
+        <f>VLOOKUP(A28,[1]Planilha1!$B$2:$C$65,2,)</f>
+        <v>7.02</v>
+      </c>
+      <c r="C28" s="8">
         <v>0.33333333333333331</v>
       </c>
-      <c r="C28" s="8">
+      <c r="D28" s="8">
         <v>6.8833333333333329</v>
       </c>
-      <c r="D28" s="8">
+      <c r="E28" s="8">
         <v>6.5500000000000007</v>
       </c>
-      <c r="E28" s="8" t="s">
+      <c r="F28" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="F28" s="8">
+      <c r="G28" s="8">
         <v>0.60000000000000009</v>
       </c>
-      <c r="G28" s="8" t="s">
+      <c r="H28" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="H28" s="8">
-        <v>1</v>
-      </c>
-      <c r="I28" s="8" t="s">
+      <c r="I28" s="8">
+        <v>1</v>
+      </c>
+      <c r="J28" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="J28" s="8">
+      <c r="K28" s="8">
         <v>0.6</v>
       </c>
-      <c r="K28" s="8" t="s">
+      <c r="L28" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="L28" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="M28" s="8" t="s">
+      <c r="M28" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="N28" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="N28" s="8">
+      <c r="O28" s="8">
         <v>0.6</v>
       </c>
-      <c r="O28" s="8">
-        <v>0</v>
-      </c>
       <c r="P28" s="8">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="Q28" s="8">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="R28" s="8">
         <v>0.25</v>
       </c>
       <c r="S28" s="8">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="T28" s="8">
         <v>0.5</v>
       </c>
       <c r="U28" s="8">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="V28" s="8">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="W28" s="8">
         <v>0.5</v>
       </c>
       <c r="X28" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.2">
+        <v>0.5</v>
+      </c>
+      <c r="Y28" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A29" s="9">
         <v>2022201037</v>
       </c>
-      <c r="B29" s="8">
+      <c r="B29" s="9">
+        <f>VLOOKUP(A29,[1]Planilha1!$B$2:$C$65,2,)</f>
+        <v>7.18</v>
+      </c>
+      <c r="C29" s="8">
         <v>0.85581699346405227</v>
       </c>
-      <c r="C29" s="8">
+      <c r="D29" s="8">
         <v>10.105816993464053</v>
       </c>
-      <c r="D29" s="8">
+      <c r="E29" s="8">
         <v>9.25</v>
       </c>
-      <c r="E29" s="8" t="s">
+      <c r="F29" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="F29" s="8">
+      <c r="G29" s="8">
         <v>0.60000000000000009</v>
       </c>
-      <c r="G29" s="8" t="s">
+      <c r="H29" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="H29" s="8">
-        <v>1</v>
-      </c>
-      <c r="I29" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="J29" s="8">
-        <v>1.2</v>
-      </c>
-      <c r="K29" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="L29" s="8">
-        <v>1</v>
-      </c>
-      <c r="M29" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="N29" s="8">
-        <v>1.2</v>
+      <c r="I29" s="8">
+        <v>1</v>
+      </c>
+      <c r="J29" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="K29" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="L29" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="M29" s="8">
+        <v>1</v>
+      </c>
+      <c r="N29" s="8" t="s">
+        <v>11</v>
       </c>
       <c r="O29" s="8">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="P29" s="8">
         <v>0.5</v>
       </c>
       <c r="Q29" s="8">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="R29" s="8">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="S29" s="8">
         <v>0.5</v>
       </c>
       <c r="T29" s="8">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="U29" s="8">
         <v>0.25</v>
       </c>
       <c r="V29" s="8">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="W29" s="8">
         <v>0.5</v>
@@ -2705,52 +3353,56 @@
       <c r="X29" s="8">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="30" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y29" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A30" s="7">
         <v>2021101896</v>
       </c>
-      <c r="B30" s="8">
+      <c r="B30" s="7">
+        <f>VLOOKUP(A30,[1]Planilha1!$B$2:$C$65,2,)</f>
+        <v>9.9</v>
+      </c>
+      <c r="C30" s="8">
         <v>0.39999999999999997</v>
       </c>
-      <c r="C30" s="8">
+      <c r="D30" s="8">
         <v>10.4</v>
       </c>
-      <c r="D30" s="8">
+      <c r="E30" s="8">
         <v>10</v>
       </c>
-      <c r="E30" s="8" t="s">
+      <c r="F30" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="F30" s="8">
+      <c r="G30" s="8">
         <v>0.60000000000000009</v>
       </c>
-      <c r="G30" s="8" t="s">
+      <c r="H30" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="H30" s="8">
-        <v>1</v>
-      </c>
-      <c r="I30" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="J30" s="8">
-        <v>1.2</v>
-      </c>
-      <c r="K30" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="L30" s="8">
-        <v>1</v>
-      </c>
-      <c r="M30" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="N30" s="8">
-        <v>1.2</v>
+      <c r="I30" s="8">
+        <v>1</v>
+      </c>
+      <c r="J30" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="K30" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="L30" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="M30" s="8">
+        <v>1</v>
+      </c>
+      <c r="N30" s="8" t="s">
+        <v>11</v>
       </c>
       <c r="O30" s="8">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="P30" s="8">
         <v>0.5</v>
@@ -2779,73 +3431,77 @@
       <c r="X30" s="8">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="31" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y30" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A31" s="9">
         <v>2022201042</v>
       </c>
-      <c r="B31" s="8">
+      <c r="B31" s="9">
+        <f>VLOOKUP(A31,[1]Planilha1!$B$2:$C$65,2,)</f>
+        <v>4.75</v>
+      </c>
+      <c r="C31" s="8">
         <v>0.92555555555555569</v>
       </c>
-      <c r="C31" s="8">
+      <c r="D31" s="8">
         <v>10.175555555555556</v>
       </c>
-      <c r="D31" s="8">
+      <c r="E31" s="8">
         <v>9.25</v>
       </c>
-      <c r="E31" s="8" t="s">
+      <c r="F31" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="F31" s="8">
+      <c r="G31" s="8">
         <v>0.60000000000000009</v>
       </c>
-      <c r="G31" s="8" t="s">
+      <c r="H31" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="H31" s="8">
-        <v>1</v>
-      </c>
-      <c r="I31" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="J31" s="8">
-        <v>1.2</v>
-      </c>
-      <c r="K31" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="L31" s="8">
-        <v>1</v>
-      </c>
-      <c r="M31" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="N31" s="8">
-        <v>1.2</v>
+      <c r="I31" s="8">
+        <v>1</v>
+      </c>
+      <c r="J31" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="K31" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="L31" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="M31" s="8">
+        <v>1</v>
+      </c>
+      <c r="N31" s="8" t="s">
+        <v>11</v>
       </c>
       <c r="O31" s="8">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="P31" s="8">
         <v>0.5</v>
       </c>
       <c r="Q31" s="8">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="R31" s="8">
         <v>0.25</v>
       </c>
       <c r="S31" s="8">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="T31" s="8">
         <v>0.5</v>
       </c>
       <c r="U31" s="8">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="V31" s="8">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="W31" s="8">
         <v>0.5</v>
@@ -2853,64 +3509,68 @@
       <c r="X31" s="8">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="32" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y31" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A32" s="7">
         <v>2020102888</v>
       </c>
-      <c r="B32" s="8">
+      <c r="B32" s="7">
+        <f>VLOOKUP(A32,[1]Planilha1!$B$2:$C$65,2,)</f>
+        <v>8.02</v>
+      </c>
+      <c r="C32" s="8">
         <v>0.75833333333333341</v>
       </c>
-      <c r="C32" s="8">
+      <c r="D32" s="8">
         <v>8.7083333333333339</v>
       </c>
-      <c r="D32" s="8">
+      <c r="E32" s="8">
         <v>7.95</v>
       </c>
-      <c r="E32" s="8" t="s">
+      <c r="F32" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="F32" s="8">
+      <c r="G32" s="8">
         <v>0.2</v>
       </c>
-      <c r="G32" s="8" t="s">
+      <c r="H32" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="H32" s="8">
+      <c r="I32" s="8">
         <v>0.60000000000000009</v>
       </c>
-      <c r="I32" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="J32" s="8">
-        <v>1.2</v>
-      </c>
-      <c r="K32" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="L32" s="8">
-        <v>1</v>
-      </c>
-      <c r="M32" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="N32" s="8">
-        <v>1.2</v>
+      <c r="J32" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="K32" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="L32" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="M32" s="8">
+        <v>1</v>
+      </c>
+      <c r="N32" s="8" t="s">
+        <v>11</v>
       </c>
       <c r="O32" s="8">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="P32" s="8">
         <v>0.5</v>
       </c>
       <c r="Q32" s="8">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="R32" s="8">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="S32" s="8">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="T32" s="8">
         <v>0.5</v>
@@ -2925,55 +3585,59 @@
         <v>0.5</v>
       </c>
       <c r="X32" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:24" x14ac:dyDescent="0.2">
+        <v>0.5</v>
+      </c>
+      <c r="Y32" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A33" s="9">
         <v>2024101765</v>
       </c>
-      <c r="B33" s="8">
+      <c r="B33" s="9">
+        <f>VLOOKUP(A33,[1]Planilha1!$B$2:$C$65,2,)</f>
+        <v>10</v>
+      </c>
+      <c r="C33" s="8">
         <v>0.99346405228758172</v>
       </c>
-      <c r="C33" s="8">
+      <c r="D33" s="8">
         <v>9.2934640522875824</v>
       </c>
-      <c r="D33" s="8">
+      <c r="E33" s="8">
         <v>8.3000000000000007</v>
       </c>
-      <c r="E33" s="8" t="s">
+      <c r="F33" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="F33" s="8">
+      <c r="G33" s="8">
         <v>0.60000000000000009</v>
       </c>
-      <c r="G33" s="8" t="s">
+      <c r="H33" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="H33" s="8">
-        <v>1</v>
-      </c>
-      <c r="I33" s="8" t="s">
+      <c r="I33" s="8">
+        <v>1</v>
+      </c>
+      <c r="J33" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="J33" s="8">
+      <c r="K33" s="8">
         <v>0.6</v>
       </c>
-      <c r="K33" s="8" t="s">
+      <c r="L33" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="L33" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="M33" s="8" t="s">
+      <c r="M33" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="N33" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="N33" s="8">
+      <c r="O33" s="8">
         <v>0.6</v>
       </c>
-      <c r="O33" s="8">
-        <v>0.5</v>
-      </c>
       <c r="P33" s="8">
         <v>0.5</v>
       </c>
@@ -3001,52 +3665,56 @@
       <c r="X33" s="8">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="34" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y33" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A34" s="7">
         <v>2022100612</v>
       </c>
-      <c r="B34" s="8">
+      <c r="B34" s="7">
+        <f>VLOOKUP(A34,[1]Planilha1!$B$2:$C$65,2,)</f>
+        <v>8</v>
+      </c>
+      <c r="C34" s="8">
         <v>0.533834422657952</v>
       </c>
-      <c r="C34" s="8">
+      <c r="D34" s="8">
         <v>9.5338344226579519</v>
       </c>
-      <c r="D34" s="8">
+      <c r="E34" s="8">
         <v>9</v>
       </c>
-      <c r="E34" s="8" t="s">
+      <c r="F34" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="F34" s="8">
+      <c r="G34" s="8">
         <v>0.60000000000000009</v>
       </c>
-      <c r="G34" s="8" t="s">
+      <c r="H34" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="H34" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="I34" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="J34" s="8">
-        <v>1.2</v>
-      </c>
-      <c r="K34" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="L34" s="8">
-        <v>1</v>
-      </c>
-      <c r="M34" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="N34" s="8">
-        <v>1.2</v>
+      <c r="I34" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="J34" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="K34" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="L34" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="M34" s="8">
+        <v>1</v>
+      </c>
+      <c r="N34" s="8" t="s">
+        <v>11</v>
       </c>
       <c r="O34" s="8">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="P34" s="8">
         <v>0.5</v>
@@ -3061,13 +3729,13 @@
         <v>0.5</v>
       </c>
       <c r="T34" s="8">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="U34" s="8">
         <v>0.25</v>
       </c>
       <c r="V34" s="8">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="W34" s="8">
         <v>0.5</v>
@@ -3075,52 +3743,56 @@
       <c r="X34" s="8">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="35" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y34" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A35" s="9">
         <v>2023101467</v>
       </c>
-      <c r="B35" s="8">
+      <c r="B35" s="9">
+        <f>VLOOKUP(A35,[1]Planilha1!$B$2:$C$65,2,)</f>
+        <v>7.95</v>
+      </c>
+      <c r="C35" s="8">
         <v>0.75816993464052285</v>
       </c>
-      <c r="C35" s="8">
+      <c r="D35" s="8">
         <v>8.0581699346405227</v>
       </c>
-      <c r="D35" s="8">
+      <c r="E35" s="8">
         <v>7.3</v>
       </c>
-      <c r="E35" s="8" t="s">
+      <c r="F35" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="F35" s="8">
+      <c r="G35" s="8">
         <v>0.60000000000000009</v>
       </c>
-      <c r="G35" s="8" t="s">
+      <c r="H35" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="H35" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="I35" s="8" t="s">
+      <c r="I35" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="J35" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="J35" s="8">
-        <v>0</v>
-      </c>
-      <c r="K35" s="8" t="s">
+      <c r="K35" s="8">
+        <v>0</v>
+      </c>
+      <c r="L35" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="L35" s="8">
-        <v>0</v>
-      </c>
-      <c r="M35" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="N35" s="8">
-        <v>1.2</v>
+      <c r="M35" s="8">
+        <v>0</v>
+      </c>
+      <c r="N35" s="8" t="s">
+        <v>11</v>
       </c>
       <c r="O35" s="8">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="P35" s="8">
         <v>0.5</v>
@@ -3149,52 +3821,56 @@
       <c r="X35" s="8">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="36" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y35" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="36" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A36" s="7">
         <v>2022100511</v>
       </c>
-      <c r="B36" s="8">
+      <c r="B36" s="7">
+        <f>VLOOKUP(A36,[1]Planilha1!$B$2:$C$65,2,)</f>
+        <v>6.79</v>
+      </c>
+      <c r="C36" s="8">
         <v>0.3202614379084967</v>
       </c>
-      <c r="C36" s="8">
+      <c r="D36" s="8">
         <v>6.670261437908497</v>
       </c>
-      <c r="D36" s="8">
+      <c r="E36" s="8">
         <v>6.35</v>
       </c>
-      <c r="E36" s="8" t="s">
+      <c r="F36" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="F36" s="8">
+      <c r="G36" s="8">
         <v>0.60000000000000009</v>
       </c>
-      <c r="G36" s="8" t="s">
+      <c r="H36" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="H36" s="8">
-        <v>1</v>
-      </c>
-      <c r="I36" s="8" t="s">
+      <c r="I36" s="8">
+        <v>1</v>
+      </c>
+      <c r="J36" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="J36" s="8">
-        <v>0</v>
-      </c>
-      <c r="K36" s="8" t="s">
+      <c r="K36" s="8">
+        <v>0</v>
+      </c>
+      <c r="L36" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="L36" s="8">
-        <v>0</v>
-      </c>
-      <c r="M36" s="8" t="s">
+      <c r="M36" s="8">
+        <v>0</v>
+      </c>
+      <c r="N36" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="N36" s="8">
-        <v>0</v>
-      </c>
       <c r="O36" s="8">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="P36" s="8">
         <v>0.5</v>
@@ -3212,10 +3888,10 @@
         <v>0.5</v>
       </c>
       <c r="U36" s="8">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="V36" s="8">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="W36" s="8">
         <v>0.5</v>
@@ -3223,52 +3899,56 @@
       <c r="X36" s="8">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="37" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y36" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A37" s="9">
         <v>2023200147</v>
       </c>
-      <c r="B37" s="8">
+      <c r="B37" s="9">
+        <f>VLOOKUP(A37,[1]Planilha1!$B$2:$C$65,2,)</f>
+        <v>7.2</v>
+      </c>
+      <c r="C37" s="8">
         <v>0.93718954248366004</v>
       </c>
-      <c r="C37" s="8">
+      <c r="D37" s="8">
         <v>10.937189542483662</v>
       </c>
-      <c r="D37" s="8">
+      <c r="E37" s="8">
         <v>10</v>
       </c>
-      <c r="E37" s="8" t="s">
+      <c r="F37" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="F37" s="8">
+      <c r="G37" s="8">
         <v>0.60000000000000009</v>
       </c>
-      <c r="G37" s="8" t="s">
+      <c r="H37" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="H37" s="8">
-        <v>1</v>
-      </c>
-      <c r="I37" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="J37" s="8">
-        <v>1.2</v>
-      </c>
-      <c r="K37" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="L37" s="8">
-        <v>1</v>
-      </c>
-      <c r="M37" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="N37" s="8">
-        <v>1.2</v>
+      <c r="I37" s="8">
+        <v>1</v>
+      </c>
+      <c r="J37" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="K37" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="L37" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="M37" s="8">
+        <v>1</v>
+      </c>
+      <c r="N37" s="8" t="s">
+        <v>11</v>
       </c>
       <c r="O37" s="8">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="P37" s="8">
         <v>0.5</v>
@@ -3297,61 +3977,65 @@
       <c r="X37" s="8">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="38" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y37" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="38" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A38" s="7">
         <v>2023100776</v>
       </c>
-      <c r="B38" s="8">
+      <c r="B38" s="7">
+        <f>VLOOKUP(A38,[1]Planilha1!$B$2:$C$65,2,)</f>
+        <v>10</v>
+      </c>
+      <c r="C38" s="8">
         <v>0.78388888888888875</v>
       </c>
-      <c r="C38" s="8">
+      <c r="D38" s="8">
         <v>10.283888888888889</v>
       </c>
-      <c r="D38" s="8">
+      <c r="E38" s="8">
         <v>9.5</v>
       </c>
-      <c r="E38" s="8" t="s">
+      <c r="F38" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="F38" s="8">
+      <c r="G38" s="8">
         <v>0.60000000000000009</v>
       </c>
-      <c r="G38" s="8" t="s">
+      <c r="H38" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="H38" s="8">
-        <v>1</v>
-      </c>
-      <c r="I38" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="J38" s="8">
-        <v>1.2</v>
-      </c>
-      <c r="K38" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="L38" s="8">
-        <v>1</v>
-      </c>
-      <c r="M38" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="N38" s="8">
-        <v>1.2</v>
+      <c r="I38" s="8">
+        <v>1</v>
+      </c>
+      <c r="J38" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="K38" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="L38" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="M38" s="8">
+        <v>1</v>
+      </c>
+      <c r="N38" s="8" t="s">
+        <v>11</v>
       </c>
       <c r="O38" s="8">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="P38" s="8">
         <v>0.5</v>
       </c>
       <c r="Q38" s="8">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="R38" s="8">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="S38" s="8">
         <v>0.5</v>
@@ -3360,10 +4044,10 @@
         <v>0.5</v>
       </c>
       <c r="U38" s="8">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="V38" s="8">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="W38" s="8">
         <v>0.5</v>
@@ -3371,52 +4055,56 @@
       <c r="X38" s="8">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="39" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y38" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="39" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A39" s="9">
         <v>2024101158</v>
       </c>
-      <c r="B39" s="8">
+      <c r="B39" s="9">
+        <f>VLOOKUP(A39,[1]Planilha1!$B$2:$C$65,2,)</f>
+        <v>9.6</v>
+      </c>
+      <c r="C39" s="8">
         <v>0.96333333333333349</v>
       </c>
-      <c r="C39" s="8">
+      <c r="D39" s="8">
         <v>10.963333333333335</v>
       </c>
-      <c r="D39" s="8">
+      <c r="E39" s="8">
         <v>10</v>
       </c>
-      <c r="E39" s="8" t="s">
+      <c r="F39" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="F39" s="8">
+      <c r="G39" s="8">
         <v>0.60000000000000009</v>
       </c>
-      <c r="G39" s="8" t="s">
+      <c r="H39" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="H39" s="8">
-        <v>1</v>
-      </c>
-      <c r="I39" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="J39" s="8">
-        <v>1.2</v>
-      </c>
-      <c r="K39" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="L39" s="8">
-        <v>1</v>
-      </c>
-      <c r="M39" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="N39" s="8">
-        <v>1.2</v>
+      <c r="I39" s="8">
+        <v>1</v>
+      </c>
+      <c r="J39" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="K39" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="L39" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="M39" s="8">
+        <v>1</v>
+      </c>
+      <c r="N39" s="8" t="s">
+        <v>11</v>
       </c>
       <c r="O39" s="8">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="P39" s="8">
         <v>0.5</v>
@@ -3445,52 +4133,56 @@
       <c r="X39" s="8">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="40" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y39" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="40" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A40" s="7">
         <v>2024101773</v>
       </c>
-      <c r="B40" s="8">
+      <c r="B40" s="7">
+        <f>VLOOKUP(A40,[1]Planilha1!$B$2:$C$65,2,)</f>
+        <v>9.5500000000000007</v>
+      </c>
+      <c r="C40" s="8">
         <v>0.79666666666666663</v>
       </c>
-      <c r="C40" s="8">
+      <c r="D40" s="8">
         <v>10.546666666666667</v>
       </c>
-      <c r="D40" s="8">
+      <c r="E40" s="8">
         <v>9.75</v>
       </c>
-      <c r="E40" s="8" t="s">
+      <c r="F40" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="F40" s="8">
+      <c r="G40" s="8">
         <v>0.60000000000000009</v>
       </c>
-      <c r="G40" s="8" t="s">
+      <c r="H40" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="H40" s="8">
-        <v>1</v>
-      </c>
-      <c r="I40" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="J40" s="8">
-        <v>1.2</v>
-      </c>
-      <c r="K40" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="L40" s="8">
-        <v>1</v>
-      </c>
-      <c r="M40" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="N40" s="8">
-        <v>1.2</v>
+      <c r="I40" s="8">
+        <v>1</v>
+      </c>
+      <c r="J40" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="K40" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="L40" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="M40" s="8">
+        <v>1</v>
+      </c>
+      <c r="N40" s="8" t="s">
+        <v>11</v>
       </c>
       <c r="O40" s="8">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="P40" s="8">
         <v>0.5</v>
@@ -3508,10 +4200,10 @@
         <v>0.5</v>
       </c>
       <c r="U40" s="8">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="V40" s="8">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="W40" s="8">
         <v>0.5</v>
@@ -3519,52 +4211,56 @@
       <c r="X40" s="8">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="41" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y40" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="41" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A41" s="9">
         <v>2023100068</v>
       </c>
-      <c r="B41" s="8">
+      <c r="B41" s="9">
+        <f>VLOOKUP(A41,[1]Planilha1!$B$2:$C$65,2,)</f>
+        <v>6.56</v>
+      </c>
+      <c r="C41" s="8">
         <v>0.32407407407407407</v>
       </c>
-      <c r="C41" s="8">
+      <c r="D41" s="8">
         <v>8.924074074074074</v>
       </c>
-      <c r="D41" s="8">
+      <c r="E41" s="8">
         <v>8.6000000000000014</v>
       </c>
-      <c r="E41" s="8" t="s">
+      <c r="F41" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="F41" s="8">
+      <c r="G41" s="8">
         <v>0.60000000000000009</v>
       </c>
-      <c r="G41" s="8" t="s">
+      <c r="H41" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="H41" s="8">
+      <c r="I41" s="8">
         <v>0.70000000000000007</v>
       </c>
-      <c r="I41" s="8" t="s">
+      <c r="J41" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="J41" s="8">
+      <c r="K41" s="8">
         <v>0.6</v>
       </c>
-      <c r="K41" s="8" t="s">
+      <c r="L41" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="L41" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="M41" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="N41" s="8">
-        <v>1.2</v>
+      <c r="M41" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="N41" s="8" t="s">
+        <v>11</v>
       </c>
       <c r="O41" s="8">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="P41" s="8">
         <v>0.5</v>
@@ -3593,58 +4289,62 @@
       <c r="X41" s="8">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="42" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y41" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="42" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A42" s="7">
         <v>2023200790</v>
       </c>
-      <c r="B42" s="8">
+      <c r="B42" s="7">
+        <f>VLOOKUP(A42,[1]Planilha1!$B$2:$C$65,2,)</f>
+        <v>7.74</v>
+      </c>
+      <c r="C42" s="8">
         <v>0.85222222222222221</v>
       </c>
-      <c r="C42" s="8">
+      <c r="D42" s="8">
         <v>6.2522222222222217</v>
       </c>
-      <c r="D42" s="8">
+      <c r="E42" s="8">
         <v>5.3999999999999995</v>
       </c>
-      <c r="E42" s="8" t="s">
+      <c r="F42" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="F42" s="8">
+      <c r="G42" s="8">
         <v>0.60000000000000009</v>
       </c>
-      <c r="G42" s="8" t="s">
+      <c r="H42" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="H42" s="8">
-        <v>1</v>
-      </c>
-      <c r="I42" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="J42" s="8">
-        <v>1.2</v>
-      </c>
-      <c r="K42" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="L42" s="8">
-        <v>1</v>
-      </c>
-      <c r="M42" s="8" t="s">
+      <c r="I42" s="8">
+        <v>1</v>
+      </c>
+      <c r="J42" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="K42" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="L42" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="M42" s="8">
+        <v>1</v>
+      </c>
+      <c r="N42" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="N42" s="8">
+      <c r="O42" s="8">
         <v>0.6</v>
       </c>
-      <c r="O42" s="8">
-        <v>0.5</v>
-      </c>
       <c r="P42" s="8">
         <v>0.5</v>
       </c>
       <c r="Q42" s="8">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="R42" s="8">
         <v>0</v>
@@ -3667,52 +4367,56 @@
       <c r="X42" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y42" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A43" s="9">
         <v>2022200719</v>
       </c>
-      <c r="B43" s="8">
+      <c r="B43" s="9">
+        <f>VLOOKUP(A43,[1]Planilha1!$B$2:$C$65,2,)</f>
+        <v>7.25</v>
+      </c>
+      <c r="C43" s="8">
         <v>0.17222222222222222</v>
       </c>
-      <c r="C43" s="8">
+      <c r="D43" s="8">
         <v>9.9222222222222225</v>
       </c>
-      <c r="D43" s="8">
+      <c r="E43" s="8">
         <v>9.75</v>
       </c>
-      <c r="E43" s="8" t="s">
+      <c r="F43" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="F43" s="8">
+      <c r="G43" s="8">
         <v>0.60000000000000009</v>
       </c>
-      <c r="G43" s="8" t="s">
+      <c r="H43" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="H43" s="8">
-        <v>1</v>
-      </c>
-      <c r="I43" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="J43" s="8">
-        <v>1.2</v>
-      </c>
-      <c r="K43" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="L43" s="8">
-        <v>1</v>
-      </c>
-      <c r="M43" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="N43" s="8">
-        <v>1.2</v>
+      <c r="I43" s="8">
+        <v>1</v>
+      </c>
+      <c r="J43" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="K43" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="L43" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="M43" s="8">
+        <v>1</v>
+      </c>
+      <c r="N43" s="8" t="s">
+        <v>11</v>
       </c>
       <c r="O43" s="8">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="P43" s="8">
         <v>0.5</v>
@@ -3730,10 +4434,10 @@
         <v>0.5</v>
       </c>
       <c r="U43" s="8">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="V43" s="8">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="W43" s="8">
         <v>0.5</v>
@@ -3741,73 +4445,77 @@
       <c r="X43" s="8">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="44" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y43" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="44" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A44" s="8">
         <v>2025201178</v>
       </c>
       <c r="B44" s="8">
+        <f>VLOOKUP(A44,[1]Planilha1!$B$2:$C$65,2,)</f>
+        <v>5.52</v>
+      </c>
+      <c r="C44" s="8">
         <v>0.65230936819172103</v>
       </c>
-      <c r="C44" s="8">
+      <c r="D44" s="8">
         <v>6.7023093681917212</v>
       </c>
-      <c r="D44" s="8">
+      <c r="E44" s="8">
         <v>6.05</v>
       </c>
-      <c r="E44" s="8" t="s">
+      <c r="F44" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="F44" s="8">
+      <c r="G44" s="8">
         <v>0.60000000000000009</v>
       </c>
-      <c r="G44" s="8" t="s">
+      <c r="H44" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="H44" s="8">
-        <v>1</v>
-      </c>
-      <c r="I44" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="J44" s="8">
-        <v>1.2</v>
-      </c>
-      <c r="K44" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="L44" s="8">
-        <v>1</v>
-      </c>
-      <c r="M44" s="8" t="s">
+      <c r="I44" s="8">
+        <v>1</v>
+      </c>
+      <c r="J44" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="K44" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="L44" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="M44" s="8">
+        <v>1</v>
+      </c>
+      <c r="N44" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="N44" s="8">
-        <v>0</v>
-      </c>
       <c r="O44" s="8">
         <v>0</v>
       </c>
       <c r="P44" s="8">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="Q44" s="8">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="R44" s="8">
         <v>0.25</v>
       </c>
       <c r="S44" s="8">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="T44" s="8">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="U44" s="8">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="V44" s="8">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="W44" s="8">
         <v>0</v>
@@ -3815,53 +4523,57 @@
       <c r="X44" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y44" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A45" s="9">
         <v>2024101775</v>
       </c>
-      <c r="B45" s="8">
+      <c r="B45" s="9">
+        <f>VLOOKUP(A45,[1]Planilha1!$B$2:$C$65,2,)</f>
+        <v>9.15</v>
+      </c>
+      <c r="C45" s="8">
         <v>0.80137254901960775</v>
       </c>
-      <c r="C45" s="8">
+      <c r="D45" s="8">
         <v>9.9513725490196077</v>
       </c>
-      <c r="D45" s="8">
+      <c r="E45" s="8">
         <v>9.1499999999999986</v>
       </c>
-      <c r="E45" s="8" t="s">
+      <c r="F45" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="F45" s="8">
+      <c r="G45" s="8">
         <v>0.60000000000000009</v>
       </c>
-      <c r="G45" s="8" t="s">
+      <c r="H45" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="H45" s="8">
-        <v>1</v>
-      </c>
-      <c r="I45" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="J45" s="8">
-        <v>1.2</v>
-      </c>
-      <c r="K45" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="L45" s="8">
-        <v>1</v>
-      </c>
-      <c r="M45" s="8" t="s">
+      <c r="I45" s="8">
+        <v>1</v>
+      </c>
+      <c r="J45" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="K45" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="L45" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="M45" s="8">
+        <v>1</v>
+      </c>
+      <c r="N45" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="N45" s="8">
+      <c r="O45" s="8">
         <v>0.6</v>
       </c>
-      <c r="O45" s="8">
-        <v>0.5</v>
-      </c>
       <c r="P45" s="8">
         <v>0.5</v>
       </c>
@@ -3878,10 +4590,10 @@
         <v>0.5</v>
       </c>
       <c r="U45" s="8">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="V45" s="8">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="W45" s="8">
         <v>0.5</v>
@@ -3889,64 +4601,68 @@
       <c r="X45" s="8">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="46" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y45" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A46" s="7">
         <v>2024103187</v>
       </c>
-      <c r="B46" s="8">
+      <c r="B46" s="7">
+        <f>VLOOKUP(A46,[1]Planilha1!$B$2:$C$65,2,)</f>
+        <v>8.7100000000000009</v>
+      </c>
+      <c r="C46" s="8">
         <v>0.59222222222222221</v>
       </c>
-      <c r="C46" s="8">
+      <c r="D46" s="8">
         <v>8.492222222222221</v>
       </c>
-      <c r="D46" s="8">
+      <c r="E46" s="8">
         <v>7.9</v>
       </c>
-      <c r="E46" s="8" t="s">
+      <c r="F46" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="F46" s="8">
+      <c r="G46" s="8">
         <v>0.60000000000000009</v>
       </c>
-      <c r="G46" s="8" t="s">
+      <c r="H46" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="H46" s="8">
-        <v>1</v>
-      </c>
-      <c r="I46" s="8" t="s">
+      <c r="I46" s="8">
+        <v>1</v>
+      </c>
+      <c r="J46" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="J46" s="8">
+      <c r="K46" s="8">
         <v>0.6</v>
       </c>
-      <c r="K46" s="8" t="s">
+      <c r="L46" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="L46" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="M46" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="N46" s="8">
-        <v>1.2</v>
+      <c r="M46" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="N46" s="8" t="s">
+        <v>11</v>
       </c>
       <c r="O46" s="8">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="P46" s="8">
         <v>0.5</v>
       </c>
       <c r="Q46" s="8">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="R46" s="8">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="S46" s="8">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="T46" s="8">
         <v>0.25</v>
@@ -3955,7 +4671,7 @@
         <v>0.25</v>
       </c>
       <c r="V46" s="8">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="W46" s="8">
         <v>0.5</v>
@@ -3963,64 +4679,68 @@
       <c r="X46" s="8">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="47" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y46" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="47" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A47" s="9">
         <v>2023102386</v>
       </c>
-      <c r="B47" s="8">
+      <c r="B47" s="9">
+        <f>VLOOKUP(A47,[1]Planilha1!$B$2:$C$65,2,)</f>
+        <v>5.86</v>
+      </c>
+      <c r="C47" s="8">
         <v>0.55148148148148135</v>
       </c>
-      <c r="C47" s="8">
+      <c r="D47" s="8">
         <v>9.5514814814814812</v>
       </c>
-      <c r="D47" s="8">
+      <c r="E47" s="8">
         <v>9</v>
       </c>
-      <c r="E47" s="8" t="s">
+      <c r="F47" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="F47" s="8">
+      <c r="G47" s="8">
         <v>0.60000000000000009</v>
       </c>
-      <c r="G47" s="8" t="s">
+      <c r="H47" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="H47" s="8">
-        <v>1</v>
-      </c>
-      <c r="I47" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="J47" s="8">
-        <v>1.2</v>
-      </c>
-      <c r="K47" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="L47" s="8">
-        <v>1</v>
-      </c>
-      <c r="M47" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="N47" s="8">
-        <v>1.2</v>
+      <c r="I47" s="8">
+        <v>1</v>
+      </c>
+      <c r="J47" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="K47" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="L47" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="M47" s="8">
+        <v>1</v>
+      </c>
+      <c r="N47" s="8" t="s">
+        <v>11</v>
       </c>
       <c r="O47" s="8">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="P47" s="8">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="Q47" s="8">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="R47" s="8">
         <v>0.25</v>
       </c>
       <c r="S47" s="8">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="T47" s="8">
         <v>0.5</v>
@@ -4037,53 +4757,57 @@
       <c r="X47" s="8">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="48" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y47" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="48" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A48" s="7">
         <v>2020101654</v>
       </c>
-      <c r="B48" s="8">
+      <c r="B48" s="7">
+        <f>VLOOKUP(A48,[1]Planilha1!$B$2:$C$65,2,)</f>
+        <v>4.8</v>
+      </c>
+      <c r="C48" s="8">
         <v>0.22222222222222221</v>
       </c>
-      <c r="C48" s="8">
+      <c r="D48" s="8">
         <v>8.1222222222222236</v>
       </c>
-      <c r="D48" s="8">
+      <c r="E48" s="8">
         <v>7.9</v>
       </c>
-      <c r="E48" s="8" t="s">
+      <c r="F48" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="F48" s="8">
+      <c r="G48" s="8">
         <v>0.60000000000000009</v>
       </c>
-      <c r="G48" s="8" t="s">
+      <c r="H48" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="H48" s="8">
+      <c r="I48" s="8">
         <v>0.60000000000000009</v>
       </c>
-      <c r="I48" s="8" t="s">
+      <c r="J48" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="J48" s="8">
+      <c r="K48" s="8">
         <v>0.6</v>
       </c>
-      <c r="K48" s="8" t="s">
+      <c r="L48" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="L48" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="M48" s="8" t="s">
+      <c r="M48" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="N48" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="N48" s="8">
+      <c r="O48" s="8">
         <v>0.6</v>
       </c>
-      <c r="O48" s="8">
-        <v>0.5</v>
-      </c>
       <c r="P48" s="8">
         <v>0.5</v>
       </c>
@@ -4111,61 +4835,65 @@
       <c r="X48" s="8">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="49" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y48" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="49" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A49" s="9">
         <v>2022201082</v>
       </c>
-      <c r="B49" s="8">
+      <c r="B49" s="9">
+        <f>VLOOKUP(A49,[1]Planilha1!$B$2:$C$65,2,)</f>
+        <v>6.96</v>
+      </c>
+      <c r="C49" s="8">
         <v>0.8574074074074074</v>
       </c>
-      <c r="C49" s="8">
+      <c r="D49" s="8">
         <v>10.507407407407408</v>
       </c>
-      <c r="D49" s="8">
+      <c r="E49" s="8">
         <v>9.65</v>
       </c>
-      <c r="E49" s="8" t="s">
+      <c r="F49" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="F49" s="8">
+      <c r="G49" s="8">
         <v>0.60000000000000009</v>
       </c>
-      <c r="G49" s="8" t="s">
+      <c r="H49" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="H49" s="8">
+      <c r="I49" s="8">
         <v>0.9</v>
       </c>
-      <c r="I49" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="J49" s="8">
-        <v>1.2</v>
-      </c>
-      <c r="K49" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="L49" s="8">
-        <v>1</v>
-      </c>
-      <c r="M49" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="N49" s="8">
-        <v>1.2</v>
+      <c r="J49" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="K49" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="L49" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="M49" s="8">
+        <v>1</v>
+      </c>
+      <c r="N49" s="8" t="s">
+        <v>11</v>
       </c>
       <c r="O49" s="8">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="P49" s="8">
         <v>0.5</v>
       </c>
       <c r="Q49" s="8">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="R49" s="8">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="S49" s="8">
         <v>0.5</v>
@@ -4185,55 +4913,59 @@
       <c r="X49" s="8">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="50" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y49" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="50" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A50" s="7">
         <v>2024101769</v>
       </c>
-      <c r="B50" s="8">
+      <c r="B50" s="7">
+        <f>VLOOKUP(A50,[1]Planilha1!$B$2:$C$65,2,)</f>
+        <v>7.3</v>
+      </c>
+      <c r="C50" s="8">
         <v>0.92555555555555569</v>
       </c>
-      <c r="C50" s="8">
+      <c r="D50" s="8">
         <v>9.8255555555555567</v>
       </c>
-      <c r="D50" s="8">
+      <c r="E50" s="8">
         <v>8.8999999999999986</v>
       </c>
-      <c r="E50" s="8" t="s">
+      <c r="F50" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="F50" s="8">
+      <c r="G50" s="8">
         <v>0.60000000000000009</v>
       </c>
-      <c r="G50" s="8" t="s">
+      <c r="H50" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="H50" s="8">
-        <v>1</v>
-      </c>
-      <c r="I50" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="J50" s="8">
-        <v>1.2</v>
-      </c>
-      <c r="K50" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="L50" s="8">
-        <v>1</v>
-      </c>
-      <c r="M50" s="8" t="s">
+      <c r="I50" s="8">
+        <v>1</v>
+      </c>
+      <c r="J50" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="K50" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="L50" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="M50" s="8">
+        <v>1</v>
+      </c>
+      <c r="N50" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="N50" s="8">
+      <c r="O50" s="8">
         <v>0.6</v>
       </c>
-      <c r="O50" s="8">
-        <v>0</v>
-      </c>
       <c r="P50" s="8">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="Q50" s="8">
         <v>0.5</v>
@@ -4259,58 +4991,62 @@
       <c r="X50" s="8">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="51" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y50" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="51" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A51" s="9">
         <v>2024101154</v>
       </c>
-      <c r="B51" s="8">
+      <c r="B51" s="9">
+        <f>VLOOKUP(A51,[1]Planilha1!$B$2:$C$65,2,)</f>
+        <v>9.15</v>
+      </c>
+      <c r="C51" s="8">
         <v>0.48055555555555551</v>
       </c>
-      <c r="C51" s="8">
+      <c r="D51" s="8">
         <v>8.530555555555555</v>
       </c>
-      <c r="D51" s="8">
+      <c r="E51" s="8">
         <v>8.0500000000000007</v>
       </c>
-      <c r="E51" s="8" t="s">
+      <c r="F51" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="F51" s="8">
+      <c r="G51" s="8">
         <v>0.60000000000000009</v>
       </c>
-      <c r="G51" s="8" t="s">
+      <c r="H51" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="H51" s="8">
-        <v>1</v>
-      </c>
-      <c r="I51" s="8" t="s">
+      <c r="I51" s="8">
+        <v>1</v>
+      </c>
+      <c r="J51" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="J51" s="8">
+      <c r="K51" s="8">
         <v>0.6</v>
       </c>
-      <c r="K51" s="8" t="s">
+      <c r="L51" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="L51" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="M51" s="8" t="s">
+      <c r="M51" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="N51" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="N51" s="8">
+      <c r="O51" s="8">
         <v>0.6</v>
       </c>
-      <c r="O51" s="8">
-        <v>0.5</v>
-      </c>
       <c r="P51" s="8">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="Q51" s="8">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="R51" s="8">
         <v>0.5</v>
@@ -4333,61 +5069,65 @@
       <c r="X51" s="8">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="52" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y51" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="52" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A52" s="7">
         <v>2022102045</v>
       </c>
-      <c r="B52" s="8">
+      <c r="B52" s="7">
+        <f>VLOOKUP(A52,[1]Planilha1!$B$2:$C$65,2,)</f>
+        <v>9.36</v>
+      </c>
+      <c r="C52" s="8">
         <v>0.61055555555555552</v>
       </c>
-      <c r="C52" s="8">
+      <c r="D52" s="8">
         <v>8.4105555555555558</v>
       </c>
-      <c r="D52" s="8">
+      <c r="E52" s="8">
         <v>7.8000000000000007</v>
       </c>
-      <c r="E52" s="8" t="s">
+      <c r="F52" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="F52" s="8">
+      <c r="G52" s="8">
         <v>0.60000000000000009</v>
       </c>
-      <c r="G52" s="8" t="s">
+      <c r="H52" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="H52" s="8">
-        <v>1</v>
-      </c>
-      <c r="I52" s="8" t="s">
+      <c r="I52" s="8">
+        <v>1</v>
+      </c>
+      <c r="J52" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="J52" s="8">
+      <c r="K52" s="8">
         <v>0.6</v>
       </c>
-      <c r="K52" s="8" t="s">
+      <c r="L52" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="L52" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="M52" s="8" t="s">
+      <c r="M52" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="N52" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="N52" s="8">
+      <c r="O52" s="8">
         <v>0.6</v>
       </c>
-      <c r="O52" s="8">
-        <v>0.5</v>
-      </c>
       <c r="P52" s="8">
         <v>0.5</v>
       </c>
       <c r="Q52" s="8">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="R52" s="8">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="S52" s="8">
         <v>0.5</v>
@@ -4396,10 +5136,10 @@
         <v>0.5</v>
       </c>
       <c r="U52" s="8">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="V52" s="8">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="W52" s="8">
         <v>0.5</v>
@@ -4407,73 +5147,77 @@
       <c r="X52" s="8">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="53" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y52" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="53" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A53" s="9">
         <v>2023101690</v>
       </c>
-      <c r="B53" s="8">
+      <c r="B53" s="9">
+        <f>VLOOKUP(A53,[1]Planilha1!$B$2:$C$65,2,)</f>
+        <v>3.15</v>
+      </c>
+      <c r="C53" s="8">
         <v>0.31481481481481477</v>
       </c>
-      <c r="C53" s="8">
+      <c r="D53" s="8">
         <v>9.0648148148148149</v>
       </c>
-      <c r="D53" s="8">
+      <c r="E53" s="8">
         <v>8.75</v>
       </c>
-      <c r="E53" s="8" t="s">
+      <c r="F53" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="F53" s="8">
+      <c r="G53" s="8">
         <v>0.60000000000000009</v>
       </c>
-      <c r="G53" s="8" t="s">
+      <c r="H53" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="H53" s="8">
-        <v>1</v>
-      </c>
-      <c r="I53" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="J53" s="8">
-        <v>1.2</v>
-      </c>
-      <c r="K53" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="L53" s="8">
-        <v>1</v>
-      </c>
-      <c r="M53" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="N53" s="8">
-        <v>1.2</v>
+      <c r="I53" s="8">
+        <v>1</v>
+      </c>
+      <c r="J53" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="K53" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="L53" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="M53" s="8">
+        <v>1</v>
+      </c>
+      <c r="N53" s="8" t="s">
+        <v>11</v>
       </c>
       <c r="O53" s="8">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="P53" s="8">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="Q53" s="8">
         <v>0.5</v>
       </c>
       <c r="R53" s="8">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="S53" s="8">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="T53" s="8">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="U53" s="8">
         <v>0.25</v>
       </c>
       <c r="V53" s="8">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="W53" s="8">
         <v>0.5</v>
@@ -4481,67 +5225,71 @@
       <c r="X53" s="8">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="54" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y53" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="54" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A54" s="7">
         <v>2023100954</v>
       </c>
-      <c r="B54" s="8">
+      <c r="B54" s="7">
+        <f>VLOOKUP(A54,[1]Planilha1!$B$2:$C$65,2,)</f>
+        <v>3.12</v>
+      </c>
+      <c r="C54" s="8">
         <v>0.32407407407407407</v>
       </c>
-      <c r="C54" s="8">
+      <c r="D54" s="8">
         <v>8.7240740740740748</v>
       </c>
-      <c r="D54" s="8">
+      <c r="E54" s="8">
         <v>8.3999999999999986</v>
       </c>
-      <c r="E54" s="8" t="s">
+      <c r="F54" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="F54" s="8">
+      <c r="G54" s="8">
         <v>0.60000000000000009</v>
       </c>
-      <c r="G54" s="8" t="s">
+      <c r="H54" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="H54" s="8">
-        <v>1</v>
-      </c>
-      <c r="I54" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="J54" s="8">
-        <v>1.2</v>
-      </c>
-      <c r="K54" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="L54" s="8">
-        <v>1</v>
-      </c>
-      <c r="M54" s="8" t="s">
+      <c r="I54" s="8">
+        <v>1</v>
+      </c>
+      <c r="J54" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="K54" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="L54" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="M54" s="8">
+        <v>1</v>
+      </c>
+      <c r="N54" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="N54" s="8">
+      <c r="O54" s="8">
         <v>0.6</v>
       </c>
-      <c r="O54" s="8">
-        <v>0</v>
-      </c>
       <c r="P54" s="8">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="Q54" s="8">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="R54" s="8">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="S54" s="8">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="T54" s="8">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="U54" s="8">
         <v>0.5</v>
@@ -4555,52 +5303,56 @@
       <c r="X54" s="8">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="55" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y54" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="55" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A55" s="9">
         <v>2024202997</v>
       </c>
-      <c r="B55" s="8">
+      <c r="B55" s="9">
+        <f>VLOOKUP(A55,[1]Planilha1!$B$2:$C$65,2,)</f>
+        <v>2.6</v>
+      </c>
+      <c r="C55" s="8">
         <v>0.49919389978213513</v>
       </c>
-      <c r="C55" s="8">
+      <c r="D55" s="8">
         <v>8.1491938997821354</v>
       </c>
-      <c r="D55" s="8">
+      <c r="E55" s="8">
         <v>7.65</v>
       </c>
-      <c r="E55" s="8" t="s">
+      <c r="F55" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="F55" s="8">
-        <v>0</v>
-      </c>
-      <c r="G55" s="8" t="s">
+      <c r="G55" s="8">
+        <v>0</v>
+      </c>
+      <c r="H55" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="H55" s="8">
-        <v>1</v>
-      </c>
-      <c r="I55" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="J55" s="8">
-        <v>1.2</v>
-      </c>
-      <c r="K55" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="L55" s="8">
-        <v>1</v>
-      </c>
-      <c r="M55" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="N55" s="8">
-        <v>1.2</v>
+      <c r="I55" s="8">
+        <v>1</v>
+      </c>
+      <c r="J55" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="K55" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="L55" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="M55" s="8">
+        <v>1</v>
+      </c>
+      <c r="N55" s="8" t="s">
+        <v>11</v>
       </c>
       <c r="O55" s="8">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="P55" s="8">
         <v>0.5</v>
@@ -4609,10 +5361,10 @@
         <v>0.5</v>
       </c>
       <c r="R55" s="8">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="S55" s="8">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="T55" s="8">
         <v>0.5</v>
@@ -4621,7 +5373,7 @@
         <v>0.5</v>
       </c>
       <c r="V55" s="8">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="W55" s="8">
         <v>0</v>
@@ -4629,64 +5381,68 @@
       <c r="X55" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="56" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y55" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A56" s="7">
         <v>2020101573</v>
       </c>
-      <c r="B56" s="8">
+      <c r="B56" s="7">
+        <f>VLOOKUP(A56,[1]Planilha1!$B$2:$C$65,2,)</f>
+        <v>3.45</v>
+      </c>
+      <c r="C56" s="8">
         <v>0.43333333333333329</v>
       </c>
-      <c r="C56" s="8">
+      <c r="D56" s="8">
         <v>5.0333333333333332</v>
       </c>
-      <c r="D56" s="8">
+      <c r="E56" s="8">
         <v>4.5999999999999996</v>
       </c>
-      <c r="E56" s="8" t="s">
+      <c r="F56" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="F56" s="8">
+      <c r="G56" s="8">
         <v>0.4</v>
       </c>
-      <c r="G56" s="8" t="s">
+      <c r="H56" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="H56" s="8">
-        <v>1</v>
-      </c>
-      <c r="I56" s="8" t="s">
+      <c r="I56" s="8">
+        <v>1</v>
+      </c>
+      <c r="J56" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="J56" s="8">
+      <c r="K56" s="8">
         <v>0.6</v>
       </c>
-      <c r="K56" s="8" t="s">
+      <c r="L56" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="L56" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="M56" s="8" t="s">
+      <c r="M56" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="N56" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="N56" s="8">
+      <c r="O56" s="8">
         <v>0.6</v>
       </c>
-      <c r="O56" s="8">
-        <v>0.5</v>
-      </c>
       <c r="P56" s="8">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="Q56" s="8">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="R56" s="8">
         <v>0</v>
       </c>
       <c r="S56" s="8">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="T56" s="8">
         <v>0.25</v>
@@ -4695,7 +5451,7 @@
         <v>0.25</v>
       </c>
       <c r="V56" s="8">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="W56" s="8">
         <v>0</v>
@@ -4703,52 +5459,56 @@
       <c r="X56" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="57" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y56" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A57" s="9">
         <v>2024101785</v>
       </c>
-      <c r="B57" s="8">
+      <c r="B57" s="9">
+        <f>VLOOKUP(A57,[1]Planilha1!$B$2:$C$65,2,)</f>
+        <v>6.86</v>
+      </c>
+      <c r="C57" s="8">
         <v>0.69679738562091498</v>
       </c>
-      <c r="C57" s="8">
+      <c r="D57" s="8">
         <v>10.446797385620915</v>
       </c>
-      <c r="D57" s="8">
+      <c r="E57" s="8">
         <v>9.75</v>
       </c>
-      <c r="E57" s="8" t="s">
+      <c r="F57" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="F57" s="8">
+      <c r="G57" s="8">
         <v>0.60000000000000009</v>
       </c>
-      <c r="G57" s="8" t="s">
+      <c r="H57" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="H57" s="8">
-        <v>1</v>
-      </c>
-      <c r="I57" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="J57" s="8">
-        <v>1.2</v>
-      </c>
-      <c r="K57" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="L57" s="8">
-        <v>1</v>
-      </c>
-      <c r="M57" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="N57" s="8">
-        <v>1.2</v>
+      <c r="I57" s="8">
+        <v>1</v>
+      </c>
+      <c r="J57" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="K57" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="L57" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="M57" s="8">
+        <v>1</v>
+      </c>
+      <c r="N57" s="8" t="s">
+        <v>11</v>
       </c>
       <c r="O57" s="8">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="P57" s="8">
         <v>0.5</v>
@@ -4766,10 +5526,10 @@
         <v>0.5</v>
       </c>
       <c r="U57" s="8">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="V57" s="8">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="W57" s="8">
         <v>0.5</v>
@@ -4777,70 +5537,74 @@
       <c r="X57" s="8">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="58" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y57" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="58" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A58" s="7">
         <v>2021201017</v>
       </c>
-      <c r="B58" s="8">
+      <c r="B58" s="7">
+        <f>VLOOKUP(A58,[1]Planilha1!$B$2:$C$65,2,)</f>
+        <v>8.58</v>
+      </c>
+      <c r="C58" s="8">
         <v>0.6755773420479303</v>
       </c>
-      <c r="C58" s="8">
+      <c r="D58" s="8">
         <v>7.7255773420479308</v>
       </c>
-      <c r="D58" s="8">
+      <c r="E58" s="8">
         <v>7.05</v>
       </c>
-      <c r="E58" s="8" t="s">
+      <c r="F58" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="F58" s="8">
+      <c r="G58" s="8">
         <v>0.60000000000000009</v>
       </c>
-      <c r="G58" s="8" t="s">
+      <c r="H58" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="H58" s="8">
-        <v>1</v>
-      </c>
-      <c r="I58" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="J58" s="8">
-        <v>1.2</v>
-      </c>
-      <c r="K58" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="L58" s="8">
-        <v>1</v>
-      </c>
-      <c r="M58" s="8" t="s">
+      <c r="I58" s="8">
+        <v>1</v>
+      </c>
+      <c r="J58" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="K58" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="L58" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="M58" s="8">
+        <v>1</v>
+      </c>
+      <c r="N58" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="N58" s="8">
-        <v>0</v>
-      </c>
       <c r="O58" s="8">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="P58" s="8">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q58" s="8">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="R58" s="8">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="S58" s="8">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="T58" s="8">
         <v>0.25</v>
       </c>
       <c r="U58" s="8">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="V58" s="8">
         <v>0.5</v>
@@ -4851,73 +5615,77 @@
       <c r="X58" s="8">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="59" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y58" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="59" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A59" s="9">
         <v>2023101691</v>
       </c>
-      <c r="B59" s="8">
+      <c r="B59" s="9">
+        <f>VLOOKUP(A59,[1]Planilha1!$B$2:$C$65,2,)</f>
+        <v>2.0699999999999998</v>
+      </c>
+      <c r="C59" s="8">
         <v>0.62575163398692812</v>
       </c>
-      <c r="C59" s="8">
+      <c r="D59" s="8">
         <v>9.875751633986928</v>
       </c>
-      <c r="D59" s="8">
+      <c r="E59" s="8">
         <v>9.25</v>
       </c>
-      <c r="E59" s="8" t="s">
+      <c r="F59" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="F59" s="8">
+      <c r="G59" s="8">
         <v>0.60000000000000009</v>
       </c>
-      <c r="G59" s="8" t="s">
+      <c r="H59" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="H59" s="8">
-        <v>1</v>
-      </c>
-      <c r="I59" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="J59" s="8">
-        <v>1.2</v>
-      </c>
-      <c r="K59" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="L59" s="8">
-        <v>1</v>
-      </c>
-      <c r="M59" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="N59" s="8">
-        <v>1.2</v>
+      <c r="I59" s="8">
+        <v>1</v>
+      </c>
+      <c r="J59" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="K59" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="L59" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="M59" s="8">
+        <v>1</v>
+      </c>
+      <c r="N59" s="8" t="s">
+        <v>11</v>
       </c>
       <c r="O59" s="8">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="P59" s="8">
         <v>0.5</v>
       </c>
       <c r="Q59" s="8">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="R59" s="8">
         <v>0.25</v>
       </c>
       <c r="S59" s="8">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="T59" s="8">
         <v>0.5</v>
       </c>
       <c r="U59" s="8">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="V59" s="8">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="W59" s="8">
         <v>0.5</v>
@@ -4925,61 +5693,65 @@
       <c r="X59" s="8">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="60" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y59" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="60" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A60" s="7">
         <v>2024101770</v>
       </c>
-      <c r="B60" s="8">
+      <c r="B60" s="7">
+        <f>VLOOKUP(A60,[1]Planilha1!$B$2:$C$65,2,)</f>
+        <v>8.34</v>
+      </c>
+      <c r="C60" s="8">
         <v>0.94481481481481489</v>
       </c>
-      <c r="C60" s="8">
+      <c r="D60" s="8">
         <v>10.694814814814816</v>
       </c>
-      <c r="D60" s="8">
+      <c r="E60" s="8">
         <v>9.75</v>
       </c>
-      <c r="E60" s="8" t="s">
+      <c r="F60" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="F60" s="8">
+      <c r="G60" s="8">
         <v>0.60000000000000009</v>
       </c>
-      <c r="G60" s="8" t="s">
+      <c r="H60" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="H60" s="8">
-        <v>1</v>
-      </c>
-      <c r="I60" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="J60" s="8">
-        <v>1.2</v>
-      </c>
-      <c r="K60" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="L60" s="8">
-        <v>1</v>
-      </c>
-      <c r="M60" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="N60" s="8">
-        <v>1.2</v>
+      <c r="I60" s="8">
+        <v>1</v>
+      </c>
+      <c r="J60" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="K60" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="L60" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="M60" s="8">
+        <v>1</v>
+      </c>
+      <c r="N60" s="8" t="s">
+        <v>11</v>
       </c>
       <c r="O60" s="8">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="P60" s="8">
         <v>0.5</v>
       </c>
       <c r="Q60" s="8">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="R60" s="8">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="S60" s="8">
         <v>0.5</v>
@@ -4999,64 +5771,68 @@
       <c r="X60" s="8">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="61" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y60" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="61" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A61" s="9">
         <v>2022200727</v>
       </c>
-      <c r="B61" s="8">
+      <c r="B61" s="9">
+        <f>VLOOKUP(A61,[1]Planilha1!$B$2:$C$65,2,)</f>
+        <v>5.3</v>
+      </c>
+      <c r="C61" s="8">
         <v>0.84722222222222221</v>
       </c>
-      <c r="C61" s="8">
+      <c r="D61" s="8">
         <v>10.347222222222221</v>
       </c>
-      <c r="D61" s="8">
+      <c r="E61" s="8">
         <v>9.5</v>
       </c>
-      <c r="E61" s="8" t="s">
+      <c r="F61" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="F61" s="8">
+      <c r="G61" s="8">
         <v>0.60000000000000009</v>
       </c>
-      <c r="G61" s="8" t="s">
+      <c r="H61" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="H61" s="8">
-        <v>1</v>
-      </c>
-      <c r="I61" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="J61" s="8">
-        <v>1.2</v>
-      </c>
-      <c r="K61" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="L61" s="8">
-        <v>1</v>
-      </c>
-      <c r="M61" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="N61" s="8">
-        <v>1.2</v>
+      <c r="I61" s="8">
+        <v>1</v>
+      </c>
+      <c r="J61" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="K61" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="L61" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="M61" s="8">
+        <v>1</v>
+      </c>
+      <c r="N61" s="8" t="s">
+        <v>11</v>
       </c>
       <c r="O61" s="8">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="P61" s="8">
         <v>0.5</v>
       </c>
       <c r="Q61" s="8">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="R61" s="8">
         <v>0.25</v>
       </c>
       <c r="S61" s="8">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="T61" s="8">
         <v>0.5</v>
@@ -5073,58 +5849,62 @@
       <c r="X61" s="8">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="62" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y61" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="62" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A62" s="7">
         <v>2023101729</v>
       </c>
-      <c r="B62" s="8">
+      <c r="B62" s="7">
+        <f>VLOOKUP(A62,[1]Planilha1!$B$2:$C$65,2,)</f>
+        <v>8.9</v>
+      </c>
+      <c r="C62" s="8">
         <v>0.59111111111111103</v>
       </c>
-      <c r="C62" s="8">
+      <c r="D62" s="8">
         <v>6.641111111111111</v>
       </c>
-      <c r="D62" s="8">
+      <c r="E62" s="8">
         <v>6.05</v>
       </c>
-      <c r="E62" s="8" t="s">
+      <c r="F62" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="F62" s="8">
+      <c r="G62" s="8">
         <v>0.60000000000000009</v>
       </c>
-      <c r="G62" s="8" t="s">
+      <c r="H62" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="H62" s="8">
+      <c r="I62" s="8">
         <v>0.9</v>
       </c>
-      <c r="I62" s="8" t="s">
+      <c r="J62" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="J62" s="8">
+      <c r="K62" s="8">
         <v>0.6</v>
       </c>
-      <c r="K62" s="8" t="s">
+      <c r="L62" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="L62" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="M62" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="N62" s="8">
-        <v>1.2</v>
+      <c r="M62" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="N62" s="8" t="s">
+        <v>11</v>
       </c>
       <c r="O62" s="8">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="P62" s="8">
         <v>0.5</v>
       </c>
       <c r="Q62" s="8">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="R62" s="8">
         <v>0.25</v>
@@ -5133,7 +5913,7 @@
         <v>0.25</v>
       </c>
       <c r="T62" s="8">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="U62" s="8">
         <v>0</v>
@@ -5142,66 +5922,70 @@
         <v>0</v>
       </c>
       <c r="W62" s="8">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="X62" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="1:24" x14ac:dyDescent="0.2">
+        <v>0.5</v>
+      </c>
+      <c r="Y62" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A63" s="9">
         <v>2023100965</v>
       </c>
-      <c r="B63" s="8">
+      <c r="B63" s="9">
+        <f>VLOOKUP(A63,[1]Planilha1!$B$2:$C$65,2,)</f>
+        <v>6.41</v>
+      </c>
+      <c r="C63" s="8">
         <v>0.52026143790849666</v>
       </c>
-      <c r="C63" s="8">
+      <c r="D63" s="8">
         <v>7.1702614379084961</v>
       </c>
-      <c r="D63" s="8">
+      <c r="E63" s="8">
         <v>6.6499999999999995</v>
       </c>
-      <c r="E63" s="8" t="s">
+      <c r="F63" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="F63" s="8">
+      <c r="G63" s="8">
         <v>0.60000000000000009</v>
       </c>
-      <c r="G63" s="8" t="s">
+      <c r="H63" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="H63" s="8">
-        <v>1</v>
-      </c>
-      <c r="I63" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="J63" s="8">
-        <v>1.2</v>
-      </c>
-      <c r="K63" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="L63" s="8">
-        <v>1</v>
-      </c>
-      <c r="M63" s="8" t="s">
+      <c r="I63" s="8">
+        <v>1</v>
+      </c>
+      <c r="J63" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="K63" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="L63" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="M63" s="8">
+        <v>1</v>
+      </c>
+      <c r="N63" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="N63" s="8">
+      <c r="O63" s="8">
         <v>0.6</v>
       </c>
-      <c r="O63" s="8">
-        <v>0.5</v>
-      </c>
       <c r="P63" s="8">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q63" s="8">
         <v>0</v>
       </c>
       <c r="R63" s="8">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="S63" s="8">
         <v>0.5</v>
@@ -5210,10 +5994,10 @@
         <v>0.5</v>
       </c>
       <c r="U63" s="8">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="V63" s="8">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="W63" s="8">
         <v>0</v>
@@ -5221,61 +6005,65 @@
       <c r="X63" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y63" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A64" s="7">
         <v>2024101155</v>
       </c>
-      <c r="B64" s="8">
+      <c r="B64" s="7">
+        <f>VLOOKUP(A64,[1]Planilha1!$B$2:$C$65,2,)</f>
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="C64" s="8">
         <v>0.78740740740740744</v>
       </c>
-      <c r="C64" s="8">
+      <c r="D64" s="8">
         <v>9.6874074074074059</v>
       </c>
-      <c r="D64" s="8">
+      <c r="E64" s="8">
         <v>8.8999999999999986</v>
       </c>
-      <c r="E64" s="8" t="s">
+      <c r="F64" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="F64" s="8">
+      <c r="G64" s="8">
         <v>0.60000000000000009</v>
       </c>
-      <c r="G64" s="8" t="s">
+      <c r="H64" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="H64" s="8">
-        <v>1</v>
-      </c>
-      <c r="I64" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="J64" s="8">
-        <v>1.2</v>
-      </c>
-      <c r="K64" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="L64" s="8">
-        <v>1</v>
-      </c>
-      <c r="M64" s="8" t="s">
+      <c r="I64" s="8">
+        <v>1</v>
+      </c>
+      <c r="J64" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="K64" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="L64" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="M64" s="8">
+        <v>1</v>
+      </c>
+      <c r="N64" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="N64" s="8">
+      <c r="O64" s="8">
         <v>0.6</v>
       </c>
-      <c r="O64" s="8">
-        <v>0.5</v>
-      </c>
       <c r="P64" s="8">
         <v>0.5</v>
       </c>
       <c r="Q64" s="8">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="R64" s="8">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="S64" s="8">
         <v>0.5</v>
@@ -5284,10 +6072,10 @@
         <v>0.5</v>
       </c>
       <c r="U64" s="8">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="V64" s="8">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="W64" s="8">
         <v>0.5</v>
@@ -5295,52 +6083,56 @@
       <c r="X64" s="8">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="65" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y64" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="65" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A65" s="9">
         <v>2023200064</v>
       </c>
-      <c r="B65" s="8">
+      <c r="B65" s="9">
+        <f>VLOOKUP(A65,[1]Planilha1!$B$2:$C$65,2,)</f>
+        <v>9.56</v>
+      </c>
+      <c r="C65" s="8">
         <v>0.71650326797385622</v>
       </c>
-      <c r="C65" s="8">
+      <c r="D65" s="8">
         <v>10.216503267973856</v>
       </c>
-      <c r="D65" s="8">
+      <c r="E65" s="8">
         <v>9.5</v>
       </c>
-      <c r="E65" s="8" t="s">
+      <c r="F65" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="F65" s="8">
+      <c r="G65" s="8">
         <v>0.60000000000000009</v>
       </c>
-      <c r="G65" s="8" t="s">
+      <c r="H65" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="H65" s="8">
-        <v>1</v>
-      </c>
-      <c r="I65" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="J65" s="8">
-        <v>1.2</v>
-      </c>
-      <c r="K65" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="L65" s="8">
-        <v>1</v>
-      </c>
-      <c r="M65" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="N65" s="8">
-        <v>1.2</v>
+      <c r="I65" s="8">
+        <v>1</v>
+      </c>
+      <c r="J65" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="K65" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="L65" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="M65" s="8">
+        <v>1</v>
+      </c>
+      <c r="N65" s="8" t="s">
+        <v>11</v>
       </c>
       <c r="O65" s="8">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="P65" s="8">
         <v>0.5</v>
@@ -5367,6 +6159,9 @@
         <v>0.5</v>
       </c>
       <c r="X65" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="Y65" s="8">
         <v>0</v>
       </c>
     </row>

--- a/notas.xlsx
+++ b/notas.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11109"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuário\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/daniloas.com/projetos/FertilidadeSoloAlegreUFES/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6BAF103-AE4A-418F-BD93-6B096AAB85C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0144A63-03ED-0D46-8EF9-2F7E21146938}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11310" xr2:uid="{BB9E0E1E-73DF-4AB6-A949-07A69840CAF7}"/>
+    <workbookView xWindow="0" yWindow="620" windowWidth="28800" windowHeight="17380" xr2:uid="{BB9E0E1E-73DF-4AB6-A949-07A69840CAF7}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="27">
   <si>
     <t>Matrícula</t>
   </si>
@@ -90,9 +90,6 @@
   </si>
   <si>
     <t>0/2</t>
-  </si>
-  <si>
-    <t>2/6</t>
   </si>
   <si>
     <t>6/10</t>
@@ -251,7 +248,7 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1115,29 +1112,29 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCC50A17-1BAD-4261-9C73-1273FB998B6D}">
   <dimension ref="A1:Y65"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11" customWidth="1"/>
-    <col min="3" max="3" width="16.28515625" customWidth="1"/>
+    <col min="3" max="3" width="16.33203125" customWidth="1"/>
     <col min="4" max="4" width="17" customWidth="1"/>
-    <col min="5" max="5" width="26.5703125" customWidth="1"/>
+    <col min="5" max="5" width="26.5" customWidth="1"/>
     <col min="6" max="6" width="7" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:25" ht="33" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>25</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>26</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>14</v>
@@ -1203,7 +1200,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A2" s="7">
         <v>2023200939</v>
       </c>
@@ -1281,7 +1278,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A3" s="9">
         <v>2023100005</v>
       </c>
@@ -1359,7 +1356,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A4" s="7">
         <v>2021101895</v>
       </c>
@@ -1437,7 +1434,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="9">
         <v>2024101156</v>
       </c>
@@ -1515,7 +1512,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A6" s="7">
         <v>2023200783</v>
       </c>
@@ -1593,7 +1590,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A7" s="9">
         <v>2022200360</v>
       </c>
@@ -1671,7 +1668,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A8" s="7">
         <v>2024101774</v>
       </c>
@@ -1749,7 +1746,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A9" s="9">
         <v>2024203414</v>
       </c>
@@ -1827,7 +1824,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A10" s="7">
         <v>2023101046</v>
       </c>
@@ -1905,7 +1902,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A11" s="9">
         <v>2019109848</v>
       </c>
@@ -1953,7 +1950,7 @@
       <c r="X11" s="8"/>
       <c r="Y11" s="8"/>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A12" s="7">
         <v>2023102012</v>
       </c>
@@ -1965,10 +1962,10 @@
         <v>0.71433551198257073</v>
       </c>
       <c r="D12" s="8">
-        <v>5.1643355119825713</v>
+        <v>6.86</v>
       </c>
       <c r="E12" s="8">
-        <v>4.45</v>
+        <v>6.15</v>
       </c>
       <c r="F12" s="8" t="s">
         <v>13</v>
@@ -1989,13 +1986,13 @@
         <v>0.6</v>
       </c>
       <c r="L12" s="8" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="M12" s="8">
         <v>0</v>
       </c>
       <c r="N12" s="8" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="O12" s="8">
         <v>0</v>
@@ -2031,7 +2028,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A13" s="9">
         <v>2024101768</v>
       </c>
@@ -2109,7 +2106,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A14" s="7">
         <v>2018104222</v>
       </c>
@@ -2187,7 +2184,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A15" s="9">
         <v>2017102706</v>
       </c>
@@ -2205,13 +2202,13 @@
         <v>4.5</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G15" s="8">
         <v>0</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I15" s="8">
         <v>0</v>
@@ -2265,7 +2262,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A16" s="7">
         <v>2024103491</v>
       </c>
@@ -2343,7 +2340,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A17" s="9">
         <v>2023100158</v>
       </c>
@@ -2421,7 +2418,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A18" s="7">
         <v>2024101776</v>
       </c>
@@ -2499,7 +2496,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A19" s="9">
         <v>2020102895</v>
       </c>
@@ -2511,10 +2508,10 @@
         <v>0.77559912854030499</v>
       </c>
       <c r="D19" s="8">
-        <v>5.1255991285403049</v>
+        <v>6.63</v>
       </c>
       <c r="E19" s="8">
-        <v>4.3499999999999996</v>
+        <v>5.85</v>
       </c>
       <c r="F19" s="8" t="s">
         <v>13</v>
@@ -2568,16 +2565,16 @@
         <v>0.25</v>
       </c>
       <c r="W19" s="8">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="X19" s="8">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Y19" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:25" x14ac:dyDescent="0.25">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A20" s="7">
         <v>2018104240</v>
       </c>
@@ -2595,7 +2592,7 @@
         <v>5.7</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G20" s="8">
         <v>0</v>
@@ -2655,7 +2652,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A21" s="9">
         <v>2024101764</v>
       </c>
@@ -2733,7 +2730,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="22" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A22" s="7">
         <v>2022102060</v>
       </c>
@@ -2751,13 +2748,13 @@
         <v>1.75</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G22" s="8">
         <v>0</v>
       </c>
       <c r="H22" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I22" s="8">
         <v>0</v>
@@ -2811,7 +2808,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A23" s="9">
         <v>2024103490</v>
       </c>
@@ -2889,7 +2886,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="24" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A24" s="7">
         <v>2023100771</v>
       </c>
@@ -2901,10 +2898,10 @@
         <v>0.60129629629629633</v>
       </c>
       <c r="D24" s="8">
-        <v>6.951296296296297</v>
+        <v>8.65</v>
       </c>
       <c r="E24" s="8">
-        <v>6.35</v>
+        <v>8.0500000000000007</v>
       </c>
       <c r="F24" s="8" t="s">
         <v>13</v>
@@ -2919,19 +2916,19 @@
         <v>1</v>
       </c>
       <c r="J24" s="8" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="K24" s="8">
         <v>0</v>
       </c>
       <c r="L24" s="8" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="M24" s="8">
         <v>0</v>
       </c>
       <c r="N24" s="8" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="O24" s="8">
         <v>0</v>
@@ -2967,7 +2964,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="25" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A25" s="9">
         <v>2023100962</v>
       </c>
@@ -2991,7 +2988,7 @@
         <v>0.4</v>
       </c>
       <c r="H25" s="8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I25" s="8">
         <v>0.60000000000000009</v>
@@ -3045,7 +3042,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A26" s="7">
         <v>2021101361</v>
       </c>
@@ -3087,7 +3084,7 @@
         <v>1</v>
       </c>
       <c r="N26" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="O26" s="8">
         <v>0</v>
@@ -3123,7 +3120,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A27" s="9">
         <v>2023201341</v>
       </c>
@@ -3201,7 +3198,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="28" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A28" s="7">
         <v>2023101463</v>
       </c>
@@ -3279,7 +3276,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A29" s="9">
         <v>2022201037</v>
       </c>
@@ -3357,7 +3354,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="30" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A30" s="7">
         <v>2021101896</v>
       </c>
@@ -3435,7 +3432,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="31" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A31" s="9">
         <v>2022201042</v>
       </c>
@@ -3513,7 +3510,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="32" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A32" s="7">
         <v>2020102888</v>
       </c>
@@ -3525,19 +3522,19 @@
         <v>0.75833333333333341</v>
       </c>
       <c r="D32" s="8">
-        <v>8.7083333333333339</v>
+        <v>10.01</v>
       </c>
       <c r="E32" s="8">
-        <v>7.95</v>
+        <v>9.25</v>
       </c>
       <c r="F32" s="8" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G32" s="8">
         <v>0.2</v>
       </c>
       <c r="H32" s="8" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="I32" s="8">
         <v>0.60000000000000009</v>
@@ -3588,10 +3585,10 @@
         <v>0.5</v>
       </c>
       <c r="Y32" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:25" x14ac:dyDescent="0.25">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A33" s="9">
         <v>2024101765</v>
       </c>
@@ -3669,7 +3666,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="34" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A34" s="7">
         <v>2022100612</v>
       </c>
@@ -3693,7 +3690,7 @@
         <v>0.60000000000000009</v>
       </c>
       <c r="H34" s="8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I34" s="8">
         <v>0.5</v>
@@ -3747,7 +3744,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="35" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A35" s="9">
         <v>2023101467</v>
       </c>
@@ -3771,7 +3768,7 @@
         <v>0.60000000000000009</v>
       </c>
       <c r="H35" s="8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I35" s="8">
         <v>0.5</v>
@@ -3825,7 +3822,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="36" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A36" s="7">
         <v>2022100511</v>
       </c>
@@ -3855,19 +3852,19 @@
         <v>1</v>
       </c>
       <c r="J36" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K36" s="8">
         <v>0</v>
       </c>
       <c r="L36" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="M36" s="8">
         <v>0</v>
       </c>
       <c r="N36" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="O36" s="8">
         <v>0</v>
@@ -3903,7 +3900,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="37" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A37" s="9">
         <v>2023200147</v>
       </c>
@@ -3981,7 +3978,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="38" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A38" s="7">
         <v>2023100776</v>
       </c>
@@ -4059,7 +4056,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="39" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A39" s="9">
         <v>2024101158</v>
       </c>
@@ -4137,7 +4134,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="40" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A40" s="7">
         <v>2024101773</v>
       </c>
@@ -4215,7 +4212,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="41" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A41" s="9">
         <v>2023100068</v>
       </c>
@@ -4239,7 +4236,7 @@
         <v>0.60000000000000009</v>
       </c>
       <c r="H41" s="8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I41" s="8">
         <v>0.70000000000000007</v>
@@ -4293,7 +4290,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="42" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A42" s="7">
         <v>2023200790</v>
       </c>
@@ -4371,7 +4368,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A43" s="9">
         <v>2022200719</v>
       </c>
@@ -4449,7 +4446,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="44" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A44" s="8">
         <v>2025201178</v>
       </c>
@@ -4527,7 +4524,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A45" s="9">
         <v>2024101775</v>
       </c>
@@ -4605,7 +4602,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="46" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A46" s="7">
         <v>2024103187</v>
       </c>
@@ -4683,7 +4680,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="47" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A47" s="9">
         <v>2023102386</v>
       </c>
@@ -4761,7 +4758,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="48" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A48" s="7">
         <v>2020101654</v>
       </c>
@@ -4785,7 +4782,7 @@
         <v>0.60000000000000009</v>
       </c>
       <c r="H48" s="8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I48" s="8">
         <v>0.60000000000000009</v>
@@ -4839,7 +4836,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="49" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A49" s="9">
         <v>2022201082</v>
       </c>
@@ -4863,7 +4860,7 @@
         <v>0.60000000000000009</v>
       </c>
       <c r="H49" s="8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I49" s="8">
         <v>0.9</v>
@@ -4917,7 +4914,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="50" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A50" s="7">
         <v>2024101769</v>
       </c>
@@ -4995,7 +4992,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="51" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A51" s="9">
         <v>2024101154</v>
       </c>
@@ -5073,7 +5070,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="52" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A52" s="7">
         <v>2022102045</v>
       </c>
@@ -5151,7 +5148,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="53" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A53" s="9">
         <v>2023101690</v>
       </c>
@@ -5229,7 +5226,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="54" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A54" s="7">
         <v>2023100954</v>
       </c>
@@ -5307,7 +5304,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="55" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A55" s="9">
         <v>2024202997</v>
       </c>
@@ -5325,7 +5322,7 @@
         <v>7.65</v>
       </c>
       <c r="F55" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G55" s="8">
         <v>0</v>
@@ -5385,7 +5382,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A56" s="7">
         <v>2020101573</v>
       </c>
@@ -5463,7 +5460,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A57" s="9">
         <v>2024101785</v>
       </c>
@@ -5541,7 +5538,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="58" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A58" s="7">
         <v>2021201017</v>
       </c>
@@ -5619,7 +5616,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="59" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A59" s="9">
         <v>2023101691</v>
       </c>
@@ -5697,7 +5694,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="60" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A60" s="7">
         <v>2024101770</v>
       </c>
@@ -5775,7 +5772,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="61" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A61" s="9">
         <v>2022200727</v>
       </c>
@@ -5853,7 +5850,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="62" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A62" s="7">
         <v>2023101729</v>
       </c>
@@ -5877,7 +5874,7 @@
         <v>0.60000000000000009</v>
       </c>
       <c r="H62" s="8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I62" s="8">
         <v>0.9</v>
@@ -5931,7 +5928,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A63" s="9">
         <v>2023100965</v>
       </c>
@@ -6009,7 +6006,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A64" s="7">
         <v>2024101155</v>
       </c>
@@ -6087,7 +6084,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="65" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A65" s="9">
         <v>2023200064</v>
       </c>

--- a/notas.xlsx
+++ b/notas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/daniloas.com/projetos/FertilidadeSoloAlegreUFES/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0144A63-03ED-0D46-8EF9-2F7E21146938}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BAB08DF-B336-0541-B5D4-81D049ABFB83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="28800" windowHeight="17380" xr2:uid="{BB9E0E1E-73DF-4AB6-A949-07A69840CAF7}"/>
   </bookViews>
@@ -1989,13 +1989,13 @@
         <v>12</v>
       </c>
       <c r="M12" s="8">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="N12" s="8" t="s">
         <v>11</v>
       </c>
       <c r="O12" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P12" s="8">
         <v>0.5</v>
@@ -2919,19 +2919,19 @@
         <v>12</v>
       </c>
       <c r="K24" s="8">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="L24" s="8" t="s">
         <v>12</v>
       </c>
       <c r="M24" s="8">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="N24" s="8" t="s">
         <v>12</v>
       </c>
       <c r="O24" s="8">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="P24" s="8">
         <v>0.5</v>

--- a/notas.xlsx
+++ b/notas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/daniloas.com/projetos/FertilidadeSoloAlegreUFES/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BAB08DF-B336-0541-B5D4-81D049ABFB83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAB229BC-90E7-6E41-95BA-01BA65898498}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="28800" windowHeight="17380" xr2:uid="{BB9E0E1E-73DF-4AB6-A949-07A69840CAF7}"/>
   </bookViews>
@@ -3531,13 +3531,13 @@
         <v>13</v>
       </c>
       <c r="G32" s="8">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="H32" s="8" t="s">
         <v>10</v>
       </c>
       <c r="I32" s="8">
-        <v>0.60000000000000009</v>
+        <v>1</v>
       </c>
       <c r="J32" s="8" t="s">
         <v>11</v>
